--- a/VENTAS TOTALES 2026.xlsx
+++ b/VENTAS TOTALES 2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="419">
   <si>
     <t>FECHA</t>
   </si>
@@ -256,6 +256,12 @@
     <t>30-04-2026</t>
   </si>
   <si>
+    <t>06-05-2026</t>
+  </si>
+  <si>
+    <t>07-05-2026</t>
+  </si>
+  <si>
     <t>1 TINTA CYAN S40600</t>
   </si>
   <si>
@@ -760,6 +766,12 @@
     <t>3 TINTAS F6470: CYAN, YELLOW, HDK</t>
   </si>
   <si>
+    <t>4 T53K220 CYAN F64/F95, 3 T53K920 HDK F64/F95, 3 T53K320 MAGENTA F64/F95, 2 T53K420 YELLOW F64/F95</t>
+  </si>
+  <si>
+    <t>12 T53K220 CYAN F64/F95, 4 T53K920 HDK F64/F95, 4 T53K420 YELLOW F64/F95</t>
+  </si>
+  <si>
     <t>WIDMER GRAPHIC</t>
   </si>
   <si>
@@ -1099,6 +1111,9 @@
     <t>RODRIGO RIVAS</t>
   </si>
   <si>
+    <t>Roberto Dutra</t>
+  </si>
+  <si>
     <t>ALBERTO</t>
   </si>
   <si>
@@ -1132,6 +1147,9 @@
     <t>QR</t>
   </si>
   <si>
+    <t>CONTADO</t>
+  </si>
+  <si>
     <t>SC-102</t>
   </si>
   <si>
@@ -1234,6 +1252,12 @@
     <t>SC-085</t>
   </si>
   <si>
+    <t>SC-120, SC-121, SC-123, SC-122</t>
+  </si>
+  <si>
+    <t>SC-120, SC-121, SC-122</t>
+  </si>
+  <si>
     <t>INSUMOS</t>
   </si>
   <si>
@@ -1244,6 +1268,9 @@
   </si>
   <si>
     <t>ACCESORIOS</t>
+  </si>
+  <si>
+    <t>CORP</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J233"/>
+  <dimension ref="A1:J236"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1641,10 +1668,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D2">
         <v>985000</v>
@@ -1653,16 +1680,16 @@
         <v>268</v>
       </c>
       <c r="G2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J2" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1670,10 +1697,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D3">
         <v>5292000</v>
@@ -1682,16 +1709,16 @@
         <v>269</v>
       </c>
       <c r="G3" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H3" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J3" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1699,10 +1726,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D4">
         <v>2180000</v>
@@ -1711,16 +1738,16 @@
         <v>270</v>
       </c>
       <c r="G4" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I4" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J4" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1728,10 +1755,10 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E5">
         <v>1808</v>
@@ -1740,16 +1767,16 @@
         <v>271</v>
       </c>
       <c r="G5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H5" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I5" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J5" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1757,10 +1784,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E6">
         <v>6850.19</v>
@@ -1769,7 +1796,7 @@
         <v>272</v>
       </c>
       <c r="G6" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1777,10 +1804,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D7">
         <v>6051000</v>
@@ -1789,16 +1816,16 @@
         <v>273</v>
       </c>
       <c r="G7" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H7" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I7" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J7" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1806,10 +1833,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D8">
         <v>985000</v>
@@ -1818,16 +1845,16 @@
         <v>274</v>
       </c>
       <c r="G8" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H8" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I8" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J8" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1835,10 +1862,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D9">
         <v>12348000</v>
@@ -1847,16 +1874,16 @@
         <v>275</v>
       </c>
       <c r="G9" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H9" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I9" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J9" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1864,10 +1891,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D10">
         <v>550000</v>
@@ -1876,16 +1903,16 @@
         <v>276</v>
       </c>
       <c r="G10" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H10" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I10" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J10" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1893,10 +1920,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D11">
         <v>57590000</v>
@@ -1905,24 +1932,24 @@
         <v>277</v>
       </c>
       <c r="G11" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H11" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I11" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="J11" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F12">
         <v>278</v>
@@ -1930,10 +1957,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F13">
         <v>279</v>
@@ -1944,10 +1971,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D14">
         <v>9590000</v>
@@ -1956,16 +1983,16 @@
         <v>280</v>
       </c>
       <c r="G14" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H14" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I14" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="J14" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1973,10 +2000,10 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D15">
         <v>7900000</v>
@@ -1985,16 +2012,16 @@
         <v>281</v>
       </c>
       <c r="G15" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H15" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I15" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="J15" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2002,10 +2029,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E16">
         <v>2298</v>
@@ -2014,16 +2041,16 @@
         <v>282</v>
       </c>
       <c r="G16" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H16" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I16" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J16" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2031,10 +2058,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D17">
         <v>995000</v>
@@ -2043,16 +2070,16 @@
         <v>283</v>
       </c>
       <c r="G17" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H17" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I17" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J17" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2060,10 +2087,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E18">
         <v>1400</v>
@@ -2077,10 +2104,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D19">
         <v>3528000</v>
@@ -2089,16 +2116,16 @@
         <v>285</v>
       </c>
       <c r="G19" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H19" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I19" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J19" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2106,10 +2133,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D20">
         <v>4320000</v>
@@ -2118,16 +2145,16 @@
         <v>286</v>
       </c>
       <c r="G20" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H20" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I20" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J20" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -2135,10 +2162,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D21">
         <v>1990000</v>
@@ -2147,16 +2174,16 @@
         <v>287</v>
       </c>
       <c r="G21" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H21" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I21" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J21" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2164,10 +2191,10 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D22">
         <v>3990000</v>
@@ -2176,16 +2203,16 @@
         <v>288</v>
       </c>
       <c r="G22" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H22" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I22" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="J22" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2193,10 +2220,10 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D23">
         <v>5190000</v>
@@ -2205,16 +2232,16 @@
         <v>289</v>
       </c>
       <c r="G23" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H23" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I23" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="J23" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2222,10 +2249,10 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D24">
         <v>939000</v>
@@ -2234,16 +2261,16 @@
         <v>290</v>
       </c>
       <c r="G24" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H24" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I24" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J24" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2251,10 +2278,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D25">
         <v>1080000</v>
@@ -2263,13 +2290,13 @@
         <v>291</v>
       </c>
       <c r="G25" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="I25" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J25" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2277,10 +2304,10 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D26">
         <v>1500000</v>
@@ -2289,7 +2316,7 @@
         <v>292</v>
       </c>
       <c r="G26" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2297,10 +2324,10 @@
         <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D27">
         <v>2890000</v>
@@ -2309,16 +2336,16 @@
         <v>293</v>
       </c>
       <c r="G27" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H27" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I27" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="J27" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2326,10 +2353,10 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D28">
         <v>3160000</v>
@@ -2338,16 +2365,16 @@
         <v>294</v>
       </c>
       <c r="G28" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H28" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I28" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J28" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2355,10 +2382,10 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E29">
         <v>1356</v>
@@ -2367,16 +2394,16 @@
         <v>295</v>
       </c>
       <c r="G29" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H29" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I29" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J29" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2384,10 +2411,10 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D30">
         <v>5190000</v>
@@ -2396,16 +2423,16 @@
         <v>296</v>
       </c>
       <c r="G30" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H30" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I30" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="J30" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2413,10 +2440,10 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D31">
         <v>4590000</v>
@@ -2425,16 +2452,16 @@
         <v>297</v>
       </c>
       <c r="G31" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H31" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I31" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="J31" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2442,10 +2469,10 @@
         <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D32">
         <v>13850000</v>
@@ -2454,16 +2481,16 @@
         <v>298</v>
       </c>
       <c r="G32" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H32" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I32" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="J32" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2471,10 +2498,10 @@
         <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D33">
         <v>2370000</v>
@@ -2483,16 +2510,16 @@
         <v>299</v>
       </c>
       <c r="G33" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H33" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I33" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J33" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2500,10 +2527,10 @@
         <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D34">
         <v>3160000</v>
@@ -2512,16 +2539,16 @@
         <v>301</v>
       </c>
       <c r="G34" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H34" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I34" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J34" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2529,10 +2556,10 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D35">
         <v>199000</v>
@@ -2541,16 +2568,16 @@
         <v>302</v>
       </c>
       <c r="G35" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I35" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J35" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2558,10 +2585,10 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D36">
         <v>3290000</v>
@@ -2570,16 +2597,16 @@
         <v>303</v>
       </c>
       <c r="G36" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H36" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I36" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="J36" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2587,10 +2614,10 @@
         <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D37">
         <v>12080000</v>
@@ -2599,16 +2626,16 @@
         <v>304</v>
       </c>
       <c r="G37" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H37" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I37" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="J37" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2616,10 +2643,10 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D38">
         <v>2370000</v>
@@ -2628,16 +2655,16 @@
         <v>305</v>
       </c>
       <c r="G38" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H38" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I38" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J38" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2645,10 +2672,10 @@
         <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C39" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D39">
         <v>199000</v>
@@ -2657,16 +2684,16 @@
         <v>306</v>
       </c>
       <c r="G39" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H39" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I39" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J39" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2674,10 +2701,10 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D40">
         <v>2590000</v>
@@ -2686,16 +2713,16 @@
         <v>307</v>
       </c>
       <c r="G40" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H40" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I40" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="J40" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2703,10 +2730,10 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C41" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D41">
         <v>6390000</v>
@@ -2715,16 +2742,16 @@
         <v>308</v>
       </c>
       <c r="G41" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H41" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I41" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="J41" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2732,10 +2759,10 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D42">
         <v>6080000</v>
@@ -2744,16 +2771,16 @@
         <v>309</v>
       </c>
       <c r="G42" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H42" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I42" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J42" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2761,10 +2788,10 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D43">
         <v>7190000</v>
@@ -2773,16 +2800,16 @@
         <v>310</v>
       </c>
       <c r="G43" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H43" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I43" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="J43" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2790,10 +2817,10 @@
         <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F44">
         <v>311</v>
@@ -2804,10 +2831,10 @@
         <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C45" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D45">
         <v>1090000</v>
@@ -2816,16 +2843,16 @@
         <v>312</v>
       </c>
       <c r="G45" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H45" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I45" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J45" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2833,10 +2860,10 @@
         <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C46" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D46">
         <v>1320000</v>
@@ -2845,16 +2872,16 @@
         <v>313</v>
       </c>
       <c r="G46" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H46" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I46" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J46" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2862,10 +2889,10 @@
         <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D47">
         <v>209000</v>
@@ -2874,16 +2901,16 @@
         <v>314</v>
       </c>
       <c r="G47" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H47" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I47" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J47" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2891,10 +2918,10 @@
         <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C48" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D48">
         <v>6445000</v>
@@ -2903,16 +2930,16 @@
         <v>315</v>
       </c>
       <c r="G48" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H48" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I48" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="J48" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2920,10 +2947,10 @@
         <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E49">
         <v>2712</v>
@@ -2932,16 +2959,16 @@
         <v>316</v>
       </c>
       <c r="G49" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H49" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I49" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J49" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2949,10 +2976,10 @@
         <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D50">
         <v>395000</v>
@@ -2961,16 +2988,16 @@
         <v>317</v>
       </c>
       <c r="G50" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H50" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I50" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="J50" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2978,10 +3005,10 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D51">
         <v>812000</v>
@@ -2990,16 +3017,16 @@
         <v>318</v>
       </c>
       <c r="G51" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H51" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I51" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J51" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -3007,10 +3034,10 @@
         <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D52">
         <v>50000000</v>
@@ -3019,10 +3046,10 @@
         <v>319</v>
       </c>
       <c r="G52" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H52" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -3030,10 +3057,10 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E53">
         <v>22390</v>
@@ -3042,16 +3069,16 @@
         <v>320</v>
       </c>
       <c r="G53" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H53" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I53" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="J53" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -3059,10 +3086,10 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D54">
         <v>405000</v>
@@ -3071,16 +3098,16 @@
         <v>321</v>
       </c>
       <c r="G54" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H54" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I54" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J54" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -3088,10 +3115,10 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D55">
         <v>7512000</v>
@@ -3100,16 +3127,16 @@
         <v>322</v>
       </c>
       <c r="G55" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H55" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I55" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J55" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -3117,10 +3144,10 @@
         <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E56">
         <v>1356</v>
@@ -3129,16 +3156,16 @@
         <v>323</v>
       </c>
       <c r="G56" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H56" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I56" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J56" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -3146,10 +3173,10 @@
         <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C57" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D57">
         <v>3790000</v>
@@ -3158,16 +3185,16 @@
         <v>324</v>
       </c>
       <c r="G57" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H57" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I57" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="J57" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -3175,10 +3202,10 @@
         <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C58" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D58">
         <v>11790000</v>
@@ -3187,16 +3214,16 @@
         <v>325</v>
       </c>
       <c r="G58" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H58" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I58" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="J58" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -3204,10 +3231,10 @@
         <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C59" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D59">
         <v>498000</v>
@@ -3216,16 +3243,16 @@
         <v>326</v>
       </c>
       <c r="G59" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H59" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I59" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J59" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -3233,10 +3260,10 @@
         <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C60" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D60">
         <v>3345000</v>
@@ -3245,16 +3272,16 @@
         <v>327</v>
       </c>
       <c r="G60" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H60" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I60" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="J60" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -3262,10 +3289,10 @@
         <v>28</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D61">
         <v>2880000</v>
@@ -3274,16 +3301,16 @@
         <v>328</v>
       </c>
       <c r="G61" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H61" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I61" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J61" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -3291,10 +3318,10 @@
         <v>29</v>
       </c>
       <c r="B62" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C62" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D62">
         <v>419000</v>
@@ -3303,24 +3330,24 @@
         <v>329</v>
       </c>
       <c r="G62" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H62" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I62" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J62" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="B63" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F63">
         <v>330</v>
@@ -3331,10 +3358,10 @@
         <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C64" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D64">
         <v>14112000</v>
@@ -3343,16 +3370,16 @@
         <v>331</v>
       </c>
       <c r="G64" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H64" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I64" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J64" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -3360,10 +3387,10 @@
         <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C65" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D65">
         <v>65000</v>
@@ -3372,16 +3399,16 @@
         <v>332</v>
       </c>
       <c r="G65" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H65" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I65" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="J65" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -3389,10 +3416,10 @@
         <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C66" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D66">
         <v>498000</v>
@@ -3401,16 +3428,16 @@
         <v>333</v>
       </c>
       <c r="G66" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H66" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I66" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J66" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -3418,10 +3445,10 @@
         <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C67" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D67">
         <v>1585000</v>
@@ -3430,16 +3457,16 @@
         <v>334</v>
       </c>
       <c r="G67" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H67" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I67" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J67" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -3447,10 +3474,10 @@
         <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C68" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D68">
         <v>199000</v>
@@ -3459,24 +3486,24 @@
         <v>335</v>
       </c>
       <c r="G68" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H68" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I68" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J68" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="B69" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F69">
         <v>336</v>
@@ -3484,10 +3511,10 @@
     </row>
     <row r="70" spans="1:10">
       <c r="B70" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C70" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F70">
         <v>337</v>
@@ -3498,10 +3525,10 @@
         <v>30</v>
       </c>
       <c r="B71" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C71" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D71">
         <v>3160000</v>
@@ -3510,16 +3537,16 @@
         <v>338</v>
       </c>
       <c r="G71" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H71" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I71" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J71" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3527,10 +3554,10 @@
         <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C72" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D72">
         <v>3645000</v>
@@ -3539,16 +3566,16 @@
         <v>339</v>
       </c>
       <c r="G72" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H72" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="I72" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="J72" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -3556,10 +3583,10 @@
         <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C73" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D73">
         <v>890000</v>
@@ -3568,13 +3595,13 @@
         <v>340</v>
       </c>
       <c r="G73" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="I73" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J73" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3582,10 +3609,10 @@
         <v>31</v>
       </c>
       <c r="B74" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D74">
         <v>3240000</v>
@@ -3594,13 +3621,13 @@
         <v>341</v>
       </c>
       <c r="G74" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="I74" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J74" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3608,10 +3635,10 @@
         <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C75" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D75">
         <v>1970000</v>
@@ -3620,16 +3647,16 @@
         <v>342</v>
       </c>
       <c r="G75" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H75" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I75" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J75" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3637,10 +3664,10 @@
         <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C76" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D76">
         <v>1690000</v>
@@ -3649,16 +3676,16 @@
         <v>343</v>
       </c>
       <c r="G76" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H76" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I76" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="J76" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3666,10 +3693,10 @@
         <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C77" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D77">
         <v>6690000</v>
@@ -3678,16 +3705,16 @@
         <v>345</v>
       </c>
       <c r="G77" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H77" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I77" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="J77" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3695,10 +3722,10 @@
         <v>34</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C78" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D78">
         <v>405000</v>
@@ -3707,16 +3734,16 @@
         <v>346</v>
       </c>
       <c r="G78" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H78" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I78" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J78" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3724,10 +3751,10 @@
         <v>34</v>
       </c>
       <c r="B79" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C79" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D79">
         <v>2370000</v>
@@ -3736,16 +3763,16 @@
         <v>347</v>
       </c>
       <c r="G79" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H79" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I79" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J79" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3753,10 +3780,10 @@
         <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C80" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E80">
         <v>6257.66</v>
@@ -3765,7 +3792,7 @@
         <v>348</v>
       </c>
       <c r="G80" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3773,10 +3800,10 @@
         <v>34</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C81" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D81">
         <v>1635000</v>
@@ -3785,24 +3812,24 @@
         <v>349</v>
       </c>
       <c r="G81" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H81" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I81" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J81" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="B82" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C82" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F82">
         <v>350</v>
@@ -3813,10 +3840,10 @@
         <v>35</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C83" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D83">
         <v>990000</v>
@@ -3825,16 +3852,16 @@
         <v>351</v>
       </c>
       <c r="G83" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H83" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I83" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J83" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3842,10 +3869,10 @@
         <v>35</v>
       </c>
       <c r="B84" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D84">
         <v>1580000</v>
@@ -3854,16 +3881,16 @@
         <v>352</v>
       </c>
       <c r="G84" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H84" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I84" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J84" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3871,10 +3898,10 @@
         <v>36</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C85" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D85">
         <v>1970000</v>
@@ -3883,16 +3910,16 @@
         <v>353</v>
       </c>
       <c r="G85" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H85" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I85" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J85" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3900,10 +3927,10 @@
         <v>36</v>
       </c>
       <c r="B86" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C86" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D86">
         <v>5190000</v>
@@ -3912,16 +3939,16 @@
         <v>354</v>
       </c>
       <c r="G86" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H86" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I86" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="J86" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -3929,10 +3956,10 @@
         <v>36</v>
       </c>
       <c r="B87" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C87" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D87">
         <v>53800000</v>
@@ -3941,24 +3968,24 @@
         <v>355</v>
       </c>
       <c r="G87" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H87" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I87" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J87" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="B88" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F88">
         <v>356</v>
@@ -3969,10 +3996,10 @@
         <v>37</v>
       </c>
       <c r="B89" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C89" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D89">
         <v>4320000</v>
@@ -3981,16 +4008,16 @@
         <v>357</v>
       </c>
       <c r="G89" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H89" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I89" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J89" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -3998,10 +4025,10 @@
         <v>38</v>
       </c>
       <c r="B90" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C90" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D90">
         <v>1580000</v>
@@ -4010,16 +4037,16 @@
         <v>358</v>
       </c>
       <c r="G90" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H90" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I90" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J90" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -4027,10 +4054,10 @@
         <v>38</v>
       </c>
       <c r="B91" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C91" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D91">
         <v>11976000</v>
@@ -4039,16 +4066,16 @@
         <v>359</v>
       </c>
       <c r="G91" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H91" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I91" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J91" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -4056,10 +4083,10 @@
         <v>38</v>
       </c>
       <c r="B92" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C92" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D92">
         <v>1990000</v>
@@ -4068,16 +4095,16 @@
         <v>360</v>
       </c>
       <c r="G92" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H92" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I92" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J92" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -4085,10 +4112,10 @@
         <v>38</v>
       </c>
       <c r="B93" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D93">
         <v>3160000</v>
@@ -4097,16 +4124,16 @@
         <v>361</v>
       </c>
       <c r="G93" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H93" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I93" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J93" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -4114,10 +4141,10 @@
         <v>39</v>
       </c>
       <c r="B94" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C94" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E94">
         <v>3616</v>
@@ -4126,16 +4153,16 @@
         <v>362</v>
       </c>
       <c r="G94" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H94" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I94" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J94" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -4143,10 +4170,10 @@
         <v>39</v>
       </c>
       <c r="B95" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C95" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D95">
         <v>1980000</v>
@@ -4155,16 +4182,16 @@
         <v>363</v>
       </c>
       <c r="G95" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H95" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I95" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J95" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -4172,10 +4199,10 @@
         <v>39</v>
       </c>
       <c r="B96" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C96" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D96">
         <v>199000</v>
@@ -4184,16 +4211,16 @@
         <v>364</v>
       </c>
       <c r="G96" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H96" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I96" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J96" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -4201,10 +4228,10 @@
         <v>40</v>
       </c>
       <c r="B97" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C97" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D97">
         <v>199000</v>
@@ -4213,16 +4240,16 @@
         <v>365</v>
       </c>
       <c r="G97" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H97" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I97" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J97" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -4230,10 +4257,10 @@
         <v>40</v>
       </c>
       <c r="B98" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C98" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D98">
         <v>2958000</v>
@@ -4242,16 +4269,16 @@
         <v>366</v>
       </c>
       <c r="G98" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H98" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I98" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J98" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -4259,10 +4286,10 @@
         <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C99" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D99">
         <v>1980000</v>
@@ -4271,16 +4298,16 @@
         <v>367</v>
       </c>
       <c r="G99" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H99" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I99" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J99" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -4288,10 +4315,10 @@
         <v>41</v>
       </c>
       <c r="B100" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C100" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D100">
         <v>790000</v>
@@ -4300,16 +4327,16 @@
         <v>368</v>
       </c>
       <c r="G100" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H100" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I100" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J100" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -4317,10 +4344,10 @@
         <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C101" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D101">
         <v>200000</v>
@@ -4329,24 +4356,24 @@
         <v>369</v>
       </c>
       <c r="G101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H101" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I101" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J101" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="B102" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C102" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F102">
         <v>370</v>
@@ -4357,10 +4384,10 @@
         <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C103" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D103">
         <v>790000</v>
@@ -4369,16 +4396,16 @@
         <v>371</v>
       </c>
       <c r="G103" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H103" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I103" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J103" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -4386,10 +4413,10 @@
         <v>42</v>
       </c>
       <c r="B104" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C104" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D104">
         <v>199000</v>
@@ -4398,16 +4425,16 @@
         <v>372</v>
       </c>
       <c r="G104" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H104" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I104" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J104" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -4415,10 +4442,10 @@
         <v>42</v>
       </c>
       <c r="B105" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C105" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D105">
         <v>498000</v>
@@ -4427,16 +4454,16 @@
         <v>373</v>
       </c>
       <c r="G105" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H105" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I105" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J105" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -4444,10 +4471,10 @@
         <v>42</v>
       </c>
       <c r="B106" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C106" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D106">
         <v>7560000</v>
@@ -4456,16 +4483,16 @@
         <v>374</v>
       </c>
       <c r="G106" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H106" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I106" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J106" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -4473,10 +4500,10 @@
         <v>42</v>
       </c>
       <c r="B107" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C107" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D107">
         <v>209000</v>
@@ -4485,16 +4512,16 @@
         <v>375</v>
       </c>
       <c r="G107" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H107" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I107" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J107" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -4502,10 +4529,10 @@
         <v>43</v>
       </c>
       <c r="B108" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D108">
         <v>2880000</v>
@@ -4514,16 +4541,16 @@
         <v>376</v>
       </c>
       <c r="G108" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H108" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I108" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J108" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -4531,10 +4558,10 @@
         <v>44</v>
       </c>
       <c r="B109" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C109" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D109">
         <v>775000</v>
@@ -4543,16 +4570,16 @@
         <v>377</v>
       </c>
       <c r="G109" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H109" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I109" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J109" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -4560,10 +4587,10 @@
         <v>44</v>
       </c>
       <c r="B110" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C110" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E110">
         <v>3164</v>
@@ -4572,24 +4599,24 @@
         <v>378</v>
       </c>
       <c r="G110" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H110" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I110" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J110" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="B111" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C111" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F111">
         <v>379</v>
@@ -4597,10 +4624,10 @@
     </row>
     <row r="112" spans="1:10">
       <c r="B112" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C112" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F112">
         <v>380</v>
@@ -4611,10 +4638,10 @@
         <v>44</v>
       </c>
       <c r="B113" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C113" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D113">
         <v>6390000</v>
@@ -4623,16 +4650,16 @@
         <v>381</v>
       </c>
       <c r="G113" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H113" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I113" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="J113" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -4640,10 +4667,10 @@
         <v>45</v>
       </c>
       <c r="B114" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C114" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D114">
         <v>1635000</v>
@@ -4652,16 +4679,16 @@
         <v>382</v>
       </c>
       <c r="G114" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H114" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I114" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J114" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -4669,10 +4696,10 @@
         <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C115" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D115">
         <v>220000</v>
@@ -4681,16 +4708,16 @@
         <v>383</v>
       </c>
       <c r="G115" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H115" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I115" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J115" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -4698,10 +4725,10 @@
         <v>45</v>
       </c>
       <c r="B116" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C116" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D116">
         <v>775000</v>
@@ -4710,24 +4737,24 @@
         <v>384</v>
       </c>
       <c r="G116" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H116" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I116" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J116" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="B117" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C117" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F117">
         <v>385</v>
@@ -4735,10 +4762,10 @@
     </row>
     <row r="118" spans="1:10">
       <c r="B118" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C118" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F118">
         <v>386</v>
@@ -4749,10 +4776,10 @@
         <v>46</v>
       </c>
       <c r="B119" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C119" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D119">
         <v>19404000</v>
@@ -4761,16 +4788,16 @@
         <v>387</v>
       </c>
       <c r="G119" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H119" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I119" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J119" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -4778,10 +4805,10 @@
         <v>46</v>
       </c>
       <c r="B120" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C120" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D120">
         <v>53600000</v>
@@ -4790,16 +4817,16 @@
         <v>388</v>
       </c>
       <c r="G120" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H120" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I120" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J120" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -4807,10 +4834,10 @@
         <v>47</v>
       </c>
       <c r="B121" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C121" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D121">
         <v>6300000</v>
@@ -4819,16 +4846,16 @@
         <v>389</v>
       </c>
       <c r="G121" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H121" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I121" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="J121" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -4836,10 +4863,10 @@
         <v>48</v>
       </c>
       <c r="B122" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C122" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D122">
         <v>19039000</v>
@@ -4848,16 +4875,16 @@
         <v>390</v>
       </c>
       <c r="G122" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H122" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I122" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J122" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -4865,10 +4892,10 @@
         <v>48</v>
       </c>
       <c r="B123" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C123" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D123">
         <v>8981700</v>
@@ -4877,16 +4904,16 @@
         <v>391</v>
       </c>
       <c r="G123" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H123" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I123" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J123" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -4894,10 +4921,10 @@
         <v>49</v>
       </c>
       <c r="B124" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C124" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D124">
         <v>265000</v>
@@ -4906,16 +4933,16 @@
         <v>392</v>
       </c>
       <c r="G124" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H124" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I124" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J124" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -4923,10 +4950,10 @@
         <v>49</v>
       </c>
       <c r="B125" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C125" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D125">
         <v>990000</v>
@@ -4935,16 +4962,16 @@
         <v>393</v>
       </c>
       <c r="G125" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H125" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I125" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J125" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -4952,10 +4979,10 @@
         <v>49</v>
       </c>
       <c r="B126" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C126" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E126">
         <v>815</v>
@@ -4969,10 +4996,10 @@
         <v>49</v>
       </c>
       <c r="B127" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D127">
         <v>2160000</v>
@@ -4981,16 +5008,16 @@
         <v>395</v>
       </c>
       <c r="G127" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H127" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I127" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J127" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -4998,10 +5025,10 @@
         <v>50</v>
       </c>
       <c r="B128" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C128" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D128">
         <v>2370000</v>
@@ -5010,16 +5037,16 @@
         <v>396</v>
       </c>
       <c r="G128" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H128" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I128" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J128" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -5027,10 +5054,10 @@
         <v>50</v>
       </c>
       <c r="B129" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C129" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E129">
         <v>4972</v>
@@ -5039,24 +5066,24 @@
         <v>397</v>
       </c>
       <c r="G129" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H129" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I129" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J129" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="130" spans="1:10">
       <c r="B130" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C130" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F130">
         <v>398</v>
@@ -5067,10 +5094,10 @@
         <v>50</v>
       </c>
       <c r="B131" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C131" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D131">
         <v>61779000</v>
@@ -5079,16 +5106,16 @@
         <v>399</v>
       </c>
       <c r="G131" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H131" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I131" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J131" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -5096,10 +5123,10 @@
         <v>50</v>
       </c>
       <c r="B132" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C132" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D132">
         <v>3600000</v>
@@ -5108,16 +5135,16 @@
         <v>400</v>
       </c>
       <c r="G132" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H132" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I132" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J132" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -5125,10 +5152,10 @@
         <v>51</v>
       </c>
       <c r="B133" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C133" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D133">
         <v>2130000</v>
@@ -5137,16 +5164,16 @@
         <v>401</v>
       </c>
       <c r="G133" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H133" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I133" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="J133" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -5154,10 +5181,10 @@
         <v>51</v>
       </c>
       <c r="B134" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C134" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D134">
         <v>996000</v>
@@ -5166,16 +5193,16 @@
         <v>402</v>
       </c>
       <c r="G134" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H134" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I134" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J134" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -5183,10 +5210,10 @@
         <v>51</v>
       </c>
       <c r="B135" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C135" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D135">
         <v>2370000</v>
@@ -5195,16 +5222,16 @@
         <v>403</v>
       </c>
       <c r="G135" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H135" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I135" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J135" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -5212,10 +5239,10 @@
         <v>52</v>
       </c>
       <c r="B136" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C136" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D136">
         <v>10990000</v>
@@ -5224,16 +5251,16 @@
         <v>404</v>
       </c>
       <c r="G136" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H136" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I136" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="J136" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -5241,10 +5268,10 @@
         <v>52</v>
       </c>
       <c r="B137" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C137" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D137">
         <v>8640000</v>
@@ -5253,16 +5280,16 @@
         <v>405</v>
       </c>
       <c r="G137" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H137" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I137" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J137" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -5270,10 +5297,10 @@
         <v>52</v>
       </c>
       <c r="B138" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C138" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D138">
         <v>498000</v>
@@ -5282,16 +5309,16 @@
         <v>406</v>
       </c>
       <c r="G138" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H138" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I138" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="J138" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -5299,10 +5326,10 @@
         <v>52</v>
       </c>
       <c r="B139" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C139" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D139">
         <v>200000</v>
@@ -5311,16 +5338,16 @@
         <v>407</v>
       </c>
       <c r="G139" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H139" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I139" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J139" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -5328,10 +5355,10 @@
         <v>52</v>
       </c>
       <c r="B140" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C140" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D140">
         <v>1080000</v>
@@ -5340,16 +5367,16 @@
         <v>408</v>
       </c>
       <c r="G140" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H140" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I140" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J140" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -5357,10 +5384,10 @@
         <v>52</v>
       </c>
       <c r="B141" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C141" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D141">
         <v>1130000</v>
@@ -5369,16 +5396,16 @@
         <v>409</v>
       </c>
       <c r="G141" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H141" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I141" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="J141" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -5386,10 +5413,10 @@
         <v>53</v>
       </c>
       <c r="B142" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C142" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D142">
         <v>790000</v>
@@ -5398,24 +5425,24 @@
         <v>410</v>
       </c>
       <c r="G142" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H142" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I142" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J142" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="143" spans="1:10">
       <c r="B143" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C143" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F143">
         <v>411</v>
@@ -5426,10 +5453,10 @@
         <v>54</v>
       </c>
       <c r="B144" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C144" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D144">
         <v>1500000</v>
@@ -5438,16 +5465,16 @@
         <v>412</v>
       </c>
       <c r="G144" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H144" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I144" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J144" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -5455,10 +5482,10 @@
         <v>54</v>
       </c>
       <c r="B145" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C145" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D145">
         <v>1440000</v>
@@ -5467,16 +5494,16 @@
         <v>413</v>
       </c>
       <c r="G145" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H145" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I145" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J145" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -5484,10 +5511,10 @@
         <v>55</v>
       </c>
       <c r="B146" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C146" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D146">
         <v>775000</v>
@@ -5496,16 +5523,16 @@
         <v>414</v>
       </c>
       <c r="G146" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H146" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I146" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J146" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -5513,10 +5540,10 @@
         <v>55</v>
       </c>
       <c r="B147" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C147" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D147">
         <v>545000</v>
@@ -5525,24 +5552,24 @@
         <v>415</v>
       </c>
       <c r="G147" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H147" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I147" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J147" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:10">
       <c r="B148" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C148" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F148">
         <v>416</v>
@@ -5553,10 +5580,10 @@
         <v>55</v>
       </c>
       <c r="B149" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C149" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D149">
         <v>56050000</v>
@@ -5565,16 +5592,16 @@
         <v>417</v>
       </c>
       <c r="G149" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H149" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I149" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J149" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -5582,10 +5609,10 @@
         <v>56</v>
       </c>
       <c r="B150" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C150" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D150">
         <v>12000000</v>
@@ -5594,16 +5621,16 @@
         <v>418</v>
       </c>
       <c r="G150" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H150" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I150" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="J150" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -5611,10 +5638,10 @@
         <v>57</v>
       </c>
       <c r="B151" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C151" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D151">
         <v>3160000</v>
@@ -5623,16 +5650,16 @@
         <v>419</v>
       </c>
       <c r="G151" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H151" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I151" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J151" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -5640,10 +5667,10 @@
         <v>57</v>
       </c>
       <c r="B152" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C152" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D152">
         <v>5292000</v>
@@ -5652,16 +5679,16 @@
         <v>420</v>
       </c>
       <c r="G152" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H152" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I152" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J152" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -5669,10 +5696,10 @@
         <v>57</v>
       </c>
       <c r="B153" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C153" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D153">
         <v>50500000</v>
@@ -5681,16 +5708,16 @@
         <v>421</v>
       </c>
       <c r="G153" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H153" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I153" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J153" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -5698,10 +5725,10 @@
         <v>58</v>
       </c>
       <c r="B154" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C154" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D154">
         <v>5000000</v>
@@ -5710,16 +5737,16 @@
         <v>422</v>
       </c>
       <c r="G154" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H154" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I154" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="J154" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -5727,10 +5754,10 @@
         <v>59</v>
       </c>
       <c r="B155" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C155" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D155">
         <v>65300000</v>
@@ -5739,16 +5766,16 @@
         <v>423</v>
       </c>
       <c r="G155" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H155" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I155" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J155" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -5756,10 +5783,10 @@
         <v>59</v>
       </c>
       <c r="B156" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C156" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D156">
         <v>1090000</v>
@@ -5768,16 +5795,16 @@
         <v>424</v>
       </c>
       <c r="G156" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H156" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I156" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J156" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -5785,10 +5812,10 @@
         <v>59</v>
       </c>
       <c r="B157" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C157" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D157">
         <v>1080000</v>
@@ -5797,24 +5824,24 @@
         <v>425</v>
       </c>
       <c r="G157" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H157" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I157" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J157" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="158" spans="1:10">
       <c r="B158" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C158" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F158">
         <v>426</v>
@@ -5825,10 +5852,10 @@
         <v>59</v>
       </c>
       <c r="B159" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C159" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D159">
         <v>5960500</v>
@@ -5837,16 +5864,16 @@
         <v>427</v>
       </c>
       <c r="G159" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H159" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I159" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J159" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -5854,10 +5881,10 @@
         <v>60</v>
       </c>
       <c r="B160" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C160" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D160">
         <v>67290000</v>
@@ -5866,16 +5893,16 @@
         <v>428</v>
       </c>
       <c r="G160" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H160" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="I160" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="J160" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -5883,10 +5910,10 @@
         <v>60</v>
       </c>
       <c r="B161" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C161" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D161">
         <v>4740000</v>
@@ -5895,16 +5922,16 @@
         <v>429</v>
       </c>
       <c r="G161" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H161" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I161" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J161" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -5912,10 +5939,10 @@
         <v>60</v>
       </c>
       <c r="B162" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C162" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D162">
         <v>1090000</v>
@@ -5924,16 +5951,16 @@
         <v>430</v>
       </c>
       <c r="G162" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H162" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I162" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J162" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -5941,10 +5968,10 @@
         <v>60</v>
       </c>
       <c r="B163" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C163" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D163">
         <v>53150000</v>
@@ -5953,16 +5980,16 @@
         <v>431</v>
       </c>
       <c r="G163" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H163" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I163" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J163" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -5970,10 +5997,10 @@
         <v>60</v>
       </c>
       <c r="B164" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C164" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D164">
         <v>220000</v>
@@ -5982,16 +6009,16 @@
         <v>432</v>
       </c>
       <c r="G164" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H164" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I164" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J164" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -5999,10 +6026,10 @@
         <v>60</v>
       </c>
       <c r="B165" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C165" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D165">
         <v>590000</v>
@@ -6011,16 +6038,16 @@
         <v>433</v>
       </c>
       <c r="G165" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H165" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="I165" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="J165" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -6028,10 +6055,10 @@
         <v>61</v>
       </c>
       <c r="B166" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C166" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D166">
         <v>939000</v>
@@ -6040,16 +6067,16 @@
         <v>434</v>
       </c>
       <c r="G166" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H166" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I166" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J166" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -6057,10 +6084,10 @@
         <v>61</v>
       </c>
       <c r="B167" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C167" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D167">
         <v>1970000</v>
@@ -6069,16 +6096,16 @@
         <v>435</v>
       </c>
       <c r="G167" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H167" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I167" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J167" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -6086,10 +6113,10 @@
         <v>61</v>
       </c>
       <c r="B168" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C168" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D168">
         <v>7560000</v>
@@ -6098,16 +6125,16 @@
         <v>436</v>
       </c>
       <c r="G168" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H168" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I168" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J168" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -6115,10 +6142,10 @@
         <v>61</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C169" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D169">
         <v>6590000</v>
@@ -6127,24 +6154,24 @@
         <v>437</v>
       </c>
       <c r="G169" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H169" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="I169" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="J169" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="170" spans="1:10">
       <c r="B170" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C170" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F170">
         <v>438</v>
@@ -6155,10 +6182,10 @@
         <v>62</v>
       </c>
       <c r="B171" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C171" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D171">
         <v>25000000</v>
@@ -6167,18 +6194,18 @@
         <v>439</v>
       </c>
       <c r="G171" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H171" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="172" spans="1:10">
       <c r="B172" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C172" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F172">
         <v>440</v>
@@ -6189,10 +6216,10 @@
         <v>62</v>
       </c>
       <c r="B173" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C173" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D173">
         <v>985000</v>
@@ -6201,24 +6228,24 @@
         <v>441</v>
       </c>
       <c r="G173" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H173" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I173" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J173" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="174" spans="1:10">
       <c r="B174" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C174" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F174">
         <v>442</v>
@@ -6229,10 +6256,10 @@
         <v>63</v>
       </c>
       <c r="B175" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C175" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D175">
         <v>4800000</v>
@@ -6241,16 +6268,16 @@
         <v>443</v>
       </c>
       <c r="G175" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H175" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I175" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J175" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -6258,10 +6285,10 @@
         <v>63</v>
       </c>
       <c r="B176" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176">
         <v>1440000</v>
@@ -6270,16 +6297,16 @@
         <v>444</v>
       </c>
       <c r="G176" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H176" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I176" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J176" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -6287,10 +6314,10 @@
         <v>64</v>
       </c>
       <c r="B177" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C177" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D177">
         <v>990000</v>
@@ -6299,16 +6326,16 @@
         <v>445</v>
       </c>
       <c r="G177" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H177" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I177" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J177" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -6316,10 +6343,10 @@
         <v>64</v>
       </c>
       <c r="B178" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C178" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D178">
         <v>2370000</v>
@@ -6328,16 +6355,16 @@
         <v>446</v>
       </c>
       <c r="G178" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H178" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I178" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J178" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -6345,10 +6372,10 @@
         <v>65</v>
       </c>
       <c r="B179" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C179" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D179">
         <v>2957500</v>
@@ -6357,16 +6384,16 @@
         <v>447</v>
       </c>
       <c r="G179" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H179" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I179" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J179" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -6374,10 +6401,10 @@
         <v>65</v>
       </c>
       <c r="B180" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C180" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D180">
         <v>1960000</v>
@@ -6386,16 +6413,16 @@
         <v>448</v>
       </c>
       <c r="G180" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H180" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I180" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J180" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -6403,10 +6430,10 @@
         <v>65</v>
       </c>
       <c r="B181" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C181" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E181">
         <v>1808</v>
@@ -6415,16 +6442,16 @@
         <v>449</v>
       </c>
       <c r="G181" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H181" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I181" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J181" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -6432,10 +6459,10 @@
         <v>65</v>
       </c>
       <c r="B182" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C182" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D182">
         <v>550000</v>
@@ -6444,16 +6471,16 @@
         <v>450</v>
       </c>
       <c r="G182" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H182" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I182" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J182" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -6461,10 +6488,10 @@
         <v>65</v>
       </c>
       <c r="B183" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C183" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D183">
         <v>6600000</v>
@@ -6473,16 +6500,16 @@
         <v>451</v>
       </c>
       <c r="G183" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H183" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I183" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J183" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -6490,10 +6517,10 @@
         <v>66</v>
       </c>
       <c r="B184" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C184" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D184">
         <v>550000</v>
@@ -6502,16 +6529,16 @@
         <v>452</v>
       </c>
       <c r="G184" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H184" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I184" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J184" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -6519,10 +6546,10 @@
         <v>66</v>
       </c>
       <c r="B185" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C185" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D185">
         <v>220000</v>
@@ -6531,16 +6558,16 @@
         <v>453</v>
       </c>
       <c r="G185" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H185" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I185" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J185" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -6548,10 +6575,10 @@
         <v>66</v>
       </c>
       <c r="B186" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C186" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D186">
         <v>5920000</v>
@@ -6560,16 +6587,16 @@
         <v>454</v>
       </c>
       <c r="G186" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H186" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I186" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J186" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -6577,10 +6604,10 @@
         <v>66</v>
       </c>
       <c r="B187" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C187" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D187">
         <v>540000</v>
@@ -6589,16 +6616,16 @@
         <v>455</v>
       </c>
       <c r="G187" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H187" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I187" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J187" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -6606,10 +6633,10 @@
         <v>66</v>
       </c>
       <c r="B188" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C188" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D188">
         <v>25500000</v>
@@ -6618,10 +6645,10 @@
         <v>456</v>
       </c>
       <c r="G188" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H188" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -6629,10 +6656,10 @@
         <v>67</v>
       </c>
       <c r="B189" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C189" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D189">
         <v>990000</v>
@@ -6641,16 +6668,16 @@
         <v>457</v>
       </c>
       <c r="G189" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H189" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I189" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J189" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -6658,10 +6685,10 @@
         <v>67</v>
       </c>
       <c r="B190" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C190" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D190">
         <v>1650000</v>
@@ -6670,16 +6697,16 @@
         <v>458</v>
       </c>
       <c r="G190" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H190" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I190" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J190" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -6687,10 +6714,10 @@
         <v>67</v>
       </c>
       <c r="B191" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C191" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D191">
         <v>2200000</v>
@@ -6699,16 +6726,16 @@
         <v>459</v>
       </c>
       <c r="G191" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H191" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I191" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J191" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="192" spans="1:10">
@@ -6716,10 +6743,10 @@
         <v>67</v>
       </c>
       <c r="B192" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C192" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D192">
         <v>1580000</v>
@@ -6728,16 +6755,16 @@
         <v>460</v>
       </c>
       <c r="G192" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H192" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I192" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J192" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="193" spans="1:10">
@@ -6745,10 +6772,10 @@
         <v>68</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C193" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D193">
         <v>50500000</v>
@@ -6757,16 +6784,16 @@
         <v>461</v>
       </c>
       <c r="G193" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H193" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="I193" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J193" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -6774,10 +6801,10 @@
         <v>68</v>
       </c>
       <c r="B194" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C194" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D194">
         <v>199000</v>
@@ -6786,16 +6813,16 @@
         <v>462</v>
       </c>
       <c r="G194" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H194" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I194" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="J194" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -6803,10 +6830,10 @@
         <v>68</v>
       </c>
       <c r="B195" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C195" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D195">
         <v>1580000</v>
@@ -6815,16 +6842,16 @@
         <v>463</v>
       </c>
       <c r="G195" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H195" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I195" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J195" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -6832,10 +6859,10 @@
         <v>68</v>
       </c>
       <c r="B196" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C196" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D196">
         <v>419000</v>
@@ -6844,16 +6871,16 @@
         <v>464</v>
       </c>
       <c r="G196" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H196" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I196" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J196" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -6861,10 +6888,10 @@
         <v>68</v>
       </c>
       <c r="B197" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C197" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D197">
         <v>8980000</v>
@@ -6873,16 +6900,16 @@
         <v>465</v>
       </c>
       <c r="G197" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H197" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I197" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="J197" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -6890,10 +6917,10 @@
         <v>68</v>
       </c>
       <c r="B198" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C198" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D198">
         <v>2890000</v>
@@ -6902,16 +6929,16 @@
         <v>466</v>
       </c>
       <c r="G198" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H198" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I198" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="J198" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -6919,10 +6946,10 @@
         <v>68</v>
       </c>
       <c r="B199" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C199" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D199">
         <v>3120000</v>
@@ -6931,16 +6958,16 @@
         <v>467</v>
       </c>
       <c r="G199" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H199" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I199" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J199" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="200" spans="1:10">
@@ -6948,10 +6975,10 @@
         <v>69</v>
       </c>
       <c r="B200" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C200" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D200">
         <v>1590000</v>
@@ -6960,24 +6987,24 @@
         <v>468</v>
       </c>
       <c r="G200" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H200" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I200" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="J200" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="201" spans="1:10">
       <c r="B201" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C201" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F201">
         <v>469</v>
@@ -6988,10 +7015,10 @@
         <v>69</v>
       </c>
       <c r="B202" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C202" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D202">
         <v>14122000</v>
@@ -7000,16 +7027,16 @@
         <v>470</v>
       </c>
       <c r="G202" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H202" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I202" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J202" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -7017,10 +7044,10 @@
         <v>70</v>
       </c>
       <c r="B203" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C203" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E203">
         <v>1400</v>
@@ -7031,10 +7058,10 @@
     </row>
     <row r="204" spans="1:10">
       <c r="B204" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C204" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F204">
         <v>472</v>
@@ -7045,10 +7072,10 @@
         <v>70</v>
       </c>
       <c r="B205" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C205" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D205">
         <v>580000</v>
@@ -7057,16 +7084,16 @@
         <v>473</v>
       </c>
       <c r="G205" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H205" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I205" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="J205" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -7074,10 +7101,10 @@
         <v>70</v>
       </c>
       <c r="B206" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D206">
         <v>2880000</v>
@@ -7086,16 +7113,16 @@
         <v>474</v>
       </c>
       <c r="G206" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H206" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I206" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J206" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -7103,10 +7130,10 @@
         <v>70</v>
       </c>
       <c r="B207" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C207" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D207">
         <v>1130000</v>
@@ -7115,16 +7142,16 @@
         <v>475</v>
       </c>
       <c r="G207" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H207" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I207" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="J207" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -7132,10 +7159,10 @@
         <v>70</v>
       </c>
       <c r="B208" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C208" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D208">
         <v>50500000</v>
@@ -7144,16 +7171,16 @@
         <v>476</v>
       </c>
       <c r="G208" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H208" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I208" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J208" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -7161,10 +7188,10 @@
         <v>71</v>
       </c>
       <c r="B209" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C209" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D209">
         <v>65800000</v>
@@ -7173,16 +7200,16 @@
         <v>477</v>
       </c>
       <c r="G209" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H209" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I209" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J209" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -7190,10 +7217,10 @@
         <v>71</v>
       </c>
       <c r="B210" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C210" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D210">
         <v>1080000</v>
@@ -7202,24 +7229,24 @@
         <v>478</v>
       </c>
       <c r="G210" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H210" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I210" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J210" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="211" spans="1:10">
       <c r="B211" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C211" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F211">
         <v>479</v>
@@ -7230,10 +7257,10 @@
         <v>72</v>
       </c>
       <c r="B212" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C212" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D212">
         <v>1970000</v>
@@ -7242,16 +7269,16 @@
         <v>480</v>
       </c>
       <c r="G212" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H212" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I212" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J212" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="213" spans="1:10">
@@ -7259,10 +7286,10 @@
         <v>72</v>
       </c>
       <c r="B213" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C213" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E213">
         <v>4972</v>
@@ -7271,16 +7298,16 @@
         <v>481</v>
       </c>
       <c r="G213" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H213" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I213" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J213" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -7288,10 +7315,10 @@
         <v>72</v>
       </c>
       <c r="B214" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C214" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D214">
         <v>2934750</v>
@@ -7300,16 +7327,16 @@
         <v>482</v>
       </c>
       <c r="G214" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H214" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I214" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J214" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -7317,10 +7344,10 @@
         <v>72</v>
       </c>
       <c r="B215" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D215">
         <v>395000</v>
@@ -7329,16 +7356,16 @@
         <v>483</v>
       </c>
       <c r="G215" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H215" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I215" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="J215" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -7346,10 +7373,10 @@
         <v>73</v>
       </c>
       <c r="B216" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C216" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D216">
         <v>3960000</v>
@@ -7358,24 +7385,24 @@
         <v>484</v>
       </c>
       <c r="G216" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H216" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I216" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J216" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="217" spans="1:10">
       <c r="B217" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C217" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F217">
         <v>485</v>
@@ -7386,10 +7413,10 @@
         <v>73</v>
       </c>
       <c r="B218" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C218" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E218">
         <v>14955</v>
@@ -7398,10 +7425,10 @@
         <v>486</v>
       </c>
       <c r="G218" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H218" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -7409,10 +7436,10 @@
         <v>74</v>
       </c>
       <c r="B219" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C219" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D219">
         <v>1000000</v>
@@ -7421,24 +7448,24 @@
         <v>487</v>
       </c>
       <c r="G219" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H219" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I219" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J219" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="220" spans="1:10">
       <c r="B220" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C220" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F220">
         <v>488</v>
@@ -7449,10 +7476,10 @@
         <v>74</v>
       </c>
       <c r="B221" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C221" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D221">
         <v>1580000</v>
@@ -7461,16 +7488,16 @@
         <v>489</v>
       </c>
       <c r="G221" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H221" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I221" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J221" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -7478,10 +7505,10 @@
         <v>74</v>
       </c>
       <c r="B222" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C222" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D222">
         <v>1080000</v>
@@ -7490,16 +7517,16 @@
         <v>490</v>
       </c>
       <c r="G222" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H222" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I222" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J222" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -7507,10 +7534,10 @@
         <v>74</v>
       </c>
       <c r="B223" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C223" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D223">
         <v>6480000</v>
@@ -7519,16 +7546,16 @@
         <v>491</v>
       </c>
       <c r="G223" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H223" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I223" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J223" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -7536,10 +7563,10 @@
         <v>74</v>
       </c>
       <c r="B224" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C224" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D224">
         <v>18890000</v>
@@ -7548,16 +7575,16 @@
         <v>492</v>
       </c>
       <c r="G224" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H224" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I224" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="J224" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -7565,10 +7592,10 @@
         <v>75</v>
       </c>
       <c r="B225" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C225" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D225">
         <v>1580000</v>
@@ -7577,16 +7604,16 @@
         <v>493</v>
       </c>
       <c r="G225" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H225" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I225" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J225" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -7594,10 +7621,10 @@
         <v>76</v>
       </c>
       <c r="B226" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C226" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E226">
         <v>1808</v>
@@ -7606,18 +7633,18 @@
         <v>494</v>
       </c>
       <c r="I226" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J226" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="227" spans="1:10">
       <c r="B227" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C227" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F227">
         <v>495</v>
@@ -7628,10 +7655,10 @@
         <v>77</v>
       </c>
       <c r="B228" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C228" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D228">
         <v>710000</v>
@@ -7640,16 +7667,16 @@
         <v>496</v>
       </c>
       <c r="G228" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H228" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I228" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J228" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -7657,10 +7684,10 @@
         <v>77</v>
       </c>
       <c r="B229" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D229">
         <v>3600000</v>
@@ -7669,16 +7696,16 @@
         <v>497</v>
       </c>
       <c r="G229" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H229" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I229" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J229" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -7686,10 +7713,10 @@
         <v>78</v>
       </c>
       <c r="B230" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C230" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D230">
         <v>3300000</v>
@@ -7698,16 +7725,16 @@
         <v>498</v>
       </c>
       <c r="G230" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H230" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I230" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="J230" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="231" spans="1:10">
@@ -7715,10 +7742,10 @@
         <v>78</v>
       </c>
       <c r="B231" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C231" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D231">
         <v>5732000</v>
@@ -7727,16 +7754,16 @@
         <v>499</v>
       </c>
       <c r="G231" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H231" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I231" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J231" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -7744,10 +7771,10 @@
         <v>79</v>
       </c>
       <c r="B232" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C232" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D232">
         <v>2350000</v>
@@ -7756,16 +7783,16 @@
         <v>500</v>
       </c>
       <c r="G232" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H232" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I232" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J232" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -7773,10 +7800,10 @@
         <v>79</v>
       </c>
       <c r="B233" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C233" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D233">
         <v>1130000</v>
@@ -7785,16 +7812,100 @@
         <v>501</v>
       </c>
       <c r="G233" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H233" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="I233" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="J233" t="s">
-        <v>408</v>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10">
+      <c r="A234" t="s">
+        <v>80</v>
+      </c>
+      <c r="B234" t="s">
+        <v>250</v>
+      </c>
+      <c r="C234" t="s">
+        <v>365</v>
+      </c>
+      <c r="D234">
+        <v>6480000</v>
+      </c>
+      <c r="F234">
+        <v>504</v>
+      </c>
+      <c r="G234" t="s">
+        <v>368</v>
+      </c>
+      <c r="H234" t="s">
+        <v>377</v>
+      </c>
+      <c r="I234" t="s">
+        <v>412</v>
+      </c>
+      <c r="J234" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10">
+      <c r="A235" t="s">
+        <v>80</v>
+      </c>
+      <c r="B235" t="s">
+        <v>251</v>
+      </c>
+      <c r="C235" t="s">
+        <v>297</v>
+      </c>
+      <c r="D235">
+        <v>17659300</v>
+      </c>
+      <c r="F235">
+        <v>502</v>
+      </c>
+      <c r="G235" t="s">
+        <v>366</v>
+      </c>
+      <c r="H235" t="s">
+        <v>377</v>
+      </c>
+      <c r="I235" t="s">
+        <v>413</v>
+      </c>
+      <c r="J235" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10">
+      <c r="A236" t="s">
+        <v>81</v>
+      </c>
+      <c r="B236" t="s">
+        <v>82</v>
+      </c>
+      <c r="C236" t="s">
+        <v>252</v>
+      </c>
+      <c r="D236">
+        <v>985000</v>
+      </c>
+      <c r="F236">
+        <v>505</v>
+      </c>
+      <c r="G236" t="s">
+        <v>366</v>
+      </c>
+      <c r="H236" t="s">
+        <v>377</v>
+      </c>
+      <c r="J236" t="s">
+        <v>418</v>
       </c>
     </row>
   </sheetData>

--- a/VENTAS TOTALES 2026.xlsx
+++ b/VENTAS TOTALES 2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="442">
   <si>
     <t>FECHA</t>
   </si>
@@ -46,6 +46,9 @@
     <t>LINEA</t>
   </si>
   <si>
+    <t>RAW_ITEMS</t>
+  </si>
+  <si>
     <t>01-05-2026</t>
   </si>
   <si>
@@ -262,6 +265,9 @@
     <t>07-05-2026</t>
   </si>
   <si>
+    <t>08-05-2026</t>
+  </si>
+  <si>
     <t>1 TINTA CYAN S40600</t>
   </si>
   <si>
@@ -772,6 +778,27 @@
     <t>12 T53K220 CYAN F64/F95, 4 T53K920 HDK F64/F95, 4 T53K420 YELLOW F64/F95</t>
   </si>
   <si>
+    <t>1 T53K220 CYAN F64/F95, 1 T53K920 HDK F64/F95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 IMP EPSON F6470 PROMO MUNDIAL </t>
+  </si>
+  <si>
+    <t>8 T53K320 MAGENTA F64/F95</t>
+  </si>
+  <si>
+    <t>1 T53K320 MAGENTA F64/F95</t>
+  </si>
+  <si>
+    <t>5 T43M320 MAGENTA F100/F110, 1 T43M420 YELLOW F100/F110, 1 T43M120 HDK F100/F110, 1 T43M220 CYAN F100/F110</t>
+  </si>
+  <si>
+    <t>2 T53K220 CYAN F64/F95</t>
+  </si>
+  <si>
+    <t>1 SCG6070SE - G6070 PAGO 50% + HORNO DTF</t>
+  </si>
+  <si>
     <t>WIDMER GRAPHIC</t>
   </si>
   <si>
@@ -1114,6 +1141,12 @@
     <t>Roberto Dutra</t>
   </si>
   <si>
+    <t xml:space="preserve">SIN LIMITES EMPRENDIMIENTO EAS </t>
+  </si>
+  <si>
+    <t>MATIAS FRANCO</t>
+  </si>
+  <si>
     <t>ALBERTO</t>
   </si>
   <si>
@@ -1258,6 +1291,21 @@
     <t>SC-120, SC-121, SC-122</t>
   </si>
   <si>
+    <t>SC-120, SC-121</t>
+  </si>
+  <si>
+    <t>SC-093</t>
+  </si>
+  <si>
+    <t>SC-123</t>
+  </si>
+  <si>
+    <t>SC-131, SC-130, SC-129, SC-128</t>
+  </si>
+  <si>
+    <t>SC-120</t>
+  </si>
+  <si>
     <t>INSUMOS</t>
   </si>
   <si>
@@ -1271,6 +1319,27 @@
   </si>
   <si>
     <t>CORP</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-120", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-121", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-093", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-123", "_CANT_NUM": 8}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-123", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-131", "_CANT_NUM": 5}, {"COD_PRODUCTO": "SC-130", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-129", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-128", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-120", "_CANT_NUM": 2}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-109", "_CANT_NUM": 1}]</t>
   </si>
 </sst>
 </file>
@@ -1628,10 +1697,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J236"/>
+  <dimension ref="A1:K243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1662,16 +1731,19 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D2">
         <v>985000</v>
@@ -1680,27 +1752,27 @@
         <v>268</v>
       </c>
       <c r="G2" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H2" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I2" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D3">
         <v>5292000</v>
@@ -1709,27 +1781,27 @@
         <v>269</v>
       </c>
       <c r="G3" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H3" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D4">
         <v>2180000</v>
@@ -1738,27 +1810,27 @@
         <v>270</v>
       </c>
       <c r="G4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H4" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I4" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E5">
         <v>1808</v>
@@ -1767,27 +1839,27 @@
         <v>271</v>
       </c>
       <c r="G5" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H5" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I5" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J5" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E6">
         <v>6850.19</v>
@@ -1796,18 +1868,18 @@
         <v>272</v>
       </c>
       <c r="G6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D7">
         <v>6051000</v>
@@ -1816,27 +1888,27 @@
         <v>273</v>
       </c>
       <c r="G7" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H7" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I7" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J7" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D8">
         <v>985000</v>
@@ -1845,27 +1917,27 @@
         <v>274</v>
       </c>
       <c r="G8" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H8" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I8" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J8" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D9">
         <v>12348000</v>
@@ -1874,27 +1946,27 @@
         <v>275</v>
       </c>
       <c r="G9" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H9" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I9" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J9" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D10">
         <v>550000</v>
@@ -1903,27 +1975,27 @@
         <v>276</v>
       </c>
       <c r="G10" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H10" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I10" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J10" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D11">
         <v>57590000</v>
@@ -1932,49 +2004,49 @@
         <v>277</v>
       </c>
       <c r="G11" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H11" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="I11" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="J11" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="B12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F12">
         <v>278</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="B13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F13">
         <v>279</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D14">
         <v>9590000</v>
@@ -1983,27 +2055,27 @@
         <v>280</v>
       </c>
       <c r="G14" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H14" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I14" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="J14" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D15">
         <v>7900000</v>
@@ -2012,27 +2084,27 @@
         <v>281</v>
       </c>
       <c r="G15" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H15" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="I15" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="J15" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E16">
         <v>2298</v>
@@ -2041,27 +2113,27 @@
         <v>282</v>
       </c>
       <c r="G16" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H16" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I16" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J16" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D17">
         <v>995000</v>
@@ -2070,27 +2142,27 @@
         <v>283</v>
       </c>
       <c r="G17" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H17" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I17" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J17" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E18">
         <v>1400</v>
@@ -2101,13 +2173,13 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D19">
         <v>3528000</v>
@@ -2116,27 +2188,27 @@
         <v>285</v>
       </c>
       <c r="G19" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H19" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I19" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J19" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D20">
         <v>4320000</v>
@@ -2145,27 +2217,27 @@
         <v>286</v>
       </c>
       <c r="G20" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H20" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I20" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J20" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="D21">
         <v>1990000</v>
@@ -2174,27 +2246,27 @@
         <v>287</v>
       </c>
       <c r="G21" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H21" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I21" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J21" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D22">
         <v>3990000</v>
@@ -2203,27 +2275,27 @@
         <v>288</v>
       </c>
       <c r="G22" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H22" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I22" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="J22" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="D23">
         <v>5190000</v>
@@ -2232,27 +2304,27 @@
         <v>289</v>
       </c>
       <c r="G23" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H23" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I23" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="J23" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D24">
         <v>939000</v>
@@ -2261,27 +2333,27 @@
         <v>290</v>
       </c>
       <c r="G24" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H24" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I24" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J24" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D25">
         <v>1080000</v>
@@ -2290,24 +2362,24 @@
         <v>291</v>
       </c>
       <c r="G25" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="I25" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J25" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D26">
         <v>1500000</v>
@@ -2316,18 +2388,18 @@
         <v>292</v>
       </c>
       <c r="G26" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D27">
         <v>2890000</v>
@@ -2336,27 +2408,27 @@
         <v>293</v>
       </c>
       <c r="G27" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H27" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I27" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="J27" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D28">
         <v>3160000</v>
@@ -2365,27 +2437,27 @@
         <v>294</v>
       </c>
       <c r="G28" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H28" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I28" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J28" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E29">
         <v>1356</v>
@@ -2394,27 +2466,27 @@
         <v>295</v>
       </c>
       <c r="G29" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H29" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I29" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J29" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D30">
         <v>5190000</v>
@@ -2423,27 +2495,27 @@
         <v>296</v>
       </c>
       <c r="G30" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H30" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I30" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="J30" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="D31">
         <v>4590000</v>
@@ -2452,27 +2524,27 @@
         <v>297</v>
       </c>
       <c r="G31" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H31" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I31" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="J31" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D32">
         <v>13850000</v>
@@ -2481,27 +2553,27 @@
         <v>298</v>
       </c>
       <c r="G32" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H32" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I32" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="J32" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D33">
         <v>2370000</v>
@@ -2510,27 +2582,27 @@
         <v>299</v>
       </c>
       <c r="G33" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H33" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I33" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J33" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D34">
         <v>3160000</v>
@@ -2539,27 +2611,27 @@
         <v>301</v>
       </c>
       <c r="G34" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H34" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I34" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J34" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C35" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D35">
         <v>199000</v>
@@ -2568,27 +2640,27 @@
         <v>302</v>
       </c>
       <c r="G35" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H35" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I35" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J35" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D36">
         <v>3290000</v>
@@ -2597,27 +2669,27 @@
         <v>303</v>
       </c>
       <c r="G36" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H36" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I36" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="J36" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="D37">
         <v>12080000</v>
@@ -2626,27 +2698,27 @@
         <v>304</v>
       </c>
       <c r="G37" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H37" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I37" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="J37" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D38">
         <v>2370000</v>
@@ -2655,27 +2727,27 @@
         <v>305</v>
       </c>
       <c r="G38" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H38" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I38" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J38" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D39">
         <v>199000</v>
@@ -2684,27 +2756,27 @@
         <v>306</v>
       </c>
       <c r="G39" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H39" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I39" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J39" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D40">
         <v>2590000</v>
@@ -2713,27 +2785,27 @@
         <v>307</v>
       </c>
       <c r="G40" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H40" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I40" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="J40" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D41">
         <v>6390000</v>
@@ -2742,27 +2814,27 @@
         <v>308</v>
       </c>
       <c r="G41" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H41" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I41" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="J41" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D42">
         <v>6080000</v>
@@ -2771,27 +2843,27 @@
         <v>309</v>
       </c>
       <c r="G42" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H42" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I42" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J42" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D43">
         <v>7190000</v>
@@ -2800,27 +2872,27 @@
         <v>310</v>
       </c>
       <c r="G43" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H43" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I43" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="J43" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F44">
         <v>311</v>
@@ -2828,13 +2900,13 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C45" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D45">
         <v>1090000</v>
@@ -2843,27 +2915,27 @@
         <v>312</v>
       </c>
       <c r="G45" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H45" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I45" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J45" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C46" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="D46">
         <v>1320000</v>
@@ -2872,27 +2944,27 @@
         <v>313</v>
       </c>
       <c r="G46" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H46" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I46" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J46" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D47">
         <v>209000</v>
@@ -2901,27 +2973,27 @@
         <v>314</v>
       </c>
       <c r="G47" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H47" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I47" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J47" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C48" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D48">
         <v>6445000</v>
@@ -2930,27 +3002,27 @@
         <v>315</v>
       </c>
       <c r="G48" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H48" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I48" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="J48" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C49" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E49">
         <v>2712</v>
@@ -2959,27 +3031,27 @@
         <v>316</v>
       </c>
       <c r="G49" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H49" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I49" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J49" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C50" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D50">
         <v>395000</v>
@@ -2988,27 +3060,27 @@
         <v>317</v>
       </c>
       <c r="G50" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H50" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I50" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="J50" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C51" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D51">
         <v>812000</v>
@@ -3017,27 +3089,27 @@
         <v>318</v>
       </c>
       <c r="G51" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H51" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I51" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J51" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C52" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D52">
         <v>50000000</v>
@@ -3046,21 +3118,21 @@
         <v>319</v>
       </c>
       <c r="G52" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H52" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E53">
         <v>22390</v>
@@ -3069,27 +3141,27 @@
         <v>320</v>
       </c>
       <c r="G53" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H53" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I53" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="J53" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C54" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D54">
         <v>405000</v>
@@ -3098,27 +3170,27 @@
         <v>321</v>
       </c>
       <c r="G54" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H54" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I54" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J54" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C55" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D55">
         <v>7512000</v>
@@ -3127,27 +3199,27 @@
         <v>322</v>
       </c>
       <c r="G55" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H55" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I55" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J55" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C56" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E56">
         <v>1356</v>
@@ -3156,27 +3228,27 @@
         <v>323</v>
       </c>
       <c r="G56" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H56" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I56" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J56" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C57" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D57">
         <v>3790000</v>
@@ -3185,27 +3257,27 @@
         <v>324</v>
       </c>
       <c r="G57" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H57" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I57" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="J57" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C58" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D58">
         <v>11790000</v>
@@ -3214,27 +3286,27 @@
         <v>325</v>
       </c>
       <c r="G58" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H58" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I58" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="J58" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C59" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D59">
         <v>498000</v>
@@ -3243,27 +3315,27 @@
         <v>326</v>
       </c>
       <c r="G59" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H59" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I59" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="J59" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C60" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D60">
         <v>3345000</v>
@@ -3272,27 +3344,27 @@
         <v>327</v>
       </c>
       <c r="G60" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H60" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I60" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="J60" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C61" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D61">
         <v>2880000</v>
@@ -3301,27 +3373,27 @@
         <v>328</v>
       </c>
       <c r="G61" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H61" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I61" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J61" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C62" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D62">
         <v>419000</v>
@@ -3330,24 +3402,24 @@
         <v>329</v>
       </c>
       <c r="G62" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H62" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I62" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J62" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="B63" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F63">
         <v>330</v>
@@ -3355,13 +3427,13 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C64" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D64">
         <v>14112000</v>
@@ -3370,27 +3442,27 @@
         <v>331</v>
       </c>
       <c r="G64" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H64" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I64" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J64" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C65" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D65">
         <v>65000</v>
@@ -3399,27 +3471,27 @@
         <v>332</v>
       </c>
       <c r="G65" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H65" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I65" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="J65" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D66">
         <v>498000</v>
@@ -3428,27 +3500,27 @@
         <v>333</v>
       </c>
       <c r="G66" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H66" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I66" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="J66" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C67" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D67">
         <v>1585000</v>
@@ -3457,27 +3529,27 @@
         <v>334</v>
       </c>
       <c r="G67" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H67" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I67" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J67" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D68">
         <v>199000</v>
@@ -3486,24 +3558,24 @@
         <v>335</v>
       </c>
       <c r="G68" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H68" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I68" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J68" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="B69" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F69">
         <v>336</v>
@@ -3511,10 +3583,10 @@
     </row>
     <row r="70" spans="1:10">
       <c r="B70" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F70">
         <v>337</v>
@@ -3522,13 +3594,13 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D71">
         <v>3160000</v>
@@ -3537,27 +3609,27 @@
         <v>338</v>
       </c>
       <c r="G71" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H71" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I71" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J71" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C72" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D72">
         <v>3645000</v>
@@ -3566,27 +3638,27 @@
         <v>339</v>
       </c>
       <c r="G72" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H72" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="I72" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="J72" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D73">
         <v>890000</v>
@@ -3595,24 +3667,24 @@
         <v>340</v>
       </c>
       <c r="G73" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="I73" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J73" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D74">
         <v>3240000</v>
@@ -3621,24 +3693,24 @@
         <v>341</v>
       </c>
       <c r="G74" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="I74" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J74" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C75" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D75">
         <v>1970000</v>
@@ -3647,27 +3719,27 @@
         <v>342</v>
       </c>
       <c r="G75" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H75" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I75" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J75" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C76" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="D76">
         <v>1690000</v>
@@ -3676,27 +3748,27 @@
         <v>343</v>
       </c>
       <c r="G76" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H76" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I76" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="J76" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C77" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D77">
         <v>6690000</v>
@@ -3705,27 +3777,27 @@
         <v>345</v>
       </c>
       <c r="G77" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H77" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I77" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="J77" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C78" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D78">
         <v>405000</v>
@@ -3734,27 +3806,27 @@
         <v>346</v>
       </c>
       <c r="G78" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H78" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I78" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J78" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C79" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D79">
         <v>2370000</v>
@@ -3763,27 +3835,27 @@
         <v>347</v>
       </c>
       <c r="G79" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H79" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I79" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J79" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C80" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E80">
         <v>6257.66</v>
@@ -3792,18 +3864,18 @@
         <v>348</v>
       </c>
       <c r="G80" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C81" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D81">
         <v>1635000</v>
@@ -3812,24 +3884,24 @@
         <v>349</v>
       </c>
       <c r="G81" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H81" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I81" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J81" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="B82" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C82" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F82">
         <v>350</v>
@@ -3837,13 +3909,13 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C83" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D83">
         <v>990000</v>
@@ -3852,27 +3924,27 @@
         <v>351</v>
       </c>
       <c r="G83" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H83" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I83" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J83" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C84" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D84">
         <v>1580000</v>
@@ -3881,27 +3953,27 @@
         <v>352</v>
       </c>
       <c r="G84" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H84" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I84" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J84" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B85" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C85" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D85">
         <v>1970000</v>
@@ -3910,27 +3982,27 @@
         <v>353</v>
       </c>
       <c r="G85" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H85" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I85" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J85" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C86" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D86">
         <v>5190000</v>
@@ -3939,27 +4011,27 @@
         <v>354</v>
       </c>
       <c r="G86" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H86" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I86" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="J86" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B87" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C87" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D87">
         <v>53800000</v>
@@ -3968,24 +4040,24 @@
         <v>355</v>
       </c>
       <c r="G87" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H87" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I87" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J87" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="B88" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C88" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F88">
         <v>356</v>
@@ -3993,13 +4065,13 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B89" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C89" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D89">
         <v>4320000</v>
@@ -4008,27 +4080,27 @@
         <v>357</v>
       </c>
       <c r="G89" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H89" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I89" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J89" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B90" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C90" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D90">
         <v>1580000</v>
@@ -4037,27 +4109,27 @@
         <v>358</v>
       </c>
       <c r="G90" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H90" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I90" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J90" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B91" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C91" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D91">
         <v>11976000</v>
@@ -4066,27 +4138,27 @@
         <v>359</v>
       </c>
       <c r="G91" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H91" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I91" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J91" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B92" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C92" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D92">
         <v>1990000</v>
@@ -4095,27 +4167,27 @@
         <v>360</v>
       </c>
       <c r="G92" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H92" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I92" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J92" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C93" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D93">
         <v>3160000</v>
@@ -4124,27 +4196,27 @@
         <v>361</v>
       </c>
       <c r="G93" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H93" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I93" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J93" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B94" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C94" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E94">
         <v>3616</v>
@@ -4153,27 +4225,27 @@
         <v>362</v>
       </c>
       <c r="G94" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H94" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I94" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J94" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B95" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C95" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D95">
         <v>1980000</v>
@@ -4182,27 +4254,27 @@
         <v>363</v>
       </c>
       <c r="G95" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H95" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I95" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J95" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B96" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D96">
         <v>199000</v>
@@ -4211,27 +4283,27 @@
         <v>364</v>
       </c>
       <c r="G96" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H96" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I96" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J96" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C97" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D97">
         <v>199000</v>
@@ -4240,27 +4312,27 @@
         <v>365</v>
       </c>
       <c r="G97" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H97" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I97" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J97" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C98" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D98">
         <v>2958000</v>
@@ -4269,27 +4341,27 @@
         <v>366</v>
       </c>
       <c r="G98" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H98" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I98" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J98" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C99" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D99">
         <v>1980000</v>
@@ -4298,27 +4370,27 @@
         <v>367</v>
       </c>
       <c r="G99" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H99" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I99" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J99" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C100" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D100">
         <v>790000</v>
@@ -4327,27 +4399,27 @@
         <v>368</v>
       </c>
       <c r="G100" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H100" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I100" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J100" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C101" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D101">
         <v>200000</v>
@@ -4356,24 +4428,24 @@
         <v>369</v>
       </c>
       <c r="G101" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H101" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I101" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J101" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="B102" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C102" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F102">
         <v>370</v>
@@ -4381,13 +4453,13 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C103" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D103">
         <v>790000</v>
@@ -4396,27 +4468,27 @@
         <v>371</v>
       </c>
       <c r="G103" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H103" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I103" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J103" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C104" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D104">
         <v>199000</v>
@@ -4425,27 +4497,27 @@
         <v>372</v>
       </c>
       <c r="G104" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H104" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I104" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J104" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B105" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C105" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D105">
         <v>498000</v>
@@ -4454,27 +4526,27 @@
         <v>373</v>
       </c>
       <c r="G105" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H105" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I105" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="J105" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B106" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C106" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D106">
         <v>7560000</v>
@@ -4483,27 +4555,27 @@
         <v>374</v>
       </c>
       <c r="G106" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H106" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I106" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J106" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B107" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C107" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D107">
         <v>209000</v>
@@ -4512,27 +4584,27 @@
         <v>375</v>
       </c>
       <c r="G107" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H107" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I107" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J107" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B108" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C108" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D108">
         <v>2880000</v>
@@ -4541,27 +4613,27 @@
         <v>376</v>
       </c>
       <c r="G108" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H108" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I108" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J108" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C109" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D109">
         <v>775000</v>
@@ -4570,27 +4642,27 @@
         <v>377</v>
       </c>
       <c r="G109" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H109" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I109" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J109" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C110" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E110">
         <v>3164</v>
@@ -4599,24 +4671,24 @@
         <v>378</v>
       </c>
       <c r="G110" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H110" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I110" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J110" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="B111" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C111" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F111">
         <v>379</v>
@@ -4624,10 +4696,10 @@
     </row>
     <row r="112" spans="1:10">
       <c r="B112" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C112" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F112">
         <v>380</v>
@@ -4635,13 +4707,13 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C113" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D113">
         <v>6390000</v>
@@ -4650,27 +4722,27 @@
         <v>381</v>
       </c>
       <c r="G113" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H113" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I113" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="J113" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B114" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C114" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D114">
         <v>1635000</v>
@@ -4679,27 +4751,27 @@
         <v>382</v>
       </c>
       <c r="G114" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H114" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I114" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J114" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="A115" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B115" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C115" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D115">
         <v>220000</v>
@@ -4708,27 +4780,27 @@
         <v>383</v>
       </c>
       <c r="G115" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H115" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I115" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J115" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B116" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C116" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D116">
         <v>775000</v>
@@ -4737,24 +4809,24 @@
         <v>384</v>
       </c>
       <c r="G116" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H116" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I116" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J116" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="B117" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C117" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F117">
         <v>385</v>
@@ -4762,10 +4834,10 @@
     </row>
     <row r="118" spans="1:10">
       <c r="B118" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C118" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F118">
         <v>386</v>
@@ -4773,13 +4845,13 @@
     </row>
     <row r="119" spans="1:10">
       <c r="A119" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B119" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C119" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D119">
         <v>19404000</v>
@@ -4788,27 +4860,27 @@
         <v>387</v>
       </c>
       <c r="G119" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H119" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I119" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J119" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="120" spans="1:10">
       <c r="A120" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B120" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C120" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="D120">
         <v>53600000</v>
@@ -4817,27 +4889,27 @@
         <v>388</v>
       </c>
       <c r="G120" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H120" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I120" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J120" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="121" spans="1:10">
       <c r="A121" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B121" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C121" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="D121">
         <v>6300000</v>
@@ -4846,27 +4918,27 @@
         <v>389</v>
       </c>
       <c r="G121" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H121" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I121" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="J121" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="A122" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B122" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C122" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D122">
         <v>19039000</v>
@@ -4875,27 +4947,27 @@
         <v>390</v>
       </c>
       <c r="G122" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H122" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I122" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="J122" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B123" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C123" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D123">
         <v>8981700</v>
@@ -4904,27 +4976,27 @@
         <v>391</v>
       </c>
       <c r="G123" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H123" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I123" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J123" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="124" spans="1:10">
       <c r="A124" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B124" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C124" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="D124">
         <v>265000</v>
@@ -4933,27 +5005,27 @@
         <v>392</v>
       </c>
       <c r="G124" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H124" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I124" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="J124" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="A125" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B125" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C125" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="D125">
         <v>990000</v>
@@ -4962,27 +5034,27 @@
         <v>393</v>
       </c>
       <c r="G125" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H125" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I125" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J125" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="126" spans="1:10">
       <c r="A126" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B126" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C126" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E126">
         <v>815</v>
@@ -4993,13 +5065,13 @@
     </row>
     <row r="127" spans="1:10">
       <c r="A127" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B127" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C127" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D127">
         <v>2160000</v>
@@ -5008,27 +5080,27 @@
         <v>395</v>
       </c>
       <c r="G127" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H127" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I127" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J127" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="128" spans="1:10">
       <c r="A128" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B128" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C128" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D128">
         <v>2370000</v>
@@ -5037,27 +5109,27 @@
         <v>396</v>
       </c>
       <c r="G128" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H128" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I128" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J128" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="129" spans="1:10">
       <c r="A129" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B129" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C129" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E129">
         <v>4972</v>
@@ -5066,24 +5138,24 @@
         <v>397</v>
       </c>
       <c r="G129" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H129" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I129" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J129" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="130" spans="1:10">
       <c r="B130" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C130" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F130">
         <v>398</v>
@@ -5091,13 +5163,13 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B131" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C131" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D131">
         <v>61779000</v>
@@ -5106,27 +5178,27 @@
         <v>399</v>
       </c>
       <c r="G131" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H131" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I131" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J131" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="132" spans="1:10">
       <c r="A132" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B132" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C132" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D132">
         <v>3600000</v>
@@ -5135,27 +5207,27 @@
         <v>400</v>
       </c>
       <c r="G132" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H132" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I132" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J132" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="133" spans="1:10">
       <c r="A133" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B133" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C133" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="D133">
         <v>2130000</v>
@@ -5164,27 +5236,27 @@
         <v>401</v>
       </c>
       <c r="G133" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H133" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I133" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="J133" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="134" spans="1:10">
       <c r="A134" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B134" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C134" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D134">
         <v>996000</v>
@@ -5193,27 +5265,27 @@
         <v>402</v>
       </c>
       <c r="G134" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H134" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I134" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="J134" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="135" spans="1:10">
       <c r="A135" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B135" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C135" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D135">
         <v>2370000</v>
@@ -5222,27 +5294,27 @@
         <v>403</v>
       </c>
       <c r="G135" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H135" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I135" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J135" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="136" spans="1:10">
       <c r="A136" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B136" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C136" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="D136">
         <v>10990000</v>
@@ -5251,27 +5323,27 @@
         <v>404</v>
       </c>
       <c r="G136" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H136" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I136" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="J136" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="137" spans="1:10">
       <c r="A137" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B137" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D137">
         <v>8640000</v>
@@ -5280,27 +5352,27 @@
         <v>405</v>
       </c>
       <c r="G137" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H137" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I137" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J137" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="138" spans="1:10">
       <c r="A138" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C138" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D138">
         <v>498000</v>
@@ -5309,27 +5381,27 @@
         <v>406</v>
       </c>
       <c r="G138" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H138" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I138" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="J138" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="139" spans="1:10">
       <c r="A139" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B139" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C139" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D139">
         <v>200000</v>
@@ -5338,27 +5410,27 @@
         <v>407</v>
       </c>
       <c r="G139" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H139" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I139" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J139" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="140" spans="1:10">
       <c r="A140" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B140" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C140" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D140">
         <v>1080000</v>
@@ -5367,27 +5439,27 @@
         <v>408</v>
       </c>
       <c r="G140" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H140" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I140" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J140" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="141" spans="1:10">
       <c r="A141" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B141" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C141" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D141">
         <v>1130000</v>
@@ -5396,27 +5468,27 @@
         <v>409</v>
       </c>
       <c r="G141" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H141" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I141" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="J141" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="142" spans="1:10">
       <c r="A142" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B142" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C142" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D142">
         <v>790000</v>
@@ -5425,24 +5497,24 @@
         <v>410</v>
       </c>
       <c r="G142" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H142" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I142" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J142" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="143" spans="1:10">
       <c r="B143" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C143" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F143">
         <v>411</v>
@@ -5450,13 +5522,13 @@
     </row>
     <row r="144" spans="1:10">
       <c r="A144" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B144" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C144" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="D144">
         <v>1500000</v>
@@ -5465,27 +5537,27 @@
         <v>412</v>
       </c>
       <c r="G144" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H144" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I144" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J144" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="145" spans="1:10">
       <c r="A145" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B145" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C145" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D145">
         <v>1440000</v>
@@ -5494,27 +5566,27 @@
         <v>413</v>
       </c>
       <c r="G145" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H145" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I145" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J145" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="146" spans="1:10">
       <c r="A146" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B146" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C146" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="D146">
         <v>775000</v>
@@ -5523,27 +5595,27 @@
         <v>414</v>
       </c>
       <c r="G146" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H146" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I146" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J146" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="147" spans="1:10">
       <c r="A147" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B147" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C147" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D147">
         <v>545000</v>
@@ -5552,24 +5624,24 @@
         <v>415</v>
       </c>
       <c r="G147" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H147" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I147" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J147" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="148" spans="1:10">
       <c r="B148" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C148" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F148">
         <v>416</v>
@@ -5577,13 +5649,13 @@
     </row>
     <row r="149" spans="1:10">
       <c r="A149" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B149" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C149" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="D149">
         <v>56050000</v>
@@ -5592,27 +5664,27 @@
         <v>417</v>
       </c>
       <c r="G149" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H149" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I149" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J149" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="150" spans="1:10">
       <c r="A150" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B150" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C150" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D150">
         <v>12000000</v>
@@ -5621,27 +5693,27 @@
         <v>418</v>
       </c>
       <c r="G150" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H150" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I150" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="J150" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="151" spans="1:10">
       <c r="A151" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B151" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C151" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D151">
         <v>3160000</v>
@@ -5650,27 +5722,27 @@
         <v>419</v>
       </c>
       <c r="G151" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H151" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I151" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J151" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="152" spans="1:10">
       <c r="A152" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B152" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C152" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D152">
         <v>5292000</v>
@@ -5679,27 +5751,27 @@
         <v>420</v>
       </c>
       <c r="G152" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H152" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I152" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J152" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="153" spans="1:10">
       <c r="A153" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B153" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C153" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D153">
         <v>50500000</v>
@@ -5708,27 +5780,27 @@
         <v>421</v>
       </c>
       <c r="G153" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H153" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I153" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J153" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="154" spans="1:10">
       <c r="A154" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B154" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C154" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="D154">
         <v>5000000</v>
@@ -5737,27 +5809,27 @@
         <v>422</v>
       </c>
       <c r="G154" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H154" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="I154" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="J154" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="155" spans="1:10">
       <c r="A155" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B155" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C155" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D155">
         <v>65300000</v>
@@ -5766,27 +5838,27 @@
         <v>423</v>
       </c>
       <c r="G155" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H155" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I155" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J155" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="156" spans="1:10">
       <c r="A156" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B156" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C156" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D156">
         <v>1090000</v>
@@ -5795,27 +5867,27 @@
         <v>424</v>
       </c>
       <c r="G156" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H156" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I156" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J156" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="157" spans="1:10">
       <c r="A157" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B157" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C157" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D157">
         <v>1080000</v>
@@ -5824,24 +5896,24 @@
         <v>425</v>
       </c>
       <c r="G157" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H157" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I157" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J157" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="158" spans="1:10">
       <c r="B158" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C158" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F158">
         <v>426</v>
@@ -5849,13 +5921,13 @@
     </row>
     <row r="159" spans="1:10">
       <c r="A159" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B159" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C159" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D159">
         <v>5960500</v>
@@ -5864,27 +5936,27 @@
         <v>427</v>
       </c>
       <c r="G159" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H159" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I159" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J159" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="160" spans="1:10">
       <c r="A160" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B160" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C160" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="D160">
         <v>67290000</v>
@@ -5893,27 +5965,27 @@
         <v>428</v>
       </c>
       <c r="G160" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H160" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I160" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="J160" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="161" spans="1:10">
       <c r="A161" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B161" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C161" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="D161">
         <v>4740000</v>
@@ -5922,27 +5994,27 @@
         <v>429</v>
       </c>
       <c r="G161" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H161" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I161" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J161" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:10">
       <c r="A162" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B162" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C162" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D162">
         <v>1090000</v>
@@ -5951,27 +6023,27 @@
         <v>430</v>
       </c>
       <c r="G162" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H162" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I162" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J162" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="1:10">
       <c r="A163" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B163" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C163" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="D163">
         <v>53150000</v>
@@ -5980,27 +6052,27 @@
         <v>431</v>
       </c>
       <c r="G163" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H163" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="I163" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J163" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:10">
       <c r="A164" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B164" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C164" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D164">
         <v>220000</v>
@@ -6009,27 +6081,27 @@
         <v>432</v>
       </c>
       <c r="G164" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H164" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I164" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J164" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:10">
       <c r="A165" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B165" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C165" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D165">
         <v>590000</v>
@@ -6038,27 +6110,27 @@
         <v>433</v>
       </c>
       <c r="G165" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H165" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="I165" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="J165" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="1:10">
       <c r="A166" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B166" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C166" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D166">
         <v>939000</v>
@@ -6067,27 +6139,27 @@
         <v>434</v>
       </c>
       <c r="G166" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H166" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I166" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J166" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:10">
       <c r="A167" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B167" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C167" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D167">
         <v>1970000</v>
@@ -6096,27 +6168,27 @@
         <v>435</v>
       </c>
       <c r="G167" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H167" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I167" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J167" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:10">
       <c r="A168" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B168" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C168" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D168">
         <v>7560000</v>
@@ -6125,27 +6197,27 @@
         <v>436</v>
       </c>
       <c r="G168" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H168" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="I168" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J168" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="169" spans="1:10">
       <c r="A169" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B169" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C169" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="D169">
         <v>6590000</v>
@@ -6154,24 +6226,24 @@
         <v>437</v>
       </c>
       <c r="G169" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H169" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="I169" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="J169" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="170" spans="1:10">
       <c r="B170" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C170" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F170">
         <v>438</v>
@@ -6179,13 +6251,13 @@
     </row>
     <row r="171" spans="1:10">
       <c r="A171" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B171" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C171" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D171">
         <v>25000000</v>
@@ -6194,18 +6266,18 @@
         <v>439</v>
       </c>
       <c r="G171" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H171" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
     </row>
     <row r="172" spans="1:10">
       <c r="B172" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F172">
         <v>440</v>
@@ -6213,13 +6285,13 @@
     </row>
     <row r="173" spans="1:10">
       <c r="A173" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B173" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C173" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D173">
         <v>985000</v>
@@ -6228,24 +6300,24 @@
         <v>441</v>
       </c>
       <c r="G173" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H173" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I173" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J173" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="174" spans="1:10">
       <c r="B174" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C174" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F174">
         <v>442</v>
@@ -6253,13 +6325,13 @@
     </row>
     <row r="175" spans="1:10">
       <c r="A175" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C175" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D175">
         <v>4800000</v>
@@ -6268,27 +6340,27 @@
         <v>443</v>
       </c>
       <c r="G175" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H175" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I175" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J175" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="176" spans="1:10">
       <c r="A176" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B176" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C176" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D176">
         <v>1440000</v>
@@ -6297,27 +6369,27 @@
         <v>444</v>
       </c>
       <c r="G176" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H176" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I176" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J176" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="177" spans="1:10">
       <c r="A177" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B177" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C177" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="D177">
         <v>990000</v>
@@ -6326,27 +6398,27 @@
         <v>445</v>
       </c>
       <c r="G177" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H177" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I177" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J177" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="178" spans="1:10">
       <c r="A178" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B178" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C178" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D178">
         <v>2370000</v>
@@ -6355,27 +6427,27 @@
         <v>446</v>
       </c>
       <c r="G178" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H178" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I178" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J178" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="179" spans="1:10">
       <c r="A179" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B179" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C179" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D179">
         <v>2957500</v>
@@ -6384,27 +6456,27 @@
         <v>447</v>
       </c>
       <c r="G179" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H179" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I179" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J179" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:10">
       <c r="A180" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B180" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C180" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D180">
         <v>1960000</v>
@@ -6413,27 +6485,27 @@
         <v>448</v>
       </c>
       <c r="G180" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H180" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I180" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J180" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="181" spans="1:10">
       <c r="A181" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B181" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C181" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E181">
         <v>1808</v>
@@ -6442,27 +6514,27 @@
         <v>449</v>
       </c>
       <c r="G181" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H181" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I181" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J181" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="182" spans="1:10">
       <c r="A182" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B182" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C182" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="D182">
         <v>550000</v>
@@ -6471,27 +6543,27 @@
         <v>450</v>
       </c>
       <c r="G182" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H182" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I182" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J182" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="183" spans="1:10">
       <c r="A183" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B183" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C183" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D183">
         <v>6600000</v>
@@ -6500,27 +6572,27 @@
         <v>451</v>
       </c>
       <c r="G183" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H183" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I183" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J183" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:10">
       <c r="A184" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B184" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C184" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="D184">
         <v>550000</v>
@@ -6529,27 +6601,27 @@
         <v>452</v>
       </c>
       <c r="G184" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H184" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I184" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J184" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="185" spans="1:10">
       <c r="A185" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B185" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C185" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D185">
         <v>220000</v>
@@ -6558,27 +6630,27 @@
         <v>453</v>
       </c>
       <c r="G185" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H185" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I185" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J185" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="186" spans="1:10">
       <c r="A186" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B186" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C186" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D186">
         <v>5920000</v>
@@ -6587,27 +6659,27 @@
         <v>454</v>
       </c>
       <c r="G186" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H186" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I186" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J186" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:10">
       <c r="A187" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B187" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C187" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D187">
         <v>540000</v>
@@ -6616,27 +6688,27 @@
         <v>455</v>
       </c>
       <c r="G187" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H187" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I187" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J187" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:10">
       <c r="A188" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B188" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C188" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D188">
         <v>25500000</v>
@@ -6645,21 +6717,21 @@
         <v>456</v>
       </c>
       <c r="G188" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H188" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="189" spans="1:10">
       <c r="A189" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B189" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="D189">
         <v>990000</v>
@@ -6668,27 +6740,27 @@
         <v>457</v>
       </c>
       <c r="G189" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H189" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I189" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J189" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="190" spans="1:10">
       <c r="A190" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B190" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C190" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="D190">
         <v>1650000</v>
@@ -6697,27 +6769,27 @@
         <v>458</v>
       </c>
       <c r="G190" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H190" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I190" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J190" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191" spans="1:10">
       <c r="A191" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B191" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C191" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="D191">
         <v>2200000</v>
@@ -6726,27 +6798,27 @@
         <v>459</v>
       </c>
       <c r="G191" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H191" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I191" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J191" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:10">
       <c r="A192" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B192" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C192" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D192">
         <v>1580000</v>
@@ -6755,27 +6827,27 @@
         <v>460</v>
       </c>
       <c r="G192" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H192" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I192" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J192" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="193" spans="1:10">
       <c r="A193" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B193" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C193" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D193">
         <v>50500000</v>
@@ -6784,27 +6856,27 @@
         <v>461</v>
       </c>
       <c r="G193" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H193" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I193" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J193" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="194" spans="1:10">
       <c r="A194" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B194" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C194" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D194">
         <v>199000</v>
@@ -6813,27 +6885,27 @@
         <v>462</v>
       </c>
       <c r="G194" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H194" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I194" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J194" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="195" spans="1:10">
       <c r="A195" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B195" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C195" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D195">
         <v>1580000</v>
@@ -6842,27 +6914,27 @@
         <v>463</v>
       </c>
       <c r="G195" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H195" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I195" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J195" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="196" spans="1:10">
       <c r="A196" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B196" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C196" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D196">
         <v>419000</v>
@@ -6871,27 +6943,27 @@
         <v>464</v>
       </c>
       <c r="G196" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H196" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I196" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J196" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="197" spans="1:10">
       <c r="A197" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B197" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C197" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="D197">
         <v>8980000</v>
@@ -6900,27 +6972,27 @@
         <v>465</v>
       </c>
       <c r="G197" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H197" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I197" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="J197" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="198" spans="1:10">
       <c r="A198" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B198" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C198" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D198">
         <v>2890000</v>
@@ -6929,27 +7001,27 @@
         <v>466</v>
       </c>
       <c r="G198" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H198" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I198" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="J198" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="199" spans="1:10">
       <c r="A199" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B199" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C199" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D199">
         <v>3120000</v>
@@ -6958,27 +7030,27 @@
         <v>467</v>
       </c>
       <c r="G199" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H199" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I199" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J199" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="200" spans="1:10">
       <c r="A200" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B200" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C200" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="D200">
         <v>1590000</v>
@@ -6987,24 +7059,24 @@
         <v>468</v>
       </c>
       <c r="G200" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H200" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I200" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="J200" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="201" spans="1:10">
       <c r="B201" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F201">
         <v>469</v>
@@ -7012,13 +7084,13 @@
     </row>
     <row r="202" spans="1:10">
       <c r="A202" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B202" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C202" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D202">
         <v>14122000</v>
@@ -7027,27 +7099,27 @@
         <v>470</v>
       </c>
       <c r="G202" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H202" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="I202" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J202" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="203" spans="1:10">
       <c r="A203" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B203" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C203" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="E203">
         <v>1400</v>
@@ -7058,10 +7130,10 @@
     </row>
     <row r="204" spans="1:10">
       <c r="B204" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C204" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F204">
         <v>472</v>
@@ -7069,13 +7141,13 @@
     </row>
     <row r="205" spans="1:10">
       <c r="A205" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B205" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C205" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="D205">
         <v>580000</v>
@@ -7084,27 +7156,27 @@
         <v>473</v>
       </c>
       <c r="G205" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H205" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I205" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="J205" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="206" spans="1:10">
       <c r="A206" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B206" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C206" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D206">
         <v>2880000</v>
@@ -7113,27 +7185,27 @@
         <v>474</v>
       </c>
       <c r="G206" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H206" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I206" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J206" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="207" spans="1:10">
       <c r="A207" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B207" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C207" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D207">
         <v>1130000</v>
@@ -7142,27 +7214,27 @@
         <v>475</v>
       </c>
       <c r="G207" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H207" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I207" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="J207" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="208" spans="1:10">
       <c r="A208" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B208" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C208" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="D208">
         <v>50500000</v>
@@ -7171,27 +7243,27 @@
         <v>476</v>
       </c>
       <c r="G208" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H208" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I208" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J208" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="209" spans="1:10">
       <c r="A209" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B209" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C209" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="D209">
         <v>65800000</v>
@@ -7200,27 +7272,27 @@
         <v>477</v>
       </c>
       <c r="G209" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H209" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I209" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="J209" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
     </row>
     <row r="210" spans="1:10">
       <c r="A210" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B210" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C210" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D210">
         <v>1080000</v>
@@ -7229,24 +7301,24 @@
         <v>478</v>
       </c>
       <c r="G210" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H210" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I210" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J210" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="211" spans="1:10">
       <c r="B211" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C211" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F211">
         <v>479</v>
@@ -7254,13 +7326,13 @@
     </row>
     <row r="212" spans="1:10">
       <c r="A212" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B212" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C212" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D212">
         <v>1970000</v>
@@ -7269,27 +7341,27 @@
         <v>480</v>
       </c>
       <c r="G212" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H212" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I212" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J212" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="213" spans="1:10">
       <c r="A213" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B213" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C213" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E213">
         <v>4972</v>
@@ -7298,27 +7370,27 @@
         <v>481</v>
       </c>
       <c r="G213" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H213" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I213" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J213" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="214" spans="1:10">
       <c r="A214" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C214" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D214">
         <v>2934750</v>
@@ -7327,27 +7399,27 @@
         <v>482</v>
       </c>
       <c r="G214" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H214" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I214" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J214" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="215" spans="1:10">
       <c r="A215" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B215" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C215" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D215">
         <v>395000</v>
@@ -7356,27 +7428,27 @@
         <v>483</v>
       </c>
       <c r="G215" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H215" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I215" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="J215" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="216" spans="1:10">
       <c r="A216" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B216" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C216" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D216">
         <v>3960000</v>
@@ -7385,24 +7457,24 @@
         <v>484</v>
       </c>
       <c r="G216" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H216" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I216" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J216" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="217" spans="1:10">
       <c r="B217" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C217" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F217">
         <v>485</v>
@@ -7410,13 +7482,13 @@
     </row>
     <row r="218" spans="1:10">
       <c r="A218" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B218" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="E218">
         <v>14955</v>
@@ -7425,21 +7497,21 @@
         <v>486</v>
       </c>
       <c r="G218" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H218" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="219" spans="1:10">
       <c r="A219" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B219" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C219" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D219">
         <v>1000000</v>
@@ -7448,24 +7520,24 @@
         <v>487</v>
       </c>
       <c r="G219" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H219" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I219" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J219" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="220" spans="1:10">
       <c r="B220" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C220" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F220">
         <v>488</v>
@@ -7473,13 +7545,13 @@
     </row>
     <row r="221" spans="1:10">
       <c r="A221" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B221" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C221" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D221">
         <v>1580000</v>
@@ -7488,27 +7560,27 @@
         <v>489</v>
       </c>
       <c r="G221" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H221" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I221" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J221" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="222" spans="1:10">
       <c r="A222" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B222" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C222" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D222">
         <v>1080000</v>
@@ -7517,27 +7589,27 @@
         <v>490</v>
       </c>
       <c r="G222" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H222" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I222" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J222" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="223" spans="1:10">
       <c r="A223" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B223" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C223" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D223">
         <v>6480000</v>
@@ -7546,27 +7618,27 @@
         <v>491</v>
       </c>
       <c r="G223" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H223" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="I223" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J223" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
     </row>
     <row r="224" spans="1:10">
       <c r="A224" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B224" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C224" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D224">
         <v>18890000</v>
@@ -7575,27 +7647,27 @@
         <v>492</v>
       </c>
       <c r="G224" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H224" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I224" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="J224" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11">
       <c r="A225" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B225" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C225" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D225">
         <v>1580000</v>
@@ -7604,27 +7676,27 @@
         <v>493</v>
       </c>
       <c r="G225" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H225" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I225" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J225" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11">
       <c r="A226" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B226" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C226" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E226">
         <v>1808</v>
@@ -7633,32 +7705,32 @@
         <v>494</v>
       </c>
       <c r="I226" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J226" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11">
       <c r="B227" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C227" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F227">
         <v>495</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" spans="1:11">
       <c r="A228" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B228" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C228" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D228">
         <v>710000</v>
@@ -7667,27 +7739,27 @@
         <v>496</v>
       </c>
       <c r="G228" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H228" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I228" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J228" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11">
       <c r="A229" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B229" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C229" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D229">
         <v>3600000</v>
@@ -7696,27 +7768,27 @@
         <v>497</v>
       </c>
       <c r="G229" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H229" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I229" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J229" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11">
       <c r="A230" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B230" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C230" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="D230">
         <v>3300000</v>
@@ -7725,27 +7797,27 @@
         <v>498</v>
       </c>
       <c r="G230" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H230" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I230" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J230" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11">
       <c r="A231" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B231" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C231" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D231">
         <v>5732000</v>
@@ -7754,27 +7826,27 @@
         <v>499</v>
       </c>
       <c r="G231" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H231" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I231" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J231" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11">
       <c r="A232" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B232" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C232" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D232">
         <v>2350000</v>
@@ -7783,27 +7855,27 @@
         <v>500</v>
       </c>
       <c r="G232" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H232" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I232" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="J232" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11">
       <c r="A233" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B233" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C233" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D233">
         <v>1130000</v>
@@ -7812,27 +7884,27 @@
         <v>501</v>
       </c>
       <c r="G233" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H233" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="I233" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="J233" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11">
       <c r="A234" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B234" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C234" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="D234">
         <v>6480000</v>
@@ -7841,27 +7913,27 @@
         <v>504</v>
       </c>
       <c r="G234" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H234" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="I234" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="J234" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11">
       <c r="A235" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B235" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C235" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D235">
         <v>17659300</v>
@@ -7870,27 +7942,27 @@
         <v>502</v>
       </c>
       <c r="G235" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H235" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="I235" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="J235" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11">
       <c r="A236" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B236" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C236" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D236">
         <v>985000</v>
@@ -7899,13 +7971,237 @@
         <v>505</v>
       </c>
       <c r="G236" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H236" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="J236" t="s">
-        <v>418</v>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11">
+      <c r="A237" t="s">
+        <v>82</v>
+      </c>
+      <c r="B237" t="s">
+        <v>254</v>
+      </c>
+      <c r="C237" t="s">
+        <v>314</v>
+      </c>
+      <c r="D237">
+        <v>1580000</v>
+      </c>
+      <c r="F237">
+        <v>506</v>
+      </c>
+      <c r="G237" t="s">
+        <v>377</v>
+      </c>
+      <c r="H237" t="s">
+        <v>388</v>
+      </c>
+      <c r="I237" t="s">
+        <v>425</v>
+      </c>
+      <c r="J237" t="s">
+        <v>434</v>
+      </c>
+      <c r="K237" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11">
+      <c r="A238" t="s">
+        <v>82</v>
+      </c>
+      <c r="B238" t="s">
+        <v>255</v>
+      </c>
+      <c r="C238" t="s">
+        <v>375</v>
+      </c>
+      <c r="D238">
+        <v>50500000</v>
+      </c>
+      <c r="F238">
+        <v>503</v>
+      </c>
+      <c r="G238" t="s">
+        <v>379</v>
+      </c>
+      <c r="H238" t="s">
+        <v>388</v>
+      </c>
+      <c r="I238" t="s">
+        <v>426</v>
+      </c>
+      <c r="J238" t="s">
+        <v>434</v>
+      </c>
+      <c r="K238" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11">
+      <c r="A239" t="s">
+        <v>83</v>
+      </c>
+      <c r="B239" t="s">
+        <v>256</v>
+      </c>
+      <c r="C239" t="s">
+        <v>262</v>
+      </c>
+      <c r="D239">
+        <v>7063720</v>
+      </c>
+      <c r="F239">
+        <v>507</v>
+      </c>
+      <c r="G239" t="s">
+        <v>377</v>
+      </c>
+      <c r="H239" t="s">
+        <v>388</v>
+      </c>
+      <c r="I239" t="s">
+        <v>427</v>
+      </c>
+      <c r="J239" t="s">
+        <v>434</v>
+      </c>
+      <c r="K239" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11">
+      <c r="A240" t="s">
+        <v>83</v>
+      </c>
+      <c r="B240" t="s">
+        <v>257</v>
+      </c>
+      <c r="C240" t="s">
+        <v>273</v>
+      </c>
+      <c r="D240">
+        <v>990000</v>
+      </c>
+      <c r="F240">
+        <v>508</v>
+      </c>
+      <c r="G240" t="s">
+        <v>379</v>
+      </c>
+      <c r="H240" t="s">
+        <v>388</v>
+      </c>
+      <c r="I240" t="s">
+        <v>427</v>
+      </c>
+      <c r="J240" t="s">
+        <v>434</v>
+      </c>
+      <c r="K240" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11">
+      <c r="A241" t="s">
+        <v>83</v>
+      </c>
+      <c r="B241" t="s">
+        <v>258</v>
+      </c>
+      <c r="C241" t="s">
+        <v>264</v>
+      </c>
+      <c r="E241">
+        <v>3616</v>
+      </c>
+      <c r="F241">
+        <v>510</v>
+      </c>
+      <c r="G241" t="s">
+        <v>377</v>
+      </c>
+      <c r="H241" t="s">
+        <v>388</v>
+      </c>
+      <c r="I241" t="s">
+        <v>428</v>
+      </c>
+      <c r="J241" t="s">
+        <v>434</v>
+      </c>
+      <c r="K241" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11">
+      <c r="A242" t="s">
+        <v>83</v>
+      </c>
+      <c r="B242" t="s">
+        <v>259</v>
+      </c>
+      <c r="C242" t="s">
+        <v>288</v>
+      </c>
+      <c r="D242">
+        <v>1580000</v>
+      </c>
+      <c r="F242">
+        <v>511</v>
+      </c>
+      <c r="G242" t="s">
+        <v>379</v>
+      </c>
+      <c r="H242" t="s">
+        <v>388</v>
+      </c>
+      <c r="I242" t="s">
+        <v>429</v>
+      </c>
+      <c r="J242" t="s">
+        <v>434</v>
+      </c>
+      <c r="K242" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11">
+      <c r="A243" t="s">
+        <v>83</v>
+      </c>
+      <c r="B243" t="s">
+        <v>260</v>
+      </c>
+      <c r="C243" t="s">
+        <v>376</v>
+      </c>
+      <c r="E243">
+        <v>7625</v>
+      </c>
+      <c r="F243">
+        <v>512</v>
+      </c>
+      <c r="G243" t="s">
+        <v>377</v>
+      </c>
+      <c r="H243" t="s">
+        <v>388</v>
+      </c>
+      <c r="I243" t="s">
+        <v>416</v>
+      </c>
+      <c r="J243" t="s">
+        <v>434</v>
+      </c>
+      <c r="K243" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>

--- a/VENTAS TOTALES 2026.xlsx
+++ b/VENTAS TOTALES 2026.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Ventas" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="369">
   <si>
     <t>FECHA</t>
   </si>
@@ -47,225 +47,6 @@
   </si>
   <si>
     <t>RAW_ITEMS</t>
-  </si>
-  <si>
-    <t>01-05-2026</t>
-  </si>
-  <si>
-    <t>01-06-2026</t>
-  </si>
-  <si>
-    <t>01-08-2026</t>
-  </si>
-  <si>
-    <t>01-09-2026</t>
-  </si>
-  <si>
-    <t>13-01-2026</t>
-  </si>
-  <si>
-    <t>01-12-2026</t>
-  </si>
-  <si>
-    <t>15-01-2026</t>
-  </si>
-  <si>
-    <t>16-01-2026</t>
-  </si>
-  <si>
-    <t>19-01-2026</t>
-  </si>
-  <si>
-    <t>20-01-2026</t>
-  </si>
-  <si>
-    <t>21-01-2026</t>
-  </si>
-  <si>
-    <t>22-01-2026</t>
-  </si>
-  <si>
-    <t>27-01-2026</t>
-  </si>
-  <si>
-    <t>28-01-2026</t>
-  </si>
-  <si>
-    <t>29-01-2026</t>
-  </si>
-  <si>
-    <t>30-01-2026</t>
-  </si>
-  <si>
-    <t>25-01-2026</t>
-  </si>
-  <si>
-    <t>02-02-2026</t>
-  </si>
-  <si>
-    <t>02-03-2026</t>
-  </si>
-  <si>
-    <t>02-05-2026</t>
-  </si>
-  <si>
-    <t>02-06-2026</t>
-  </si>
-  <si>
-    <t>02-09-2026</t>
-  </si>
-  <si>
-    <t>02-10-2026</t>
-  </si>
-  <si>
-    <t>02-11-2026</t>
-  </si>
-  <si>
-    <t>02-12-2026</t>
-  </si>
-  <si>
-    <t>13-02-2026</t>
-  </si>
-  <si>
-    <t>16-02-2026</t>
-  </si>
-  <si>
-    <t>17-02-2026</t>
-  </si>
-  <si>
-    <t>18-02-2026</t>
-  </si>
-  <si>
-    <t>19-02-2026</t>
-  </si>
-  <si>
-    <t>20-02-2026</t>
-  </si>
-  <si>
-    <t>23-02-2026</t>
-  </si>
-  <si>
-    <t>24-02-2026</t>
-  </si>
-  <si>
-    <t>25-02-2026</t>
-  </si>
-  <si>
-    <t>26-02-2026</t>
-  </si>
-  <si>
-    <t>27-02-2026</t>
-  </si>
-  <si>
-    <t>03-04-2026</t>
-  </si>
-  <si>
-    <t>03-05-2026</t>
-  </si>
-  <si>
-    <t>03-06-2026</t>
-  </si>
-  <si>
-    <t>03-09-2026</t>
-  </si>
-  <si>
-    <t>03-12-2026</t>
-  </si>
-  <si>
-    <t>13-03-2026</t>
-  </si>
-  <si>
-    <t>16-03-2026</t>
-  </si>
-  <si>
-    <t>17-03-2026</t>
-  </si>
-  <si>
-    <t>18-03-2026</t>
-  </si>
-  <si>
-    <t>19-03-2026</t>
-  </si>
-  <si>
-    <t>20-03-2026</t>
-  </si>
-  <si>
-    <t>23-03-2026</t>
-  </si>
-  <si>
-    <t>24-03-2026</t>
-  </si>
-  <si>
-    <t>25-03-2026</t>
-  </si>
-  <si>
-    <t>27-03-2026</t>
-  </si>
-  <si>
-    <t>30-03-2026</t>
-  </si>
-  <si>
-    <t>31-03-2026</t>
-  </si>
-  <si>
-    <t>04-06-2026</t>
-  </si>
-  <si>
-    <t>04-07-2026</t>
-  </si>
-  <si>
-    <t>04-08-2026</t>
-  </si>
-  <si>
-    <t>04-09-2026</t>
-  </si>
-  <si>
-    <t>04-10-2026</t>
-  </si>
-  <si>
-    <t>13-04-2026</t>
-  </si>
-  <si>
-    <t>14-04-2026</t>
-  </si>
-  <si>
-    <t>15-04-2026</t>
-  </si>
-  <si>
-    <t>16-04-2026</t>
-  </si>
-  <si>
-    <t>17-04-2026</t>
-  </si>
-  <si>
-    <t>20-04-2026</t>
-  </si>
-  <si>
-    <t>21-04-2026</t>
-  </si>
-  <si>
-    <t>22-04-2026</t>
-  </si>
-  <si>
-    <t>24-04-2026</t>
-  </si>
-  <si>
-    <t>27-04-2026</t>
-  </si>
-  <si>
-    <t>29-04-2026</t>
-  </si>
-  <si>
-    <t>30-04-2026</t>
-  </si>
-  <si>
-    <t>06-05-2026</t>
-  </si>
-  <si>
-    <t>07-05-2026</t>
-  </si>
-  <si>
-    <t>08-05-2026</t>
   </si>
   <si>
     <t>1 TINTA CYAN S40600</t>
@@ -1346,6 +1127,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -1398,11 +1183,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1699,51 +1486,54 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K243"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="A2" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>84</v>
-      </c>
       <c r="C2" t="s">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="D2">
         <v>985000</v>
@@ -1752,27 +1542,27 @@
         <v>268</v>
       </c>
       <c r="G2" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H2" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I2" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J2" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
+      <c r="A3" s="3">
+        <v>46143</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="D3">
         <v>5292000</v>
@@ -1781,27 +1571,27 @@
         <v>269</v>
       </c>
       <c r="G3" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H3" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I3" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J3" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
+      <c r="A4" s="3">
+        <v>46150</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>190</v>
       </c>
       <c r="D4">
         <v>2180000</v>
@@ -1810,27 +1600,27 @@
         <v>270</v>
       </c>
       <c r="G4" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H4" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I4" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J4" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
+      <c r="A5" s="3">
+        <v>46150</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E5">
         <v>1808</v>
@@ -1839,27 +1629,27 @@
         <v>271</v>
       </c>
       <c r="G5" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H5" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I5" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J5" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>12</v>
+      <c r="A6" s="3">
+        <v>46150</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>265</v>
+        <v>192</v>
       </c>
       <c r="E6">
         <v>6850.19</v>
@@ -1868,18 +1658,18 @@
         <v>272</v>
       </c>
       <c r="G6" t="s">
-        <v>378</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>13</v>
+      <c r="A7" s="3">
+        <v>46150</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="D7">
         <v>6051000</v>
@@ -1888,27 +1678,27 @@
         <v>273</v>
       </c>
       <c r="G7" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H7" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I7" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J7" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>13</v>
+      <c r="A8" s="3">
+        <v>46150</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>267</v>
+        <v>194</v>
       </c>
       <c r="D8">
         <v>985000</v>
@@ -1917,27 +1707,27 @@
         <v>274</v>
       </c>
       <c r="G8" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H8" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I8" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J8" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>13</v>
+      <c r="A9" s="3">
+        <v>46150</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="D9">
         <v>12348000</v>
@@ -1946,27 +1736,27 @@
         <v>275</v>
       </c>
       <c r="G9" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H9" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I9" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J9" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>14</v>
+      <c r="A10" s="3">
+        <v>46150</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>268</v>
+        <v>195</v>
       </c>
       <c r="D10">
         <v>550000</v>
@@ -1975,27 +1765,27 @@
         <v>276</v>
       </c>
       <c r="G10" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H10" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="I10" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J10" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>14</v>
+      <c r="A11" s="3">
+        <v>46150</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>269</v>
+        <v>196</v>
       </c>
       <c r="D11">
         <v>57590000</v>
@@ -2004,49 +1794,55 @@
         <v>277</v>
       </c>
       <c r="G11" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H11" t="s">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="I11" t="s">
-        <v>391</v>
+        <v>318</v>
       </c>
       <c r="J11" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:11">
+      <c r="A12" s="3">
+        <v>46150</v>
+      </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F12">
         <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:11">
+      <c r="A13" s="3">
+        <v>46150</v>
+      </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F13">
         <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>15</v>
+      <c r="A14" s="3">
+        <v>46150</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="D14">
         <v>9590000</v>
@@ -2055,27 +1851,27 @@
         <v>280</v>
       </c>
       <c r="G14" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H14" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I14" t="s">
-        <v>392</v>
+        <v>319</v>
       </c>
       <c r="J14" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>16</v>
+      <c r="A15" s="3">
+        <v>46150</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>269</v>
+        <v>196</v>
       </c>
       <c r="D15">
         <v>7900000</v>
@@ -2084,27 +1880,27 @@
         <v>281</v>
       </c>
       <c r="G15" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H15" t="s">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="I15" t="s">
-        <v>393</v>
+        <v>320</v>
       </c>
       <c r="J15" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>16</v>
+      <c r="A16" s="3">
+        <v>46150</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E16">
         <v>2298</v>
@@ -2113,27 +1909,27 @@
         <v>282</v>
       </c>
       <c r="G16" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H16" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I16" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J16" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>16</v>
+      <c r="A17" s="3">
+        <v>46150</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="D17">
         <v>995000</v>
@@ -2142,27 +1938,27 @@
         <v>283</v>
       </c>
       <c r="G17" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H17" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I17" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J17" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>16</v>
+      <c r="A18" s="3">
+        <v>46150</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>265</v>
+        <v>192</v>
       </c>
       <c r="E18">
         <v>1400</v>
@@ -2172,14 +1968,14 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>16</v>
+      <c r="A19" s="3">
+        <v>46150</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="D19">
         <v>3528000</v>
@@ -2188,27 +1984,27 @@
         <v>285</v>
       </c>
       <c r="G19" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H19" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I19" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J19" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>16</v>
+      <c r="A20" s="3">
+        <v>46150</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D20">
         <v>4320000</v>
@@ -2217,27 +2013,27 @@
         <v>286</v>
       </c>
       <c r="G20" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H20" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I20" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J20" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>15</v>
+      <c r="A21" s="3">
+        <v>46150</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>273</v>
+        <v>200</v>
       </c>
       <c r="D21">
         <v>1990000</v>
@@ -2246,27 +2042,27 @@
         <v>287</v>
       </c>
       <c r="G21" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H21" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I21" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J21" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>15</v>
+      <c r="A22" s="3">
+        <v>46150</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="D22">
         <v>3990000</v>
@@ -2275,27 +2071,27 @@
         <v>288</v>
       </c>
       <c r="G22" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H22" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I22" t="s">
-        <v>394</v>
+        <v>321</v>
       </c>
       <c r="J22" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>15</v>
+      <c r="A23" s="3">
+        <v>46150</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
       <c r="D23">
         <v>5190000</v>
@@ -2304,27 +2100,27 @@
         <v>289</v>
       </c>
       <c r="G23" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H23" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="I23" t="s">
-        <v>395</v>
+        <v>322</v>
       </c>
       <c r="J23" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>15</v>
+      <c r="A24" s="3">
+        <v>46150</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>276</v>
+        <v>203</v>
       </c>
       <c r="D24">
         <v>939000</v>
@@ -2333,27 +2129,27 @@
         <v>290</v>
       </c>
       <c r="G24" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H24" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I24" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J24" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>17</v>
+      <c r="A25" s="3">
+        <v>46150</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D25">
         <v>1080000</v>
@@ -2362,24 +2158,24 @@
         <v>291</v>
       </c>
       <c r="G25" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="I25" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J25" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" t="s">
-        <v>18</v>
+      <c r="A26" s="3">
+        <v>46150</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="D26">
         <v>1500000</v>
@@ -2388,18 +2184,18 @@
         <v>292</v>
       </c>
       <c r="G26" t="s">
-        <v>378</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" t="s">
-        <v>18</v>
+      <c r="A27" s="3">
+        <v>46150</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>278</v>
+        <v>205</v>
       </c>
       <c r="D27">
         <v>2890000</v>
@@ -2408,27 +2204,27 @@
         <v>293</v>
       </c>
       <c r="G27" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H27" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I27" t="s">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="J27" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" t="s">
-        <v>18</v>
+      <c r="A28" s="3">
+        <v>46150</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>279</v>
+        <v>206</v>
       </c>
       <c r="D28">
         <v>3160000</v>
@@ -2437,27 +2233,27 @@
         <v>294</v>
       </c>
       <c r="G28" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H28" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I28" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J28" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" t="s">
-        <v>18</v>
+      <c r="A29" s="3">
+        <v>46150</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E29">
         <v>1356</v>
@@ -2466,27 +2262,27 @@
         <v>295</v>
       </c>
       <c r="G29" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H29" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I29" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J29" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>19</v>
+      <c r="A30" s="3">
+        <v>46150</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>280</v>
+        <v>207</v>
       </c>
       <c r="D30">
         <v>5190000</v>
@@ -2495,27 +2291,27 @@
         <v>296</v>
       </c>
       <c r="G30" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H30" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I30" t="s">
-        <v>395</v>
+        <v>322</v>
       </c>
       <c r="J30" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" t="s">
-        <v>19</v>
+      <c r="A31" s="3">
+        <v>46150</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>281</v>
+        <v>208</v>
       </c>
       <c r="D31">
         <v>4590000</v>
@@ -2524,27 +2320,27 @@
         <v>297</v>
       </c>
       <c r="G31" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H31" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I31" t="s">
-        <v>397</v>
+        <v>324</v>
       </c>
       <c r="J31" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" t="s">
-        <v>19</v>
+      <c r="A32" s="3">
+        <v>46150</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>282</v>
+        <v>209</v>
       </c>
       <c r="D32">
         <v>13850000</v>
@@ -2553,27 +2349,27 @@
         <v>298</v>
       </c>
       <c r="G32" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H32" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="I32" t="s">
-        <v>398</v>
+        <v>325</v>
       </c>
       <c r="J32" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>19</v>
+      <c r="A33" s="3">
+        <v>46150</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>283</v>
+        <v>210</v>
       </c>
       <c r="D33">
         <v>2370000</v>
@@ -2582,27 +2378,27 @@
         <v>299</v>
       </c>
       <c r="G33" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H33" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I33" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J33" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" t="s">
-        <v>20</v>
+      <c r="A34" s="3">
+        <v>46150</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>284</v>
+        <v>211</v>
       </c>
       <c r="D34">
         <v>3160000</v>
@@ -2611,27 +2407,27 @@
         <v>301</v>
       </c>
       <c r="G34" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H34" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I34" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J34" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" t="s">
-        <v>21</v>
+      <c r="A35" s="3">
+        <v>46150</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="D35">
         <v>199000</v>
@@ -2640,27 +2436,27 @@
         <v>302</v>
       </c>
       <c r="G35" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H35" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I35" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J35" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" t="s">
-        <v>21</v>
+      <c r="A36" s="3">
+        <v>46150</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>286</v>
+        <v>213</v>
       </c>
       <c r="D36">
         <v>3290000</v>
@@ -2669,27 +2465,27 @@
         <v>303</v>
       </c>
       <c r="G36" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H36" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I36" t="s">
-        <v>400</v>
+        <v>327</v>
       </c>
       <c r="J36" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>21</v>
+      <c r="A37" s="3">
+        <v>46150</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>287</v>
+        <v>214</v>
       </c>
       <c r="D37">
         <v>12080000</v>
@@ -2698,27 +2494,27 @@
         <v>304</v>
       </c>
       <c r="G37" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H37" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="I37" t="s">
-        <v>398</v>
+        <v>325</v>
       </c>
       <c r="J37" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" t="s">
-        <v>21</v>
+      <c r="A38" s="3">
+        <v>46150</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="D38">
         <v>2370000</v>
@@ -2727,27 +2523,27 @@
         <v>305</v>
       </c>
       <c r="G38" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H38" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I38" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J38" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>21</v>
+      <c r="A39" s="3">
+        <v>46150</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>289</v>
+        <v>216</v>
       </c>
       <c r="D39">
         <v>199000</v>
@@ -2756,27 +2552,27 @@
         <v>306</v>
       </c>
       <c r="G39" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H39" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I39" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J39" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" t="s">
-        <v>21</v>
+      <c r="A40" s="3">
+        <v>46150</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>290</v>
+        <v>217</v>
       </c>
       <c r="D40">
         <v>2590000</v>
@@ -2785,27 +2581,27 @@
         <v>307</v>
       </c>
       <c r="G40" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H40" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I40" t="s">
-        <v>401</v>
+        <v>328</v>
       </c>
       <c r="J40" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" t="s">
-        <v>21</v>
+      <c r="A41" s="3">
+        <v>46150</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>291</v>
+        <v>218</v>
       </c>
       <c r="D41">
         <v>6390000</v>
@@ -2814,27 +2610,27 @@
         <v>308</v>
       </c>
       <c r="G41" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H41" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="I41" t="s">
-        <v>402</v>
+        <v>329</v>
       </c>
       <c r="J41" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" t="s">
-        <v>22</v>
+      <c r="A42" s="3">
+        <v>46150</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="D42">
         <v>6080000</v>
@@ -2843,27 +2639,27 @@
         <v>309</v>
       </c>
       <c r="G42" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H42" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I42" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J42" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" t="s">
-        <v>22</v>
+      <c r="A43" s="3">
+        <v>46150</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>280</v>
+        <v>207</v>
       </c>
       <c r="D43">
         <v>7190000</v>
@@ -2872,41 +2668,41 @@
         <v>310</v>
       </c>
       <c r="G43" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H43" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I43" t="s">
-        <v>403</v>
+        <v>330</v>
       </c>
       <c r="J43" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" t="s">
-        <v>22</v>
+      <c r="A44" s="3">
+        <v>46150</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F44">
         <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" t="s">
-        <v>22</v>
+      <c r="A45" s="3">
+        <v>46150</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>292</v>
+        <v>219</v>
       </c>
       <c r="D45">
         <v>1090000</v>
@@ -2915,27 +2711,27 @@
         <v>312</v>
       </c>
       <c r="G45" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H45" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I45" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J45" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" t="s">
-        <v>23</v>
+      <c r="A46" s="3">
+        <v>46150</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>293</v>
+        <v>220</v>
       </c>
       <c r="D46">
         <v>1320000</v>
@@ -2944,27 +2740,27 @@
         <v>313</v>
       </c>
       <c r="G46" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H46" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I46" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J46" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" t="s">
-        <v>24</v>
+      <c r="A47" s="3">
+        <v>46150</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>294</v>
+        <v>221</v>
       </c>
       <c r="D47">
         <v>209000</v>
@@ -2973,27 +2769,27 @@
         <v>314</v>
       </c>
       <c r="G47" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H47" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I47" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J47" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" t="s">
-        <v>24</v>
+      <c r="A48" s="3">
+        <v>46150</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>295</v>
+        <v>222</v>
       </c>
       <c r="D48">
         <v>6445000</v>
@@ -3002,27 +2798,27 @@
         <v>315</v>
       </c>
       <c r="G48" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H48" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I48" t="s">
-        <v>402</v>
+        <v>329</v>
       </c>
       <c r="J48" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" t="s">
-        <v>24</v>
+      <c r="A49" s="3">
+        <v>46150</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="C49" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E49">
         <v>2712</v>
@@ -3031,27 +2827,27 @@
         <v>316</v>
       </c>
       <c r="G49" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H49" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I49" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J49" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" t="s">
-        <v>24</v>
+      <c r="A50" s="3">
+        <v>46150</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>296</v>
+        <v>223</v>
       </c>
       <c r="D50">
         <v>395000</v>
@@ -3060,27 +2856,27 @@
         <v>317</v>
       </c>
       <c r="G50" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H50" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I50" t="s">
-        <v>404</v>
+        <v>331</v>
       </c>
       <c r="J50" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" t="s">
-        <v>24</v>
+      <c r="A51" s="3">
+        <v>46150</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>295</v>
+        <v>222</v>
       </c>
       <c r="D51">
         <v>812000</v>
@@ -3089,27 +2885,27 @@
         <v>318</v>
       </c>
       <c r="G51" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H51" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I51" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J51" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" t="s">
-        <v>25</v>
+      <c r="A52" s="3">
+        <v>46150</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="D52">
         <v>50000000</v>
@@ -3118,21 +2914,21 @@
         <v>319</v>
       </c>
       <c r="G52" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H52" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" t="s">
-        <v>26</v>
+      <c r="A53" s="3">
+        <v>46150</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="E53">
         <v>22390</v>
@@ -3141,27 +2937,27 @@
         <v>320</v>
       </c>
       <c r="G53" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H53" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I53" t="s">
-        <v>406</v>
+        <v>333</v>
       </c>
       <c r="J53" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" t="s">
-        <v>26</v>
+      <c r="A54" s="3">
+        <v>46150</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>299</v>
+        <v>226</v>
       </c>
       <c r="D54">
         <v>405000</v>
@@ -3170,27 +2966,27 @@
         <v>321</v>
       </c>
       <c r="G54" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H54" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I54" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J54" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" t="s">
-        <v>26</v>
+      <c r="A55" s="3">
+        <v>46150</v>
       </c>
       <c r="B55" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>300</v>
+        <v>227</v>
       </c>
       <c r="D55">
         <v>7512000</v>
@@ -3199,27 +2995,27 @@
         <v>322</v>
       </c>
       <c r="G55" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H55" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I55" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J55" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" t="s">
-        <v>27</v>
+      <c r="A56" s="3">
+        <v>46150</v>
       </c>
       <c r="B56" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E56">
         <v>1356</v>
@@ -3228,27 +3024,27 @@
         <v>323</v>
       </c>
       <c r="G56" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H56" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I56" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J56" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" t="s">
-        <v>27</v>
+      <c r="A57" s="3">
+        <v>46150</v>
       </c>
       <c r="B57" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>301</v>
+        <v>228</v>
       </c>
       <c r="D57">
         <v>3790000</v>
@@ -3257,27 +3053,27 @@
         <v>324</v>
       </c>
       <c r="G57" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H57" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I57" t="s">
-        <v>407</v>
+        <v>334</v>
       </c>
       <c r="J57" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" t="s">
-        <v>28</v>
+      <c r="A58" s="3">
+        <v>46150</v>
       </c>
       <c r="B58" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>302</v>
+        <v>229</v>
       </c>
       <c r="D58">
         <v>11790000</v>
@@ -3286,27 +3082,27 @@
         <v>325</v>
       </c>
       <c r="G58" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H58" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I58" t="s">
-        <v>408</v>
+        <v>335</v>
       </c>
       <c r="J58" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" t="s">
-        <v>28</v>
+      <c r="A59" s="3">
+        <v>46150</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="D59">
         <v>498000</v>
@@ -3315,27 +3111,27 @@
         <v>326</v>
       </c>
       <c r="G59" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H59" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I59" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="J59" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" t="s">
-        <v>28</v>
+      <c r="A60" s="3">
+        <v>46150</v>
       </c>
       <c r="B60" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>304</v>
+        <v>231</v>
       </c>
       <c r="D60">
         <v>3345000</v>
@@ -3344,27 +3140,27 @@
         <v>327</v>
       </c>
       <c r="G60" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H60" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I60" t="s">
-        <v>400</v>
+        <v>327</v>
       </c>
       <c r="J60" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" t="s">
-        <v>29</v>
+      <c r="A61" s="3">
+        <v>46150</v>
       </c>
       <c r="B61" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D61">
         <v>2880000</v>
@@ -3373,27 +3169,27 @@
         <v>328</v>
       </c>
       <c r="G61" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H61" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I61" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J61" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" t="s">
-        <v>30</v>
+      <c r="A62" s="3">
+        <v>46150</v>
       </c>
       <c r="B62" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>305</v>
+        <v>232</v>
       </c>
       <c r="D62">
         <v>419000</v>
@@ -3402,38 +3198,41 @@
         <v>329</v>
       </c>
       <c r="G62" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H62" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I62" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J62" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="63" spans="1:10">
+      <c r="A63" s="3">
+        <v>46150</v>
+      </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F63">
         <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" t="s">
-        <v>30</v>
+      <c r="A64" s="3">
+        <v>46150</v>
       </c>
       <c r="B64" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>306</v>
+        <v>233</v>
       </c>
       <c r="D64">
         <v>14112000</v>
@@ -3442,27 +3241,27 @@
         <v>331</v>
       </c>
       <c r="G64" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H64" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="I64" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J64" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" t="s">
-        <v>30</v>
+      <c r="A65" s="3">
+        <v>46150</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>307</v>
+        <v>234</v>
       </c>
       <c r="D65">
         <v>65000</v>
@@ -3471,27 +3270,27 @@
         <v>332</v>
       </c>
       <c r="G65" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H65" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I65" t="s">
-        <v>410</v>
+        <v>337</v>
       </c>
       <c r="J65" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" t="s">
-        <v>31</v>
+      <c r="A66" s="3">
+        <v>46150</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="C66" t="s">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="D66">
         <v>498000</v>
@@ -3500,27 +3299,27 @@
         <v>333</v>
       </c>
       <c r="G66" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H66" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I66" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="J66" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" t="s">
-        <v>31</v>
+      <c r="A67" s="3">
+        <v>46150</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>308</v>
+        <v>235</v>
       </c>
       <c r="D67">
         <v>1585000</v>
@@ -3529,27 +3328,27 @@
         <v>334</v>
       </c>
       <c r="G67" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H67" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I67" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J67" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" t="s">
-        <v>31</v>
+      <c r="A68" s="3">
+        <v>46150</v>
       </c>
       <c r="B68" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="C68" t="s">
-        <v>309</v>
+        <v>236</v>
       </c>
       <c r="D68">
         <v>199000</v>
@@ -3558,49 +3357,55 @@
         <v>335</v>
       </c>
       <c r="G68" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H68" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I68" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J68" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69" spans="1:10">
+      <c r="A69" s="3">
+        <v>46150</v>
+      </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C69" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F69">
         <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:10">
+      <c r="A70" s="3">
+        <v>46150</v>
+      </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F70">
         <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" t="s">
-        <v>31</v>
+      <c r="A71" s="3">
+        <v>46150</v>
       </c>
       <c r="B71" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="C71" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="D71">
         <v>3160000</v>
@@ -3609,27 +3414,27 @@
         <v>338</v>
       </c>
       <c r="G71" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H71" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I71" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J71" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" t="s">
-        <v>32</v>
+      <c r="A72" s="3">
+        <v>46150</v>
       </c>
       <c r="B72" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="C72" t="s">
-        <v>310</v>
+        <v>237</v>
       </c>
       <c r="D72">
         <v>3645000</v>
@@ -3638,27 +3443,27 @@
         <v>339</v>
       </c>
       <c r="G72" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H72" t="s">
-        <v>384</v>
+        <v>311</v>
       </c>
       <c r="I72" t="s">
-        <v>400</v>
+        <v>327</v>
       </c>
       <c r="J72" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" t="s">
-        <v>32</v>
+      <c r="A73" s="3">
+        <v>46150</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D73">
         <v>890000</v>
@@ -3667,24 +3472,24 @@
         <v>340</v>
       </c>
       <c r="G73" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="I73" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J73" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" t="s">
-        <v>32</v>
+      <c r="A74" s="3">
+        <v>46150</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D74">
         <v>3240000</v>
@@ -3693,24 +3498,24 @@
         <v>341</v>
       </c>
       <c r="G74" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="I74" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J74" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" t="s">
-        <v>33</v>
+      <c r="A75" s="3">
+        <v>46150</v>
       </c>
       <c r="B75" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>194</v>
       </c>
       <c r="D75">
         <v>1970000</v>
@@ -3719,27 +3524,27 @@
         <v>342</v>
       </c>
       <c r="G75" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H75" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I75" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J75" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" t="s">
-        <v>33</v>
+      <c r="A76" s="3">
+        <v>46150</v>
       </c>
       <c r="B76" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>311</v>
+        <v>238</v>
       </c>
       <c r="D76">
         <v>1690000</v>
@@ -3748,27 +3553,27 @@
         <v>343</v>
       </c>
       <c r="G76" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H76" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I76" t="s">
-        <v>411</v>
+        <v>338</v>
       </c>
       <c r="J76" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" t="s">
-        <v>34</v>
+      <c r="A77" s="3">
+        <v>46150</v>
       </c>
       <c r="B77" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>312</v>
+        <v>239</v>
       </c>
       <c r="D77">
         <v>6690000</v>
@@ -3777,27 +3582,27 @@
         <v>345</v>
       </c>
       <c r="G77" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H77" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I77" t="s">
-        <v>412</v>
+        <v>339</v>
       </c>
       <c r="J77" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" t="s">
-        <v>35</v>
+      <c r="A78" s="3">
+        <v>46150</v>
       </c>
       <c r="B78" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>313</v>
+        <v>240</v>
       </c>
       <c r="D78">
         <v>405000</v>
@@ -3806,27 +3611,27 @@
         <v>346</v>
       </c>
       <c r="G78" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H78" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I78" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J78" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" t="s">
-        <v>35</v>
+      <c r="A79" s="3">
+        <v>46150</v>
       </c>
       <c r="B79" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>314</v>
+        <v>241</v>
       </c>
       <c r="D79">
         <v>2370000</v>
@@ -3835,27 +3640,27 @@
         <v>347</v>
       </c>
       <c r="G79" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H79" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I79" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J79" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" t="s">
-        <v>35</v>
+      <c r="A80" s="3">
+        <v>46150</v>
       </c>
       <c r="B80" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E80">
         <v>6257.66</v>
@@ -3864,18 +3669,18 @@
         <v>348</v>
       </c>
       <c r="G80" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" t="s">
-        <v>35</v>
+      <c r="A81" s="3">
+        <v>46150</v>
       </c>
       <c r="B81" t="s">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>308</v>
+        <v>235</v>
       </c>
       <c r="D81">
         <v>1635000</v>
@@ -3884,38 +3689,41 @@
         <v>349</v>
       </c>
       <c r="G81" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H81" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I81" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J81" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="82" spans="1:10">
+      <c r="A82" s="3">
+        <v>46150</v>
+      </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F82">
         <v>350</v>
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" t="s">
-        <v>36</v>
+      <c r="A83" s="3">
+        <v>46150</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="C83" t="s">
-        <v>315</v>
+        <v>242</v>
       </c>
       <c r="D83">
         <v>990000</v>
@@ -3924,27 +3732,27 @@
         <v>351</v>
       </c>
       <c r="G83" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H83" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I83" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J83" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" t="s">
-        <v>36</v>
+      <c r="A84" s="3">
+        <v>46150</v>
       </c>
       <c r="B84" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="D84">
         <v>1580000</v>
@@ -3953,27 +3761,27 @@
         <v>352</v>
       </c>
       <c r="G84" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H84" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I84" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J84" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" t="s">
-        <v>37</v>
+      <c r="A85" s="3">
+        <v>46150</v>
       </c>
       <c r="B85" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="D85">
         <v>1970000</v>
@@ -3982,27 +3790,27 @@
         <v>353</v>
       </c>
       <c r="G85" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H85" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I85" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J85" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" t="s">
+      <c r="A86" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B86" t="s">
         <v>37</v>
       </c>
-      <c r="B86" t="s">
-        <v>110</v>
-      </c>
       <c r="C86" t="s">
-        <v>316</v>
+        <v>243</v>
       </c>
       <c r="D86">
         <v>5190000</v>
@@ -4011,27 +3819,27 @@
         <v>354</v>
       </c>
       <c r="G86" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H86" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I86" t="s">
-        <v>395</v>
+        <v>322</v>
       </c>
       <c r="J86" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" t="s">
-        <v>37</v>
+      <c r="A87" s="3">
+        <v>46150</v>
       </c>
       <c r="B87" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>317</v>
+        <v>244</v>
       </c>
       <c r="D87">
         <v>53800000</v>
@@ -4040,38 +3848,41 @@
         <v>355</v>
       </c>
       <c r="G87" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H87" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I87" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J87" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="88" spans="1:10">
+      <c r="A88" s="3">
+        <v>46150</v>
+      </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F88">
         <v>356</v>
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" t="s">
-        <v>38</v>
+      <c r="A89" s="3">
+        <v>46150</v>
       </c>
       <c r="B89" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="C89" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D89">
         <v>4320000</v>
@@ -4080,27 +3891,27 @@
         <v>357</v>
       </c>
       <c r="G89" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H89" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="I89" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J89" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" t="s">
-        <v>39</v>
+      <c r="A90" s="3">
+        <v>46150</v>
       </c>
       <c r="B90" t="s">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="C90" t="s">
-        <v>314</v>
+        <v>241</v>
       </c>
       <c r="D90">
         <v>1580000</v>
@@ -4109,27 +3920,27 @@
         <v>358</v>
       </c>
       <c r="G90" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H90" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I90" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J90" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" t="s">
-        <v>39</v>
+      <c r="A91" s="3">
+        <v>46150</v>
       </c>
       <c r="B91" t="s">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="C91" t="s">
-        <v>318</v>
+        <v>245</v>
       </c>
       <c r="D91">
         <v>11976000</v>
@@ -4138,27 +3949,27 @@
         <v>359</v>
       </c>
       <c r="G91" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H91" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I91" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J91" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" t="s">
-        <v>39</v>
+      <c r="A92" s="3">
+        <v>46150</v>
       </c>
       <c r="B92" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="C92" t="s">
-        <v>319</v>
+        <v>246</v>
       </c>
       <c r="D92">
         <v>1990000</v>
@@ -4167,27 +3978,27 @@
         <v>360</v>
       </c>
       <c r="G92" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H92" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I92" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J92" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" t="s">
-        <v>39</v>
+      <c r="A93" s="3">
+        <v>46150</v>
       </c>
       <c r="B93" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>279</v>
+        <v>206</v>
       </c>
       <c r="D93">
         <v>3160000</v>
@@ -4196,27 +4007,27 @@
         <v>361</v>
       </c>
       <c r="G93" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H93" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I93" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J93" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" t="s">
-        <v>40</v>
+      <c r="A94" s="3">
+        <v>46150</v>
       </c>
       <c r="B94" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E94">
         <v>3616</v>
@@ -4225,27 +4036,27 @@
         <v>362</v>
       </c>
       <c r="G94" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H94" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I94" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J94" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" t="s">
-        <v>40</v>
+      <c r="A95" s="3">
+        <v>46150</v>
       </c>
       <c r="B95" t="s">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="C95" t="s">
-        <v>315</v>
+        <v>242</v>
       </c>
       <c r="D95">
         <v>1980000</v>
@@ -4254,27 +4065,27 @@
         <v>363</v>
       </c>
       <c r="G95" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H95" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I95" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J95" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" t="s">
-        <v>40</v>
+      <c r="A96" s="3">
+        <v>46150</v>
       </c>
       <c r="B96" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="C96" t="s">
-        <v>320</v>
+        <v>247</v>
       </c>
       <c r="D96">
         <v>199000</v>
@@ -4283,27 +4094,27 @@
         <v>364</v>
       </c>
       <c r="G96" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H96" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I96" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J96" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" t="s">
-        <v>41</v>
+      <c r="A97" s="3">
+        <v>46150</v>
       </c>
       <c r="B97" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="C97" t="s">
-        <v>321</v>
+        <v>248</v>
       </c>
       <c r="D97">
         <v>199000</v>
@@ -4312,27 +4123,27 @@
         <v>365</v>
       </c>
       <c r="G97" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H97" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I97" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J97" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" t="s">
-        <v>41</v>
+      <c r="A98" s="3">
+        <v>46150</v>
       </c>
       <c r="B98" t="s">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="C98" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="D98">
         <v>2958000</v>
@@ -4341,27 +4152,27 @@
         <v>366</v>
       </c>
       <c r="G98" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H98" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I98" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J98" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" t="s">
-        <v>42</v>
+      <c r="A99" s="3">
+        <v>46150</v>
       </c>
       <c r="B99" t="s">
-        <v>165</v>
+        <v>92</v>
       </c>
       <c r="C99" t="s">
-        <v>315</v>
+        <v>242</v>
       </c>
       <c r="D99">
         <v>1980000</v>
@@ -4370,27 +4181,27 @@
         <v>367</v>
       </c>
       <c r="G99" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H99" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I99" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J99" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" t="s">
-        <v>42</v>
+      <c r="A100" s="3">
+        <v>46150</v>
       </c>
       <c r="B100" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="C100" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="D100">
         <v>790000</v>
@@ -4399,27 +4210,27 @@
         <v>368</v>
       </c>
       <c r="G100" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H100" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I100" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J100" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" t="s">
-        <v>42</v>
+      <c r="A101" s="3">
+        <v>46150</v>
       </c>
       <c r="B101" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="C101" t="s">
-        <v>322</v>
+        <v>249</v>
       </c>
       <c r="D101">
         <v>200000</v>
@@ -4428,38 +4239,41 @@
         <v>369</v>
       </c>
       <c r="G101" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H101" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="I101" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J101" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:10">
+      <c r="A102" s="3">
+        <v>46150</v>
+      </c>
       <c r="B102" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C102" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F102">
         <v>370</v>
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" t="s">
-        <v>43</v>
+      <c r="A103" s="3">
+        <v>46150</v>
       </c>
       <c r="B103" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="C103" t="s">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="D103">
         <v>790000</v>
@@ -4468,27 +4282,27 @@
         <v>371</v>
       </c>
       <c r="G103" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H103" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I103" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J103" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" t="s">
-        <v>43</v>
+      <c r="A104" s="3">
+        <v>46150</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="C104" t="s">
-        <v>324</v>
+        <v>251</v>
       </c>
       <c r="D104">
         <v>199000</v>
@@ -4497,27 +4311,27 @@
         <v>372</v>
       </c>
       <c r="G104" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H104" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I104" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J104" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" t="s">
-        <v>43</v>
+      <c r="A105" s="3">
+        <v>46150</v>
       </c>
       <c r="B105" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="C105" t="s">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="D105">
         <v>498000</v>
@@ -4526,27 +4340,27 @@
         <v>373</v>
       </c>
       <c r="G105" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H105" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I105" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="J105" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" t="s">
-        <v>43</v>
+      <c r="A106" s="3">
+        <v>46150</v>
       </c>
       <c r="B106" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="C106" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D106">
         <v>7560000</v>
@@ -4555,27 +4369,27 @@
         <v>374</v>
       </c>
       <c r="G106" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H106" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="I106" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J106" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" t="s">
-        <v>43</v>
+      <c r="A107" s="3">
+        <v>46150</v>
       </c>
       <c r="B107" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="C107" t="s">
-        <v>325</v>
+        <v>252</v>
       </c>
       <c r="D107">
         <v>209000</v>
@@ -4584,27 +4398,27 @@
         <v>375</v>
       </c>
       <c r="G107" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H107" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I107" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J107" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" t="s">
-        <v>44</v>
+      <c r="A108" s="3">
+        <v>46150</v>
       </c>
       <c r="B108" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="C108" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D108">
         <v>2880000</v>
@@ -4613,27 +4427,27 @@
         <v>376</v>
       </c>
       <c r="G108" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H108" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I108" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J108" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" t="s">
-        <v>45</v>
+      <c r="A109" s="3">
+        <v>46150</v>
       </c>
       <c r="B109" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="C109" t="s">
-        <v>326</v>
+        <v>253</v>
       </c>
       <c r="D109">
         <v>775000</v>
@@ -4642,27 +4456,27 @@
         <v>377</v>
       </c>
       <c r="G109" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H109" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I109" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J109" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" t="s">
-        <v>45</v>
+      <c r="A110" s="3">
+        <v>46150</v>
       </c>
       <c r="B110" t="s">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="C110" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E110">
         <v>3164</v>
@@ -4671,49 +4485,55 @@
         <v>378</v>
       </c>
       <c r="G110" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H110" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I110" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J110" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="1:10">
+      <c r="A111" s="3">
+        <v>46150</v>
+      </c>
       <c r="B111" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C111" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F111">
         <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:10">
+      <c r="A112" s="3">
+        <v>46150</v>
+      </c>
       <c r="B112" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C112" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F112">
         <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" t="s">
-        <v>45</v>
+      <c r="A113" s="3">
+        <v>46150</v>
       </c>
       <c r="B113" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="C113" t="s">
-        <v>327</v>
+        <v>254</v>
       </c>
       <c r="D113">
         <v>6390000</v>
@@ -4722,27 +4542,27 @@
         <v>381</v>
       </c>
       <c r="G113" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H113" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I113" t="s">
-        <v>402</v>
+        <v>329</v>
       </c>
       <c r="J113" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" t="s">
-        <v>46</v>
+      <c r="A114" s="3">
+        <v>46150</v>
       </c>
       <c r="B114" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="C114" t="s">
-        <v>308</v>
+        <v>235</v>
       </c>
       <c r="D114">
         <v>1635000</v>
@@ -4751,27 +4571,27 @@
         <v>382</v>
       </c>
       <c r="G114" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H114" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I114" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J114" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" t="s">
-        <v>46</v>
+      <c r="A115" s="3">
+        <v>46150</v>
       </c>
       <c r="B115" t="s">
-        <v>174</v>
+        <v>101</v>
       </c>
       <c r="C115" t="s">
-        <v>328</v>
+        <v>255</v>
       </c>
       <c r="D115">
         <v>220000</v>
@@ -4780,27 +4600,27 @@
         <v>383</v>
       </c>
       <c r="G115" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H115" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I115" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J115" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" t="s">
-        <v>46</v>
+      <c r="A116" s="3">
+        <v>46150</v>
       </c>
       <c r="B116" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="C116" t="s">
-        <v>329</v>
+        <v>256</v>
       </c>
       <c r="D116">
         <v>775000</v>
@@ -4809,49 +4629,55 @@
         <v>384</v>
       </c>
       <c r="G116" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H116" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I116" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J116" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="117" spans="1:10">
+      <c r="A117" s="3">
+        <v>46150</v>
+      </c>
       <c r="B117" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C117" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F117">
         <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:10">
+      <c r="A118" s="3">
+        <v>46150</v>
+      </c>
       <c r="B118" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C118" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F118">
         <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" t="s">
-        <v>47</v>
+      <c r="A119" s="3">
+        <v>46150</v>
       </c>
       <c r="B119" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="C119" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="D119">
         <v>19404000</v>
@@ -4860,27 +4686,27 @@
         <v>387</v>
       </c>
       <c r="G119" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H119" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I119" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J119" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" t="s">
-        <v>47</v>
+      <c r="A120" s="3">
+        <v>46150</v>
       </c>
       <c r="B120" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="C120" t="s">
-        <v>330</v>
+        <v>257</v>
       </c>
       <c r="D120">
         <v>53600000</v>
@@ -4889,27 +4715,27 @@
         <v>388</v>
       </c>
       <c r="G120" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H120" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I120" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J120" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" t="s">
-        <v>48</v>
+      <c r="A121" s="3">
+        <v>46150</v>
       </c>
       <c r="B121" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="C121" t="s">
-        <v>331</v>
+        <v>258</v>
       </c>
       <c r="D121">
         <v>6300000</v>
@@ -4918,27 +4744,27 @@
         <v>389</v>
       </c>
       <c r="G121" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H121" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I121" t="s">
-        <v>402</v>
+        <v>329</v>
       </c>
       <c r="J121" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="122" spans="1:10">
-      <c r="A122" t="s">
-        <v>49</v>
+      <c r="A122" s="3">
+        <v>46150</v>
       </c>
       <c r="B122" t="s">
-        <v>176</v>
+        <v>103</v>
       </c>
       <c r="C122" t="s">
-        <v>332</v>
+        <v>259</v>
       </c>
       <c r="D122">
         <v>19039000</v>
@@ -4947,27 +4773,27 @@
         <v>390</v>
       </c>
       <c r="G122" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H122" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I122" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="J122" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" t="s">
-        <v>49</v>
+      <c r="A123" s="3">
+        <v>46150</v>
       </c>
       <c r="B123" t="s">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="C123" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="D123">
         <v>8981700</v>
@@ -4976,27 +4802,27 @@
         <v>391</v>
       </c>
       <c r="G123" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H123" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I123" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J123" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" t="s">
-        <v>50</v>
+      <c r="A124" s="3">
+        <v>46150</v>
       </c>
       <c r="B124" t="s">
-        <v>178</v>
+        <v>105</v>
       </c>
       <c r="C124" t="s">
-        <v>333</v>
+        <v>260</v>
       </c>
       <c r="D124">
         <v>265000</v>
@@ -5005,27 +4831,27 @@
         <v>392</v>
       </c>
       <c r="G124" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H124" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I124" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="J124" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" t="s">
-        <v>50</v>
+      <c r="A125" s="3">
+        <v>46150</v>
       </c>
       <c r="B125" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="C125" t="s">
-        <v>334</v>
+        <v>261</v>
       </c>
       <c r="D125">
         <v>990000</v>
@@ -5034,27 +4860,27 @@
         <v>393</v>
       </c>
       <c r="G125" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H125" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I125" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J125" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="126" spans="1:10">
-      <c r="A126" t="s">
-        <v>50</v>
+      <c r="A126" s="3">
+        <v>46150</v>
       </c>
       <c r="B126" t="s">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="C126" t="s">
-        <v>265</v>
+        <v>192</v>
       </c>
       <c r="E126">
         <v>815</v>
@@ -5064,14 +4890,14 @@
       </c>
     </row>
     <row r="127" spans="1:10">
-      <c r="A127" t="s">
-        <v>50</v>
+      <c r="A127" s="3">
+        <v>46150</v>
       </c>
       <c r="B127" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="C127" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D127">
         <v>2160000</v>
@@ -5080,27 +4906,27 @@
         <v>395</v>
       </c>
       <c r="G127" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H127" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I127" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J127" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="A128" t="s">
-        <v>51</v>
+      <c r="A128" s="3">
+        <v>46150</v>
       </c>
       <c r="B128" t="s">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="C128" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="D128">
         <v>2370000</v>
@@ -5109,27 +4935,27 @@
         <v>396</v>
       </c>
       <c r="G128" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H128" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I128" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J128" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" t="s">
-        <v>51</v>
+      <c r="A129" s="3">
+        <v>46150</v>
       </c>
       <c r="B129" t="s">
-        <v>183</v>
+        <v>110</v>
       </c>
       <c r="C129" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E129">
         <v>4972</v>
@@ -5138,38 +4964,41 @@
         <v>397</v>
       </c>
       <c r="G129" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H129" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I129" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J129" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="130" spans="1:10">
+      <c r="A130" s="3">
+        <v>46150</v>
+      </c>
       <c r="B130" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C130" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F130">
         <v>398</v>
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" t="s">
-        <v>51</v>
+      <c r="A131" s="3">
+        <v>46150</v>
       </c>
       <c r="B131" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="C131" t="s">
-        <v>335</v>
+        <v>262</v>
       </c>
       <c r="D131">
         <v>61779000</v>
@@ -5178,27 +5007,27 @@
         <v>399</v>
       </c>
       <c r="G131" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H131" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="I131" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J131" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="132" spans="1:10">
-      <c r="A132" t="s">
-        <v>51</v>
+      <c r="A132" s="3">
+        <v>46150</v>
       </c>
       <c r="B132" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C132" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D132">
         <v>3600000</v>
@@ -5207,27 +5036,27 @@
         <v>400</v>
       </c>
       <c r="G132" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H132" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I132" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J132" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" t="s">
-        <v>52</v>
+      <c r="A133" s="3">
+        <v>46150</v>
       </c>
       <c r="B133" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="C133" t="s">
-        <v>336</v>
+        <v>263</v>
       </c>
       <c r="D133">
         <v>2130000</v>
@@ -5236,27 +5065,27 @@
         <v>401</v>
       </c>
       <c r="G133" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H133" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I133" t="s">
-        <v>414</v>
+        <v>341</v>
       </c>
       <c r="J133" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" t="s">
-        <v>52</v>
+      <c r="A134" s="3">
+        <v>46150</v>
       </c>
       <c r="B134" t="s">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="C134" t="s">
-        <v>332</v>
+        <v>259</v>
       </c>
       <c r="D134">
         <v>996000</v>
@@ -5265,27 +5094,27 @@
         <v>402</v>
       </c>
       <c r="G134" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H134" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I134" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="J134" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="A135" t="s">
-        <v>52</v>
+      <c r="A135" s="3">
+        <v>46150</v>
       </c>
       <c r="B135" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="C135" t="s">
-        <v>314</v>
+        <v>241</v>
       </c>
       <c r="D135">
         <v>2370000</v>
@@ -5294,27 +5123,27 @@
         <v>403</v>
       </c>
       <c r="G135" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H135" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I135" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J135" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="136" spans="1:10">
-      <c r="A136" t="s">
-        <v>53</v>
+      <c r="A136" s="3">
+        <v>46150</v>
       </c>
       <c r="B136" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="C136" t="s">
-        <v>337</v>
+        <v>264</v>
       </c>
       <c r="D136">
         <v>10990000</v>
@@ -5323,27 +5152,27 @@
         <v>404</v>
       </c>
       <c r="G136" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H136" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I136" t="s">
-        <v>415</v>
+        <v>342</v>
       </c>
       <c r="J136" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="137" spans="1:10">
-      <c r="A137" t="s">
-        <v>53</v>
+      <c r="A137" s="3">
+        <v>46150</v>
       </c>
       <c r="B137" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="C137" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D137">
         <v>8640000</v>
@@ -5352,27 +5181,27 @@
         <v>405</v>
       </c>
       <c r="G137" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H137" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="I137" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J137" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" t="s">
-        <v>53</v>
+      <c r="A138" s="3">
+        <v>46150</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="C138" t="s">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="D138">
         <v>498000</v>
@@ -5381,27 +5210,27 @@
         <v>406</v>
       </c>
       <c r="G138" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H138" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I138" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="J138" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" t="s">
-        <v>53</v>
+      <c r="A139" s="3">
+        <v>46150</v>
       </c>
       <c r="B139" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="C139" t="s">
-        <v>338</v>
+        <v>265</v>
       </c>
       <c r="D139">
         <v>200000</v>
@@ -5410,27 +5239,27 @@
         <v>407</v>
       </c>
       <c r="G139" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H139" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="I139" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J139" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" t="s">
-        <v>53</v>
+      <c r="A140" s="3">
+        <v>46150</v>
       </c>
       <c r="B140" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="C140" t="s">
-        <v>308</v>
+        <v>235</v>
       </c>
       <c r="D140">
         <v>1080000</v>
@@ -5439,27 +5268,27 @@
         <v>408</v>
       </c>
       <c r="G140" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H140" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I140" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J140" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" t="s">
-        <v>53</v>
+      <c r="A141" s="3">
+        <v>46150</v>
       </c>
       <c r="B141" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
       <c r="C141" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="D141">
         <v>1130000</v>
@@ -5468,27 +5297,27 @@
         <v>409</v>
       </c>
       <c r="G141" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H141" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I141" t="s">
-        <v>416</v>
+        <v>343</v>
       </c>
       <c r="J141" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="142" spans="1:10">
-      <c r="A142" t="s">
-        <v>54</v>
+      <c r="A142" s="3">
+        <v>46150</v>
       </c>
       <c r="B142" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="C142" t="s">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="D142">
         <v>790000</v>
@@ -5497,38 +5326,41 @@
         <v>410</v>
       </c>
       <c r="G142" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H142" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I142" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J142" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="143" spans="1:10">
+      <c r="A143" s="3">
+        <v>46150</v>
+      </c>
       <c r="B143" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C143" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F143">
         <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" t="s">
-        <v>55</v>
+      <c r="A144" s="3">
+        <v>46150</v>
       </c>
       <c r="B144" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="C144" t="s">
-        <v>339</v>
+        <v>266</v>
       </c>
       <c r="D144">
         <v>1500000</v>
@@ -5537,27 +5369,27 @@
         <v>412</v>
       </c>
       <c r="G144" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H144" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I144" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J144" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" t="s">
-        <v>55</v>
+      <c r="A145" s="3">
+        <v>46150</v>
       </c>
       <c r="B145" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
       <c r="C145" t="s">
-        <v>308</v>
+        <v>235</v>
       </c>
       <c r="D145">
         <v>1440000</v>
@@ -5566,27 +5398,27 @@
         <v>413</v>
       </c>
       <c r="G145" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H145" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I145" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J145" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" t="s">
-        <v>56</v>
+      <c r="A146" s="3">
+        <v>46150</v>
       </c>
       <c r="B146" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="C146" t="s">
-        <v>340</v>
+        <v>267</v>
       </c>
       <c r="D146">
         <v>775000</v>
@@ -5595,27 +5427,27 @@
         <v>414</v>
       </c>
       <c r="G146" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H146" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I146" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J146" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="147" spans="1:10">
-      <c r="A147" t="s">
-        <v>56</v>
+      <c r="A147" s="3">
+        <v>46150</v>
       </c>
       <c r="B147" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="C147" t="s">
-        <v>341</v>
+        <v>268</v>
       </c>
       <c r="D147">
         <v>545000</v>
@@ -5624,38 +5456,41 @@
         <v>415</v>
       </c>
       <c r="G147" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H147" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I147" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J147" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="148" spans="1:10">
+      <c r="A148" s="3">
+        <v>46150</v>
+      </c>
       <c r="B148" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C148" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F148">
         <v>416</v>
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" t="s">
-        <v>56</v>
+      <c r="A149" s="3">
+        <v>46150</v>
       </c>
       <c r="B149" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="C149" t="s">
-        <v>342</v>
+        <v>269</v>
       </c>
       <c r="D149">
         <v>56050000</v>
@@ -5664,27 +5499,27 @@
         <v>417</v>
       </c>
       <c r="G149" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H149" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="I149" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J149" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" t="s">
-        <v>57</v>
+      <c r="A150" s="3">
+        <v>46150</v>
       </c>
       <c r="B150" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="C150" t="s">
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="D150">
         <v>12000000</v>
@@ -5693,27 +5528,27 @@
         <v>418</v>
       </c>
       <c r="G150" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H150" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I150" t="s">
-        <v>417</v>
+        <v>344</v>
       </c>
       <c r="J150" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" t="s">
-        <v>58</v>
+      <c r="A151" s="3">
+        <v>46150</v>
       </c>
       <c r="B151" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="C151" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="D151">
         <v>3160000</v>
@@ -5722,27 +5557,27 @@
         <v>419</v>
       </c>
       <c r="G151" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H151" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I151" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J151" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" t="s">
-        <v>58</v>
+      <c r="A152" s="3">
+        <v>46150</v>
       </c>
       <c r="B152" t="s">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="D152">
         <v>5292000</v>
@@ -5751,27 +5586,27 @@
         <v>420</v>
       </c>
       <c r="G152" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H152" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I152" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J152" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" t="s">
-        <v>58</v>
+      <c r="A153" s="3">
+        <v>46150</v>
       </c>
       <c r="B153" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="C153" t="s">
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="D153">
         <v>50500000</v>
@@ -5780,27 +5615,27 @@
         <v>421</v>
       </c>
       <c r="G153" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H153" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I153" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J153" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" t="s">
-        <v>59</v>
+      <c r="A154" s="3">
+        <v>46150</v>
       </c>
       <c r="B154" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="C154" t="s">
-        <v>345</v>
+        <v>272</v>
       </c>
       <c r="D154">
         <v>5000000</v>
@@ -5809,27 +5644,27 @@
         <v>422</v>
       </c>
       <c r="G154" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H154" t="s">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="I154" t="s">
-        <v>418</v>
+        <v>345</v>
       </c>
       <c r="J154" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" t="s">
-        <v>60</v>
+      <c r="A155" s="3">
+        <v>46150</v>
       </c>
       <c r="B155" t="s">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="C155" t="s">
-        <v>335</v>
+        <v>262</v>
       </c>
       <c r="D155">
         <v>65300000</v>
@@ -5838,27 +5673,27 @@
         <v>423</v>
       </c>
       <c r="G155" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H155" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="I155" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J155" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="156" spans="1:10">
-      <c r="A156" t="s">
-        <v>60</v>
+      <c r="A156" s="3">
+        <v>46150</v>
       </c>
       <c r="B156" t="s">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="C156" t="s">
-        <v>341</v>
+        <v>268</v>
       </c>
       <c r="D156">
         <v>1090000</v>
@@ -5867,27 +5702,27 @@
         <v>424</v>
       </c>
       <c r="G156" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H156" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I156" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J156" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="157" spans="1:10">
-      <c r="A157" t="s">
-        <v>60</v>
+      <c r="A157" s="3">
+        <v>46150</v>
       </c>
       <c r="B157" t="s">
-        <v>202</v>
+        <v>129</v>
       </c>
       <c r="C157" t="s">
-        <v>308</v>
+        <v>235</v>
       </c>
       <c r="D157">
         <v>1080000</v>
@@ -5896,38 +5731,41 @@
         <v>425</v>
       </c>
       <c r="G157" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H157" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I157" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J157" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="158" spans="1:10">
+      <c r="A158" s="3">
+        <v>46150</v>
+      </c>
       <c r="B158" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C158" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F158">
         <v>426</v>
       </c>
     </row>
     <row r="159" spans="1:10">
-      <c r="A159" t="s">
-        <v>60</v>
+      <c r="A159" s="3">
+        <v>46150</v>
       </c>
       <c r="B159" t="s">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="C159" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="D159">
         <v>5960500</v>
@@ -5936,27 +5774,27 @@
         <v>427</v>
       </c>
       <c r="G159" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H159" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I159" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J159" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="160" spans="1:10">
-      <c r="A160" t="s">
-        <v>61</v>
+      <c r="A160" s="3">
+        <v>46150</v>
       </c>
       <c r="B160" t="s">
-        <v>204</v>
+        <v>131</v>
       </c>
       <c r="C160" t="s">
-        <v>346</v>
+        <v>273</v>
       </c>
       <c r="D160">
         <v>67290000</v>
@@ -5965,27 +5803,27 @@
         <v>428</v>
       </c>
       <c r="G160" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H160" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="I160" t="s">
-        <v>419</v>
+        <v>346</v>
       </c>
       <c r="J160" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="161" spans="1:10">
-      <c r="A161" t="s">
-        <v>61</v>
+      <c r="A161" s="3">
+        <v>46150</v>
       </c>
       <c r="B161" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="C161" t="s">
-        <v>347</v>
+        <v>274</v>
       </c>
       <c r="D161">
         <v>4740000</v>
@@ -5994,27 +5832,27 @@
         <v>429</v>
       </c>
       <c r="G161" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H161" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I161" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J161" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="162" spans="1:10">
-      <c r="A162" t="s">
-        <v>61</v>
+      <c r="A162" s="3">
+        <v>46150</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="C162" t="s">
-        <v>341</v>
+        <v>268</v>
       </c>
       <c r="D162">
         <v>1090000</v>
@@ -6023,27 +5861,27 @@
         <v>430</v>
       </c>
       <c r="G162" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H162" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I162" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J162" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="163" spans="1:10">
-      <c r="A163" t="s">
-        <v>61</v>
+      <c r="A163" s="3">
+        <v>46150</v>
       </c>
       <c r="B163" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="C163" t="s">
-        <v>348</v>
+        <v>275</v>
       </c>
       <c r="D163">
         <v>53150000</v>
@@ -6052,27 +5890,27 @@
         <v>431</v>
       </c>
       <c r="G163" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H163" t="s">
-        <v>386</v>
+        <v>313</v>
       </c>
       <c r="I163" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J163" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="164" spans="1:10">
-      <c r="A164" t="s">
-        <v>61</v>
+      <c r="A164" s="3">
+        <v>46150</v>
       </c>
       <c r="B164" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C164" t="s">
-        <v>349</v>
+        <v>276</v>
       </c>
       <c r="D164">
         <v>220000</v>
@@ -6081,27 +5919,27 @@
         <v>432</v>
       </c>
       <c r="G164" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H164" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I164" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J164" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="165" spans="1:10">
-      <c r="A165" t="s">
-        <v>61</v>
+      <c r="A165" s="3">
+        <v>46150</v>
       </c>
       <c r="B165" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="C165" t="s">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D165">
         <v>590000</v>
@@ -6110,27 +5948,27 @@
         <v>433</v>
       </c>
       <c r="G165" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H165" t="s">
-        <v>387</v>
+        <v>314</v>
       </c>
       <c r="I165" t="s">
-        <v>420</v>
+        <v>347</v>
       </c>
       <c r="J165" t="s">
-        <v>433</v>
+        <v>360</v>
       </c>
     </row>
     <row r="166" spans="1:10">
-      <c r="A166" t="s">
-        <v>62</v>
+      <c r="A166" s="3">
+        <v>46150</v>
       </c>
       <c r="B166" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="C166" t="s">
-        <v>276</v>
+        <v>203</v>
       </c>
       <c r="D166">
         <v>939000</v>
@@ -6139,27 +5977,27 @@
         <v>434</v>
       </c>
       <c r="G166" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H166" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I166" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J166" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="167" spans="1:10">
-      <c r="A167" t="s">
-        <v>62</v>
+      <c r="A167" s="3">
+        <v>46150</v>
       </c>
       <c r="B167" t="s">
-        <v>208</v>
+        <v>135</v>
       </c>
       <c r="C167" t="s">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="D167">
         <v>1970000</v>
@@ -6168,27 +6006,27 @@
         <v>435</v>
       </c>
       <c r="G167" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H167" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I167" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J167" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="168" spans="1:10">
-      <c r="A168" t="s">
-        <v>62</v>
+      <c r="A168" s="3">
+        <v>46150</v>
       </c>
       <c r="B168" t="s">
-        <v>209</v>
+        <v>136</v>
       </c>
       <c r="C168" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D168">
         <v>7560000</v>
@@ -6197,27 +6035,27 @@
         <v>436</v>
       </c>
       <c r="G168" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H168" t="s">
-        <v>386</v>
+        <v>313</v>
       </c>
       <c r="I168" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J168" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="169" spans="1:10">
-      <c r="A169" t="s">
-        <v>62</v>
+      <c r="A169" s="3">
+        <v>46150</v>
       </c>
       <c r="B169" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="C169" t="s">
-        <v>351</v>
+        <v>278</v>
       </c>
       <c r="D169">
         <v>6590000</v>
@@ -6226,38 +6064,41 @@
         <v>437</v>
       </c>
       <c r="G169" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H169" t="s">
-        <v>387</v>
+        <v>314</v>
       </c>
       <c r="I169" t="s">
-        <v>402</v>
+        <v>329</v>
       </c>
       <c r="J169" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="170" spans="1:10">
+      <c r="A170" s="3">
+        <v>46150</v>
+      </c>
       <c r="B170" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C170" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F170">
         <v>438</v>
       </c>
     </row>
     <row r="171" spans="1:10">
-      <c r="A171" t="s">
-        <v>63</v>
+      <c r="A171" s="3">
+        <v>46150</v>
       </c>
       <c r="B171" t="s">
-        <v>210</v>
+        <v>137</v>
       </c>
       <c r="C171" t="s">
-        <v>352</v>
+        <v>279</v>
       </c>
       <c r="D171">
         <v>25000000</v>
@@ -6266,32 +6107,35 @@
         <v>439</v>
       </c>
       <c r="G171" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H171" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
     </row>
     <row r="172" spans="1:10">
+      <c r="A172" s="3">
+        <v>46150</v>
+      </c>
       <c r="B172" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C172" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F172">
         <v>440</v>
       </c>
     </row>
     <row r="173" spans="1:10">
-      <c r="A173" t="s">
-        <v>63</v>
+      <c r="A173" s="3">
+        <v>46150</v>
       </c>
       <c r="B173" t="s">
-        <v>211</v>
+        <v>138</v>
       </c>
       <c r="C173" t="s">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="D173">
         <v>985000</v>
@@ -6300,38 +6144,41 @@
         <v>441</v>
       </c>
       <c r="G173" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H173" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I173" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J173" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="174" spans="1:10">
+      <c r="A174" s="3">
+        <v>46150</v>
+      </c>
       <c r="B174" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C174" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F174">
         <v>442</v>
       </c>
     </row>
     <row r="175" spans="1:10">
-      <c r="A175" t="s">
-        <v>64</v>
+      <c r="A175" s="3">
+        <v>46150</v>
       </c>
       <c r="B175" t="s">
-        <v>212</v>
+        <v>139</v>
       </c>
       <c r="C175" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="D175">
         <v>4800000</v>
@@ -6340,27 +6187,27 @@
         <v>443</v>
       </c>
       <c r="G175" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H175" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I175" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J175" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="176" spans="1:10">
-      <c r="A176" t="s">
-        <v>64</v>
+      <c r="A176" s="3">
+        <v>46150</v>
       </c>
       <c r="B176" t="s">
-        <v>213</v>
+        <v>140</v>
       </c>
       <c r="C176" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D176">
         <v>1440000</v>
@@ -6369,27 +6216,27 @@
         <v>444</v>
       </c>
       <c r="G176" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H176" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I176" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J176" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="177" spans="1:10">
-      <c r="A177" t="s">
-        <v>65</v>
+      <c r="A177" s="3">
+        <v>46150</v>
       </c>
       <c r="B177" t="s">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="C177" t="s">
-        <v>354</v>
+        <v>281</v>
       </c>
       <c r="D177">
         <v>990000</v>
@@ -6398,27 +6245,27 @@
         <v>445</v>
       </c>
       <c r="G177" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H177" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I177" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J177" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="178" spans="1:10">
-      <c r="A178" t="s">
-        <v>65</v>
+      <c r="A178" s="3">
+        <v>46150</v>
       </c>
       <c r="B178" t="s">
+        <v>142</v>
+      </c>
+      <c r="C178" t="s">
         <v>215</v>
-      </c>
-      <c r="C178" t="s">
-        <v>288</v>
       </c>
       <c r="D178">
         <v>2370000</v>
@@ -6427,27 +6274,27 @@
         <v>446</v>
       </c>
       <c r="G178" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H178" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I178" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J178" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="179" spans="1:10">
-      <c r="A179" t="s">
-        <v>66</v>
+      <c r="A179" s="3">
+        <v>46150</v>
       </c>
       <c r="B179" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="C179" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="D179">
         <v>2957500</v>
@@ -6456,27 +6303,27 @@
         <v>447</v>
       </c>
       <c r="G179" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H179" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I179" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J179" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="180" spans="1:10">
-      <c r="A180" t="s">
-        <v>66</v>
+      <c r="A180" s="3">
+        <v>46150</v>
       </c>
       <c r="B180" t="s">
-        <v>217</v>
+        <v>144</v>
       </c>
       <c r="C180" t="s">
-        <v>355</v>
+        <v>282</v>
       </c>
       <c r="D180">
         <v>1960000</v>
@@ -6485,27 +6332,27 @@
         <v>448</v>
       </c>
       <c r="G180" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H180" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I180" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J180" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="181" spans="1:10">
-      <c r="A181" t="s">
-        <v>66</v>
+      <c r="A181" s="3">
+        <v>46150</v>
       </c>
       <c r="B181" t="s">
-        <v>218</v>
+        <v>145</v>
       </c>
       <c r="C181" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E181">
         <v>1808</v>
@@ -6514,27 +6361,27 @@
         <v>449</v>
       </c>
       <c r="G181" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H181" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I181" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J181" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="182" spans="1:10">
-      <c r="A182" t="s">
-        <v>66</v>
+      <c r="A182" s="3">
+        <v>46150</v>
       </c>
       <c r="B182" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="C182" t="s">
-        <v>356</v>
+        <v>283</v>
       </c>
       <c r="D182">
         <v>550000</v>
@@ -6543,27 +6390,27 @@
         <v>450</v>
       </c>
       <c r="G182" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H182" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I182" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J182" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="183" spans="1:10">
-      <c r="A183" t="s">
-        <v>66</v>
+      <c r="A183" s="3">
+        <v>46150</v>
       </c>
       <c r="B183" t="s">
-        <v>219</v>
+        <v>146</v>
       </c>
       <c r="C183" t="s">
-        <v>357</v>
+        <v>284</v>
       </c>
       <c r="D183">
         <v>6600000</v>
@@ -6572,27 +6419,27 @@
         <v>451</v>
       </c>
       <c r="G183" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H183" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I183" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J183" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="184" spans="1:10">
-      <c r="A184" t="s">
-        <v>67</v>
+      <c r="A184" s="3">
+        <v>46150</v>
       </c>
       <c r="B184" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="C184" t="s">
-        <v>358</v>
+        <v>285</v>
       </c>
       <c r="D184">
         <v>550000</v>
@@ -6601,27 +6448,27 @@
         <v>452</v>
       </c>
       <c r="G184" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H184" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I184" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J184" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="185" spans="1:10">
-      <c r="A185" t="s">
-        <v>67</v>
+      <c r="A185" s="3">
+        <v>46150</v>
       </c>
       <c r="B185" t="s">
-        <v>220</v>
+        <v>147</v>
       </c>
       <c r="C185" t="s">
-        <v>338</v>
+        <v>265</v>
       </c>
       <c r="D185">
         <v>220000</v>
@@ -6630,27 +6477,27 @@
         <v>453</v>
       </c>
       <c r="G185" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H185" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I185" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J185" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="186" spans="1:10">
-      <c r="A186" t="s">
-        <v>67</v>
+      <c r="A186" s="3">
+        <v>46150</v>
       </c>
       <c r="B186" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
       <c r="C186" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="D186">
         <v>5920000</v>
@@ -6659,27 +6506,27 @@
         <v>454</v>
       </c>
       <c r="G186" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H186" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I186" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J186" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="187" spans="1:10">
-      <c r="A187" t="s">
-        <v>67</v>
+      <c r="A187" s="3">
+        <v>46150</v>
       </c>
       <c r="B187" t="s">
-        <v>222</v>
+        <v>149</v>
       </c>
       <c r="C187" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="D187">
         <v>540000</v>
@@ -6688,27 +6535,27 @@
         <v>455</v>
       </c>
       <c r="G187" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H187" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I187" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J187" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="188" spans="1:10">
-      <c r="A188" t="s">
-        <v>67</v>
+      <c r="A188" s="3">
+        <v>46150</v>
       </c>
       <c r="B188" t="s">
-        <v>223</v>
+        <v>150</v>
       </c>
       <c r="C188" t="s">
-        <v>352</v>
+        <v>279</v>
       </c>
       <c r="D188">
         <v>25500000</v>
@@ -6717,21 +6564,21 @@
         <v>456</v>
       </c>
       <c r="G188" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H188" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
     </row>
     <row r="189" spans="1:10">
-      <c r="A189" t="s">
-        <v>68</v>
+      <c r="A189" s="3">
+        <v>46150</v>
       </c>
       <c r="B189" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="C189" t="s">
-        <v>359</v>
+        <v>286</v>
       </c>
       <c r="D189">
         <v>990000</v>
@@ -6740,27 +6587,27 @@
         <v>457</v>
       </c>
       <c r="G189" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H189" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I189" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J189" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="190" spans="1:10">
-      <c r="A190" t="s">
-        <v>68</v>
+      <c r="A190" s="3">
+        <v>46150</v>
       </c>
       <c r="B190" t="s">
-        <v>224</v>
+        <v>151</v>
       </c>
       <c r="C190" t="s">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="D190">
         <v>1650000</v>
@@ -6769,27 +6616,27 @@
         <v>458</v>
       </c>
       <c r="G190" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H190" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I190" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J190" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="191" spans="1:10">
-      <c r="A191" t="s">
-        <v>68</v>
+      <c r="A191" s="3">
+        <v>46150</v>
       </c>
       <c r="B191" t="s">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="C191" t="s">
-        <v>356</v>
+        <v>283</v>
       </c>
       <c r="D191">
         <v>2200000</v>
@@ -6798,27 +6645,27 @@
         <v>459</v>
       </c>
       <c r="G191" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H191" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I191" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J191" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="192" spans="1:10">
-      <c r="A192" t="s">
-        <v>68</v>
+      <c r="A192" s="3">
+        <v>46150</v>
       </c>
       <c r="B192" t="s">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="C192" t="s">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="D192">
         <v>1580000</v>
@@ -6827,27 +6674,27 @@
         <v>460</v>
       </c>
       <c r="G192" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H192" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I192" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J192" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="193" spans="1:10">
-      <c r="A193" t="s">
-        <v>69</v>
+      <c r="A193" s="3">
+        <v>46150</v>
       </c>
       <c r="B193" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="C193" t="s">
-        <v>362</v>
+        <v>289</v>
       </c>
       <c r="D193">
         <v>50500000</v>
@@ -6856,27 +6703,27 @@
         <v>461</v>
       </c>
       <c r="G193" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H193" t="s">
-        <v>383</v>
+        <v>310</v>
       </c>
       <c r="I193" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J193" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="194" spans="1:10">
-      <c r="A194" t="s">
-        <v>69</v>
+      <c r="A194" s="3">
+        <v>46150</v>
       </c>
       <c r="B194" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="C194" t="s">
-        <v>363</v>
+        <v>290</v>
       </c>
       <c r="D194">
         <v>199000</v>
@@ -6885,27 +6732,27 @@
         <v>462</v>
       </c>
       <c r="G194" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H194" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I194" t="s">
-        <v>399</v>
+        <v>326</v>
       </c>
       <c r="J194" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="195" spans="1:10">
-      <c r="A195" t="s">
-        <v>69</v>
+      <c r="A195" s="3">
+        <v>46150</v>
       </c>
       <c r="B195" t="s">
-        <v>227</v>
+        <v>154</v>
       </c>
       <c r="C195" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="D195">
         <v>1580000</v>
@@ -6914,27 +6761,27 @@
         <v>463</v>
       </c>
       <c r="G195" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H195" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I195" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J195" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="196" spans="1:10">
-      <c r="A196" t="s">
-        <v>69</v>
+      <c r="A196" s="3">
+        <v>46150</v>
       </c>
       <c r="B196" t="s">
-        <v>228</v>
+        <v>155</v>
       </c>
       <c r="C196" t="s">
-        <v>364</v>
+        <v>291</v>
       </c>
       <c r="D196">
         <v>419000</v>
@@ -6943,27 +6790,27 @@
         <v>464</v>
       </c>
       <c r="G196" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H196" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I196" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J196" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="197" spans="1:10">
-      <c r="A197" t="s">
-        <v>69</v>
+      <c r="A197" s="3">
+        <v>46150</v>
       </c>
       <c r="B197" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="C197" t="s">
-        <v>365</v>
+        <v>292</v>
       </c>
       <c r="D197">
         <v>8980000</v>
@@ -6972,27 +6819,27 @@
         <v>465</v>
       </c>
       <c r="G197" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H197" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I197" t="s">
-        <v>421</v>
+        <v>348</v>
       </c>
       <c r="J197" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="198" spans="1:10">
-      <c r="A198" t="s">
-        <v>69</v>
+      <c r="A198" s="3">
+        <v>46150</v>
       </c>
       <c r="B198" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="C198" t="s">
-        <v>366</v>
+        <v>293</v>
       </c>
       <c r="D198">
         <v>2890000</v>
@@ -7001,27 +6848,27 @@
         <v>466</v>
       </c>
       <c r="G198" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H198" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I198" t="s">
-        <v>396</v>
+        <v>323</v>
       </c>
       <c r="J198" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="199" spans="1:10">
-      <c r="A199" t="s">
-        <v>69</v>
+      <c r="A199" s="3">
+        <v>46150</v>
       </c>
       <c r="B199" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="C199" t="s">
-        <v>367</v>
+        <v>294</v>
       </c>
       <c r="D199">
         <v>3120000</v>
@@ -7030,27 +6877,27 @@
         <v>467</v>
       </c>
       <c r="G199" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H199" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I199" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J199" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="200" spans="1:10">
-      <c r="A200" t="s">
-        <v>70</v>
+      <c r="A200" s="3">
+        <v>46150</v>
       </c>
       <c r="B200" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C200" t="s">
-        <v>368</v>
+        <v>295</v>
       </c>
       <c r="D200">
         <v>1590000</v>
@@ -7059,38 +6906,41 @@
         <v>468</v>
       </c>
       <c r="G200" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H200" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I200" t="s">
-        <v>411</v>
+        <v>338</v>
       </c>
       <c r="J200" t="s">
-        <v>431</v>
+        <v>358</v>
       </c>
     </row>
     <row r="201" spans="1:10">
+      <c r="A201" s="3">
+        <v>46150</v>
+      </c>
       <c r="B201" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C201" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F201">
         <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:10">
-      <c r="A202" t="s">
-        <v>70</v>
+      <c r="A202" s="3">
+        <v>46150</v>
       </c>
       <c r="B202" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="D202">
         <v>14122000</v>
@@ -7099,27 +6949,27 @@
         <v>470</v>
       </c>
       <c r="G202" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H202" t="s">
-        <v>386</v>
+        <v>313</v>
       </c>
       <c r="I202" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J202" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="203" spans="1:10">
-      <c r="A203" t="s">
-        <v>71</v>
+      <c r="A203" s="3">
+        <v>46150</v>
       </c>
       <c r="B203" t="s">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="C203" t="s">
-        <v>369</v>
+        <v>296</v>
       </c>
       <c r="E203">
         <v>1400</v>
@@ -7129,25 +6979,28 @@
       </c>
     </row>
     <row r="204" spans="1:10">
+      <c r="A204" s="3">
+        <v>46150</v>
+      </c>
       <c r="B204" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C204" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F204">
         <v>472</v>
       </c>
     </row>
     <row r="205" spans="1:10">
-      <c r="A205" t="s">
-        <v>71</v>
+      <c r="A205" s="3">
+        <v>46150</v>
       </c>
       <c r="B205" t="s">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="C205" t="s">
-        <v>333</v>
+        <v>260</v>
       </c>
       <c r="D205">
         <v>580000</v>
@@ -7156,27 +7009,27 @@
         <v>473</v>
       </c>
       <c r="G205" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H205" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I205" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="J205" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="206" spans="1:10">
-      <c r="A206" t="s">
-        <v>71</v>
+      <c r="A206" s="3">
+        <v>46150</v>
       </c>
       <c r="B206" t="s">
-        <v>234</v>
+        <v>161</v>
       </c>
       <c r="C206" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D206">
         <v>2880000</v>
@@ -7185,27 +7038,27 @@
         <v>474</v>
       </c>
       <c r="G206" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H206" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I206" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J206" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="207" spans="1:10">
-      <c r="A207" t="s">
-        <v>71</v>
+      <c r="A207" s="3">
+        <v>46150</v>
       </c>
       <c r="B207" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
       <c r="C207" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="D207">
         <v>1130000</v>
@@ -7214,27 +7067,27 @@
         <v>475</v>
       </c>
       <c r="G207" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H207" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I207" t="s">
-        <v>416</v>
+        <v>343</v>
       </c>
       <c r="J207" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="208" spans="1:10">
-      <c r="A208" t="s">
-        <v>71</v>
+      <c r="A208" s="3">
+        <v>46150</v>
       </c>
       <c r="B208" t="s">
-        <v>235</v>
+        <v>162</v>
       </c>
       <c r="C208" t="s">
-        <v>370</v>
+        <v>297</v>
       </c>
       <c r="D208">
         <v>50500000</v>
@@ -7243,27 +7096,27 @@
         <v>476</v>
       </c>
       <c r="G208" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H208" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I208" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J208" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="209" spans="1:10">
-      <c r="A209" t="s">
-        <v>72</v>
+      <c r="A209" s="3">
+        <v>46150</v>
       </c>
       <c r="B209" t="s">
-        <v>236</v>
+        <v>163</v>
       </c>
       <c r="C209" t="s">
-        <v>371</v>
+        <v>298</v>
       </c>
       <c r="D209">
         <v>65800000</v>
@@ -7272,27 +7125,27 @@
         <v>477</v>
       </c>
       <c r="G209" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H209" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I209" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="J209" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="210" spans="1:10">
-      <c r="A210" t="s">
-        <v>72</v>
+      <c r="A210" s="3">
+        <v>46150</v>
       </c>
       <c r="B210" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="C210" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="D210">
         <v>1080000</v>
@@ -7301,38 +7154,41 @@
         <v>478</v>
       </c>
       <c r="G210" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H210" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I210" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J210" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="211" spans="1:10">
+      <c r="A211" s="3">
+        <v>46150</v>
+      </c>
       <c r="B211" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C211" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F211">
         <v>479</v>
       </c>
     </row>
     <row r="212" spans="1:10">
-      <c r="A212" t="s">
-        <v>73</v>
+      <c r="A212" s="3">
+        <v>46150</v>
       </c>
       <c r="B212" t="s">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="C212" t="s">
-        <v>267</v>
+        <v>194</v>
       </c>
       <c r="D212">
         <v>1970000</v>
@@ -7341,27 +7197,27 @@
         <v>480</v>
       </c>
       <c r="G212" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H212" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I212" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J212" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="213" spans="1:10">
-      <c r="A213" t="s">
-        <v>73</v>
+      <c r="A213" s="3">
+        <v>46150</v>
       </c>
       <c r="B213" t="s">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="C213" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E213">
         <v>4972</v>
@@ -7370,27 +7226,27 @@
         <v>481</v>
       </c>
       <c r="G213" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H213" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I213" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J213" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="A214" t="s">
-        <v>73</v>
+      <c r="A214" s="3">
+        <v>46150</v>
       </c>
       <c r="B214" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="C214" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="D214">
         <v>2934750</v>
@@ -7399,27 +7255,27 @@
         <v>482</v>
       </c>
       <c r="G214" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H214" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I214" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J214" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" t="s">
-        <v>73</v>
+      <c r="A215" s="3">
+        <v>46150</v>
       </c>
       <c r="B215" t="s">
-        <v>240</v>
+        <v>167</v>
       </c>
       <c r="C215" t="s">
-        <v>296</v>
+        <v>223</v>
       </c>
       <c r="D215">
         <v>395000</v>
@@ -7428,27 +7284,27 @@
         <v>483</v>
       </c>
       <c r="G215" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H215" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I215" t="s">
-        <v>404</v>
+        <v>331</v>
       </c>
       <c r="J215" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="216" spans="1:10">
-      <c r="A216" t="s">
-        <v>74</v>
+      <c r="A216" s="3">
+        <v>46150</v>
       </c>
       <c r="B216" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="C216" t="s">
-        <v>315</v>
+        <v>242</v>
       </c>
       <c r="D216">
         <v>3960000</v>
@@ -7457,38 +7313,41 @@
         <v>484</v>
       </c>
       <c r="G216" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H216" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I216" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J216" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="217" spans="1:10">
+      <c r="A217" s="3">
+        <v>46150</v>
+      </c>
       <c r="B217" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C217" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F217">
         <v>485</v>
       </c>
     </row>
     <row r="218" spans="1:10">
-      <c r="A218" t="s">
-        <v>74</v>
+      <c r="A218" s="3">
+        <v>46150</v>
       </c>
       <c r="B218" t="s">
-        <v>241</v>
+        <v>168</v>
       </c>
       <c r="C218" t="s">
-        <v>372</v>
+        <v>299</v>
       </c>
       <c r="E218">
         <v>14955</v>
@@ -7497,21 +7356,21 @@
         <v>486</v>
       </c>
       <c r="G218" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H218" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
     </row>
     <row r="219" spans="1:10">
-      <c r="A219" t="s">
-        <v>75</v>
+      <c r="A219" s="3">
+        <v>46150</v>
       </c>
       <c r="B219" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="C219" t="s">
-        <v>319</v>
+        <v>246</v>
       </c>
       <c r="D219">
         <v>1000000</v>
@@ -7520,38 +7379,41 @@
         <v>487</v>
       </c>
       <c r="G219" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H219" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I219" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J219" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="220" spans="1:10">
+      <c r="A220" s="3">
+        <v>46150</v>
+      </c>
       <c r="B220" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C220" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F220">
         <v>488</v>
       </c>
     </row>
     <row r="221" spans="1:10">
-      <c r="A221" t="s">
-        <v>75</v>
+      <c r="A221" s="3">
+        <v>46150</v>
       </c>
       <c r="B221" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="C221" t="s">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="D221">
         <v>1580000</v>
@@ -7560,27 +7422,27 @@
         <v>489</v>
       </c>
       <c r="G221" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H221" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I221" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J221" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="222" spans="1:10">
-      <c r="A222" t="s">
-        <v>75</v>
+      <c r="A222" s="3">
+        <v>46150</v>
       </c>
       <c r="B222" t="s">
-        <v>243</v>
+        <v>170</v>
       </c>
       <c r="C222" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="D222">
         <v>1080000</v>
@@ -7589,27 +7451,27 @@
         <v>490</v>
       </c>
       <c r="G222" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H222" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I222" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J222" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="223" spans="1:10">
-      <c r="A223" t="s">
-        <v>75</v>
+      <c r="A223" s="3">
+        <v>46150</v>
       </c>
       <c r="B223" t="s">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="C223" t="s">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D223">
         <v>6480000</v>
@@ -7618,27 +7480,27 @@
         <v>491</v>
       </c>
       <c r="G223" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H223" t="s">
-        <v>386</v>
+        <v>313</v>
       </c>
       <c r="I223" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J223" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="224" spans="1:10">
-      <c r="A224" t="s">
-        <v>75</v>
+      <c r="A224" s="3">
+        <v>46150</v>
       </c>
       <c r="B224" t="s">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="C224" t="s">
-        <v>373</v>
+        <v>300</v>
       </c>
       <c r="D224">
         <v>18890000</v>
@@ -7647,27 +7509,27 @@
         <v>492</v>
       </c>
       <c r="G224" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H224" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I224" t="s">
-        <v>422</v>
+        <v>349</v>
       </c>
       <c r="J224" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="225" spans="1:11">
-      <c r="A225" t="s">
-        <v>76</v>
+      <c r="A225" s="3">
+        <v>46150</v>
       </c>
       <c r="B225" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="C225" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="D225">
         <v>1580000</v>
@@ -7676,27 +7538,27 @@
         <v>493</v>
       </c>
       <c r="G225" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H225" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I225" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J225" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="226" spans="1:11">
-      <c r="A226" t="s">
-        <v>77</v>
+      <c r="A226" s="3">
+        <v>46150</v>
       </c>
       <c r="B226" t="s">
-        <v>246</v>
+        <v>173</v>
       </c>
       <c r="C226" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E226">
         <v>1808</v>
@@ -7705,32 +7567,35 @@
         <v>494</v>
       </c>
       <c r="I226" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J226" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="227" spans="1:11">
+      <c r="A227" s="3">
+        <v>46150</v>
+      </c>
       <c r="B227" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="C227" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F227">
         <v>495</v>
       </c>
     </row>
     <row r="228" spans="1:11">
-      <c r="A228" t="s">
-        <v>78</v>
+      <c r="A228" s="3">
+        <v>46150</v>
       </c>
       <c r="B228" t="s">
-        <v>247</v>
+        <v>174</v>
       </c>
       <c r="C228" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="D228">
         <v>710000</v>
@@ -7739,27 +7604,27 @@
         <v>496</v>
       </c>
       <c r="G228" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H228" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I228" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J228" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="229" spans="1:11">
-      <c r="A229" t="s">
-        <v>78</v>
+      <c r="A229" s="3">
+        <v>46150</v>
       </c>
       <c r="B229" t="s">
-        <v>248</v>
+        <v>175</v>
       </c>
       <c r="C229" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D229">
         <v>3600000</v>
@@ -7768,27 +7633,27 @@
         <v>497</v>
       </c>
       <c r="G229" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H229" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I229" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J229" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="230" spans="1:11">
-      <c r="A230" t="s">
-        <v>79</v>
+      <c r="A230" s="3">
+        <v>46150</v>
       </c>
       <c r="B230" t="s">
-        <v>249</v>
+        <v>176</v>
       </c>
       <c r="C230" t="s">
-        <v>356</v>
+        <v>283</v>
       </c>
       <c r="D230">
         <v>3300000</v>
@@ -7797,27 +7662,27 @@
         <v>498</v>
       </c>
       <c r="G230" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H230" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I230" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="J230" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="231" spans="1:11">
-      <c r="A231" t="s">
-        <v>79</v>
+      <c r="A231" s="3">
+        <v>46150</v>
       </c>
       <c r="B231" t="s">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="C231" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="D231">
         <v>5732000</v>
@@ -7826,27 +7691,27 @@
         <v>499</v>
       </c>
       <c r="G231" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H231" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I231" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J231" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="232" spans="1:11">
-      <c r="A232" t="s">
-        <v>80</v>
+      <c r="A232" s="3">
+        <v>46150</v>
       </c>
       <c r="B232" t="s">
-        <v>251</v>
+        <v>178</v>
       </c>
       <c r="C232" t="s">
-        <v>367</v>
+        <v>294</v>
       </c>
       <c r="D232">
         <v>2350000</v>
@@ -7855,27 +7720,27 @@
         <v>500</v>
       </c>
       <c r="G232" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H232" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I232" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="J232" t="s">
-        <v>430</v>
+        <v>357</v>
       </c>
     </row>
     <row r="233" spans="1:11">
-      <c r="A233" t="s">
-        <v>80</v>
+      <c r="A233" s="3">
+        <v>46150</v>
       </c>
       <c r="B233" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
       <c r="C233" t="s">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="D233">
         <v>1130000</v>
@@ -7884,27 +7749,27 @@
         <v>501</v>
       </c>
       <c r="G233" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H233" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="I233" t="s">
-        <v>416</v>
+        <v>343</v>
       </c>
       <c r="J233" t="s">
-        <v>432</v>
+        <v>359</v>
       </c>
     </row>
     <row r="234" spans="1:11">
-      <c r="A234" t="s">
-        <v>81</v>
+      <c r="A234" s="3">
+        <v>46150</v>
       </c>
       <c r="B234" t="s">
-        <v>252</v>
+        <v>179</v>
       </c>
       <c r="C234" t="s">
-        <v>374</v>
+        <v>301</v>
       </c>
       <c r="D234">
         <v>6480000</v>
@@ -7913,27 +7778,27 @@
         <v>504</v>
       </c>
       <c r="G234" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H234" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="I234" t="s">
-        <v>423</v>
+        <v>350</v>
       </c>
       <c r="J234" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
     </row>
     <row r="235" spans="1:11">
-      <c r="A235" t="s">
-        <v>81</v>
+      <c r="A235" s="3">
+        <v>46150</v>
       </c>
       <c r="B235" t="s">
-        <v>253</v>
+        <v>180</v>
       </c>
       <c r="C235" t="s">
-        <v>306</v>
+        <v>233</v>
       </c>
       <c r="D235">
         <v>17659300</v>
@@ -7942,27 +7807,27 @@
         <v>502</v>
       </c>
       <c r="G235" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H235" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="I235" t="s">
-        <v>424</v>
+        <v>351</v>
       </c>
       <c r="J235" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
     </row>
     <row r="236" spans="1:11">
-      <c r="A236" t="s">
-        <v>82</v>
+      <c r="A236" s="3">
+        <v>46150</v>
       </c>
       <c r="B236" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="C236" t="s">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="D236">
         <v>985000</v>
@@ -7971,24 +7836,24 @@
         <v>505</v>
       </c>
       <c r="G236" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H236" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="J236" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
     </row>
     <row r="237" spans="1:11">
-      <c r="A237" t="s">
-        <v>82</v>
+      <c r="A237" s="3">
+        <v>46150</v>
       </c>
       <c r="B237" t="s">
-        <v>254</v>
+        <v>181</v>
       </c>
       <c r="C237" t="s">
-        <v>314</v>
+        <v>241</v>
       </c>
       <c r="D237">
         <v>1580000</v>
@@ -7997,30 +7862,30 @@
         <v>506</v>
       </c>
       <c r="G237" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H237" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="I237" t="s">
-        <v>425</v>
+        <v>352</v>
       </c>
       <c r="J237" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
       <c r="K237" t="s">
-        <v>435</v>
+        <v>362</v>
       </c>
     </row>
     <row r="238" spans="1:11">
-      <c r="A238" t="s">
-        <v>82</v>
+      <c r="A238" s="3">
+        <v>46150</v>
       </c>
       <c r="B238" t="s">
-        <v>255</v>
+        <v>182</v>
       </c>
       <c r="C238" t="s">
-        <v>375</v>
+        <v>302</v>
       </c>
       <c r="D238">
         <v>50500000</v>
@@ -8029,30 +7894,30 @@
         <v>503</v>
       </c>
       <c r="G238" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H238" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="I238" t="s">
-        <v>426</v>
+        <v>353</v>
       </c>
       <c r="J238" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
       <c r="K238" t="s">
-        <v>436</v>
+        <v>363</v>
       </c>
     </row>
     <row r="239" spans="1:11">
-      <c r="A239" t="s">
-        <v>83</v>
+      <c r="A239" s="3">
+        <v>46150</v>
       </c>
       <c r="B239" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="C239" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="D239">
         <v>7063720</v>
@@ -8061,30 +7926,30 @@
         <v>507</v>
       </c>
       <c r="G239" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H239" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="I239" t="s">
-        <v>427</v>
+        <v>354</v>
       </c>
       <c r="J239" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
       <c r="K239" t="s">
-        <v>437</v>
+        <v>364</v>
       </c>
     </row>
     <row r="240" spans="1:11">
-      <c r="A240" t="s">
-        <v>83</v>
+      <c r="A240" s="3">
+        <v>46150</v>
       </c>
       <c r="B240" t="s">
-        <v>257</v>
+        <v>184</v>
       </c>
       <c r="C240" t="s">
-        <v>273</v>
+        <v>200</v>
       </c>
       <c r="D240">
         <v>990000</v>
@@ -8093,30 +7958,30 @@
         <v>508</v>
       </c>
       <c r="G240" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H240" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="I240" t="s">
-        <v>427</v>
+        <v>354</v>
       </c>
       <c r="J240" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
       <c r="K240" t="s">
-        <v>438</v>
+        <v>365</v>
       </c>
     </row>
     <row r="241" spans="1:11">
-      <c r="A241" t="s">
-        <v>83</v>
+      <c r="A241" s="3">
+        <v>46150</v>
       </c>
       <c r="B241" t="s">
-        <v>258</v>
+        <v>185</v>
       </c>
       <c r="C241" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E241">
         <v>3616</v>
@@ -8125,30 +7990,30 @@
         <v>510</v>
       </c>
       <c r="G241" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H241" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="I241" t="s">
-        <v>428</v>
+        <v>355</v>
       </c>
       <c r="J241" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
       <c r="K241" t="s">
-        <v>439</v>
+        <v>366</v>
       </c>
     </row>
     <row r="242" spans="1:11">
-      <c r="A242" t="s">
-        <v>83</v>
+      <c r="A242" s="3">
+        <v>46150</v>
       </c>
       <c r="B242" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="C242" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="D242">
         <v>1580000</v>
@@ -8157,30 +8022,30 @@
         <v>511</v>
       </c>
       <c r="G242" t="s">
-        <v>379</v>
+        <v>306</v>
       </c>
       <c r="H242" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="I242" t="s">
-        <v>429</v>
+        <v>356</v>
       </c>
       <c r="J242" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
       <c r="K242" t="s">
-        <v>440</v>
+        <v>367</v>
       </c>
     </row>
     <row r="243" spans="1:11">
-      <c r="A243" t="s">
-        <v>83</v>
+      <c r="A243" s="3">
+        <v>46150</v>
       </c>
       <c r="B243" t="s">
-        <v>260</v>
+        <v>187</v>
       </c>
       <c r="C243" t="s">
-        <v>376</v>
+        <v>303</v>
       </c>
       <c r="E243">
         <v>7625</v>
@@ -8189,19 +8054,19 @@
         <v>512</v>
       </c>
       <c r="G243" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="H243" t="s">
-        <v>388</v>
+        <v>315</v>
       </c>
       <c r="I243" t="s">
-        <v>416</v>
+        <v>343</v>
       </c>
       <c r="J243" t="s">
-        <v>434</v>
+        <v>361</v>
       </c>
       <c r="K243" t="s">
-        <v>441</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/VENTAS TOTALES 2026.xlsx
+++ b/VENTAS TOTALES 2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="389">
   <si>
     <t>FECHA</t>
   </si>
@@ -580,19 +580,49 @@
     <t>1 SCG6070SE - G6070 PAGO 50% + HORNO DTF</t>
   </si>
   <si>
+    <t>1  PAGO DEL 50% IMP EPSONG6070 Y HORNO DTF</t>
+  </si>
+  <si>
+    <t>2 TINTA EPSON T53K220 CYAN (F64/F95) - UNITARIO, 2 TINTA EPSON T53K320 MAGENTA (F64/F95) - UNITARIO</t>
+  </si>
+  <si>
+    <t>1 TINTA EPSON T49M2 CYAN (F170/F570) - 140ML, 1 TINTA EPSON T49M1 BLACK (F170/F570) - 140ML, 1 TINTA EPSON T49M4 YELLOW (F170/F570) - 140ML, 1 TINTA EPSON T49M3 MAGENTA (F170/F570) - 140ML</t>
+  </si>
+  <si>
+    <t>1 CAJA F170 DE MANTENIMIENTO</t>
+  </si>
+  <si>
+    <t>1 T46C220 CYAN F63/F94, 1 T46C420 YELLOW F63/F94</t>
+  </si>
+  <si>
+    <t>2 T46C220 CYAN F63/F94</t>
+  </si>
+  <si>
+    <t>1 KIT DE LIMPIEZA DE CABEZAL F22/G60 C13S400216</t>
+  </si>
+  <si>
+    <t>1 T46C220 CYAN F63/F94, 1 T46C120 YHDK F63/F94, 1 T46C320 MAGENTA F63/F94, 1 T46C420 YELLOW F63/F94</t>
+  </si>
+  <si>
+    <t>1 IMPRESORA EPSON F170</t>
+  </si>
+  <si>
+    <t>1 TINTA EPSON T49M2 CYAN (F170/F570) - 140ML</t>
+  </si>
+  <si>
     <t>WIDMER GRAPHIC</t>
   </si>
   <si>
     <t>TECNOTEXTIL E.A.S</t>
   </si>
   <si>
-    <t>JESSI LENS S.R.L</t>
+    <t>GRUPO VARGAS S.R.L</t>
   </si>
   <si>
     <t>LUAN DEPORTES S.A</t>
   </si>
   <si>
-    <t>EPSON ARGENTINA</t>
+    <t>EPSON ARGENTINA S.R.L</t>
   </si>
   <si>
     <t>GRUPO UTEX E.A.S</t>
@@ -625,7 +655,7 @@
     <t>PASCUALA DAVALOS</t>
   </si>
   <si>
-    <t>OSVAL JIMENEZ</t>
+    <t>OSVAL GIMENEZ</t>
   </si>
   <si>
     <t>ROBERTO DUTRA</t>
@@ -649,7 +679,7 @@
     <t>ARNALDO CORONEL</t>
   </si>
   <si>
-    <t>GRUPO VIBER E.A.S</t>
+    <t>GRUPO VIBE E.A.S</t>
   </si>
   <si>
     <t>DAIANA ALBINO</t>
@@ -673,9 +703,6 @@
     <t>JULIO CESAR BENITEZ</t>
   </si>
   <si>
-    <t>JESSY LENS S.R.L</t>
-  </si>
-  <si>
     <t>SPORT LOVERS S.A</t>
   </si>
   <si>
@@ -691,15 +718,9 @@
     <t>MARIO GODOY</t>
   </si>
   <si>
-    <t>BRUPO VARGAS S.R.L</t>
-  </si>
-  <si>
     <t>CARLOS MENDOZA</t>
   </si>
   <si>
-    <t>OSVAL GIMENEZ</t>
-  </si>
-  <si>
     <t>BEATRIZ ORTIZ</t>
   </si>
   <si>
@@ -715,15 +736,9 @@
     <t>ROMINA FIGUEREDO</t>
   </si>
   <si>
-    <t>TEXNOTEXTIL E.A.S</t>
-  </si>
-  <si>
     <t>MARIA VALENZUELA</t>
   </si>
   <si>
-    <t>GRUPO VARGAS S.R.L</t>
-  </si>
-  <si>
     <t>GRACIELA OVIEDO</t>
   </si>
   <si>
@@ -754,9 +769,6 @@
     <t>SERGIO GRECO</t>
   </si>
   <si>
-    <t>EUCLIDES VERA</t>
-  </si>
-  <si>
     <t>EVA PRIETO</t>
   </si>
   <si>
@@ -766,9 +778,6 @@
     <t>SIN NOMBRE</t>
   </si>
   <si>
-    <t>GRUPO VIBE E.A.S</t>
-  </si>
-  <si>
     <t>ISIDRO RUIZ DIAZ</t>
   </si>
   <si>
@@ -823,7 +832,7 @@
     <t>INTER GROUP S.A</t>
   </si>
   <si>
-    <t>MARIO BAEZ</t>
+    <t>MARIO ANDRES BAEZ</t>
   </si>
   <si>
     <t>LILIAN FLORENTIN</t>
@@ -838,12 +847,6 @@
     <t>ANGEL GODOY</t>
   </si>
   <si>
-    <t>ALCIDEZ VALDEZ</t>
-  </si>
-  <si>
-    <t>MARIO ANDRES BAEZ</t>
-  </si>
-  <si>
     <t>ALBERTO RAMIRES</t>
   </si>
   <si>
@@ -856,9 +859,6 @@
     <t>ALEJANDRO HERMOSILLA</t>
   </si>
   <si>
-    <t>GRUPO VARGAS SRL</t>
-  </si>
-  <si>
     <t>LUIS ADORNO</t>
   </si>
   <si>
@@ -880,9 +880,6 @@
     <t>JULIO GONZALES</t>
   </si>
   <si>
-    <t>ANDRES BAEZ</t>
-  </si>
-  <si>
     <t>MARIELA LOPEZ</t>
   </si>
   <si>
@@ -904,9 +901,6 @@
     <t>GABRIEL MELGAREJO</t>
   </si>
   <si>
-    <t>EPSON ARGENTINA SRL</t>
-  </si>
-  <si>
     <t>LUIS CARRILLO</t>
   </si>
   <si>
@@ -928,6 +922,21 @@
     <t>MATIAS FRANCO</t>
   </si>
   <si>
+    <t>ANGEL AGUILAR</t>
+  </si>
+  <si>
+    <t>ROCIO FERREIRA</t>
+  </si>
+  <si>
+    <t>RAUL BENITEZ</t>
+  </si>
+  <si>
+    <t>REC-80106</t>
+  </si>
+  <si>
+    <t>0521</t>
+  </si>
+  <si>
     <t>ALBERTO</t>
   </si>
   <si>
@@ -937,6 +946,9 @@
     <t>MAURO</t>
   </si>
   <si>
+    <t>Administrador SOLPRO</t>
+  </si>
+  <si>
     <t>TRANS</t>
   </si>
   <si>
@@ -1087,6 +1099,27 @@
     <t>SC-120</t>
   </si>
   <si>
+    <t>SC-120, SC-123</t>
+  </si>
+  <si>
+    <t>SC-132, SC-133, SC-134, SC-135</t>
+  </si>
+  <si>
+    <t>SC-140, SC-138</t>
+  </si>
+  <si>
+    <t>SC-140</t>
+  </si>
+  <si>
+    <t>SC-136</t>
+  </si>
+  <si>
+    <t>SC-140, SC-141, SC-139, SC-138</t>
+  </si>
+  <si>
+    <t>SC-132</t>
+  </si>
+  <si>
     <t>INSUMOS</t>
   </si>
   <si>
@@ -1121,6 +1154,33 @@
   </si>
   <si>
     <t>[{"COD_PRODUCTO": "SC-109", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-120", "_CANT_NUM": 2}, {"COD_PRODUCTO": "SC-123", "_CANT_NUM": 2}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-132", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-133", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-134", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-135", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-103", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-140", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-138", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-140", "_CANT_NUM": 2}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-136", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-140", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-141", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-139", "_CANT_NUM": 1}, {"COD_PRODUCTO": "SC-138", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-001", "_CANT_NUM": 1}]</t>
+  </si>
+  <si>
+    <t>[{"COD_PRODUCTO": "SC-132", "_CANT_NUM": 1}]</t>
   </si>
 </sst>
 </file>
@@ -1129,18 +1189,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1156,7 +1208,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1164,31 +1216,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1484,56 +1518,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K243"/>
+  <dimension ref="A1:K254"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>46143</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D2">
         <v>985000</v>
@@ -1542,27 +1576,27 @@
         <v>268</v>
       </c>
       <c r="G2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J2" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>46143</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D3">
         <v>5292000</v>
@@ -1571,27 +1605,27 @@
         <v>269</v>
       </c>
       <c r="G3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J3" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>46150</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D4">
         <v>2180000</v>
@@ -1600,27 +1634,27 @@
         <v>270</v>
       </c>
       <c r="G4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J4" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>46150</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E5">
         <v>1808</v>
@@ -1629,27 +1663,27 @@
         <v>271</v>
       </c>
       <c r="G5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H5" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J5" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>46150</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="E6">
         <v>6850.19</v>
@@ -1658,18 +1692,18 @@
         <v>272</v>
       </c>
       <c r="G6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>46150</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D7">
         <v>6051000</v>
@@ -1678,27 +1712,27 @@
         <v>273</v>
       </c>
       <c r="G7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H7" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I7" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J7" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>46150</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D8">
         <v>985000</v>
@@ -1707,27 +1741,27 @@
         <v>274</v>
       </c>
       <c r="G8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H8" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I8" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J8" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>46150</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D9">
         <v>12348000</v>
@@ -1736,27 +1770,27 @@
         <v>275</v>
       </c>
       <c r="G9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H9" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I9" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J9" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>46150</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D10">
         <v>550000</v>
@@ -1765,27 +1799,27 @@
         <v>276</v>
       </c>
       <c r="G10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H10" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I10" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J10" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>46150</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D11">
         <v>57590000</v>
@@ -1794,20 +1828,20 @@
         <v>277</v>
       </c>
       <c r="G11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H11" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="I11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J11" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>46150</v>
       </c>
       <c r="B12" t="s">
@@ -1821,7 +1855,7 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>46150</v>
       </c>
       <c r="B13" t="s">
@@ -1835,14 +1869,14 @@
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>46150</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D14">
         <v>9590000</v>
@@ -1851,27 +1885,27 @@
         <v>280</v>
       </c>
       <c r="G14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H14" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I14" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J14" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>46150</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D15">
         <v>7900000</v>
@@ -1880,27 +1914,27 @@
         <v>281</v>
       </c>
       <c r="G15" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H15" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="I15" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="J15" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>46150</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E16">
         <v>2298</v>
@@ -1909,27 +1943,27 @@
         <v>282</v>
       </c>
       <c r="G16" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H16" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I16" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J16" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>46150</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="D17">
         <v>995000</v>
@@ -1938,27 +1972,27 @@
         <v>283</v>
       </c>
       <c r="G17" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H17" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I17" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J17" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>46150</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="E18">
         <v>1400</v>
@@ -1968,14 +2002,14 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>46150</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D19">
         <v>3528000</v>
@@ -1984,27 +2018,27 @@
         <v>285</v>
       </c>
       <c r="G19" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H19" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I19" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J19" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>46150</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D20">
         <v>4320000</v>
@@ -2013,27 +2047,27 @@
         <v>286</v>
       </c>
       <c r="G20" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H20" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I20" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J20" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>46150</v>
       </c>
       <c r="B21" t="s">
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D21">
         <v>1990000</v>
@@ -2042,27 +2076,27 @@
         <v>287</v>
       </c>
       <c r="G21" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H21" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I21" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J21" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>46150</v>
       </c>
       <c r="B22" t="s">
         <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="D22">
         <v>3990000</v>
@@ -2071,27 +2105,27 @@
         <v>288</v>
       </c>
       <c r="G22" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H22" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I22" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J22" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="3">
+      <c r="A23" s="2">
         <v>46150</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D23">
         <v>5190000</v>
@@ -2100,27 +2134,27 @@
         <v>289</v>
       </c>
       <c r="G23" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I23" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="J23" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>46150</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D24">
         <v>939000</v>
@@ -2129,27 +2163,27 @@
         <v>290</v>
       </c>
       <c r="G24" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H24" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I24" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J24" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>46150</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D25">
         <v>1080000</v>
@@ -2158,24 +2192,24 @@
         <v>291</v>
       </c>
       <c r="G25" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I25" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J25" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>46150</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="D26">
         <v>1500000</v>
@@ -2184,18 +2218,18 @@
         <v>292</v>
       </c>
       <c r="G26" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>46150</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="D27">
         <v>2890000</v>
@@ -2204,27 +2238,27 @@
         <v>293</v>
       </c>
       <c r="G27" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H27" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I27" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J27" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>46150</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D28">
         <v>3160000</v>
@@ -2233,27 +2267,27 @@
         <v>294</v>
       </c>
       <c r="G28" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H28" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I28" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J28" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="3">
+      <c r="A29" s="2">
         <v>46150</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E29">
         <v>1356</v>
@@ -2262,27 +2296,27 @@
         <v>295</v>
       </c>
       <c r="G29" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H29" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I29" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J29" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="3">
+      <c r="A30" s="2">
         <v>46150</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D30">
         <v>5190000</v>
@@ -2291,27 +2325,27 @@
         <v>296</v>
       </c>
       <c r="G30" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H30" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I30" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="J30" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="3">
+      <c r="A31" s="2">
         <v>46150</v>
       </c>
       <c r="B31" t="s">
         <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D31">
         <v>4590000</v>
@@ -2320,27 +2354,27 @@
         <v>297</v>
       </c>
       <c r="G31" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H31" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I31" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="J31" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>46150</v>
       </c>
       <c r="B32" t="s">
         <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D32">
         <v>13850000</v>
@@ -2349,27 +2383,27 @@
         <v>298</v>
       </c>
       <c r="G32" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H32" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I32" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J32" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="3">
+      <c r="A33" s="2">
         <v>46150</v>
       </c>
       <c r="B33" t="s">
         <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D33">
         <v>2370000</v>
@@ -2378,27 +2412,27 @@
         <v>299</v>
       </c>
       <c r="G33" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H33" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I33" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J33" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="3">
+      <c r="A34" s="2">
         <v>46150</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D34">
         <v>3160000</v>
@@ -2407,27 +2441,27 @@
         <v>301</v>
       </c>
       <c r="G34" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H34" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I34" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J34" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="3">
+      <c r="A35" s="2">
         <v>46150</v>
       </c>
       <c r="B35" t="s">
         <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D35">
         <v>199000</v>
@@ -2436,27 +2470,27 @@
         <v>302</v>
       </c>
       <c r="G35" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H35" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I35" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J35" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="3">
+      <c r="A36" s="2">
         <v>46150</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D36">
         <v>3290000</v>
@@ -2465,27 +2499,27 @@
         <v>303</v>
       </c>
       <c r="G36" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H36" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I36" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J36" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="3">
+      <c r="A37" s="2">
         <v>46150</v>
       </c>
       <c r="B37" t="s">
         <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="D37">
         <v>12080000</v>
@@ -2494,27 +2528,27 @@
         <v>304</v>
       </c>
       <c r="G37" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H37" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I37" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J37" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="3">
+      <c r="A38" s="2">
         <v>46150</v>
       </c>
       <c r="B38" t="s">
         <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D38">
         <v>2370000</v>
@@ -2523,27 +2557,27 @@
         <v>305</v>
       </c>
       <c r="G38" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H38" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I38" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J38" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="3">
+      <c r="A39" s="2">
         <v>46150</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D39">
         <v>199000</v>
@@ -2552,27 +2586,27 @@
         <v>306</v>
       </c>
       <c r="G39" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H39" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I39" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J39" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="3">
+      <c r="A40" s="2">
         <v>46150</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D40">
         <v>2590000</v>
@@ -2581,27 +2615,27 @@
         <v>307</v>
       </c>
       <c r="G40" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H40" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I40" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J40" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="3">
+      <c r="A41" s="2">
         <v>46150</v>
       </c>
       <c r="B41" t="s">
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D41">
         <v>6390000</v>
@@ -2610,27 +2644,27 @@
         <v>308</v>
       </c>
       <c r="G41" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H41" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I41" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J41" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="3">
+      <c r="A42" s="2">
         <v>46150</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D42">
         <v>6080000</v>
@@ -2639,27 +2673,27 @@
         <v>309</v>
       </c>
       <c r="G42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H42" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I42" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J42" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="3">
+      <c r="A43" s="2">
         <v>46150</v>
       </c>
       <c r="B43" t="s">
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D43">
         <v>7190000</v>
@@ -2668,20 +2702,20 @@
         <v>310</v>
       </c>
       <c r="G43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H43" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I43" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J43" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="3">
+      <c r="A44" s="2">
         <v>46150</v>
       </c>
       <c r="B44" t="s">
@@ -2695,14 +2729,14 @@
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="3">
+      <c r="A45" s="2">
         <v>46150</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="D45">
         <v>1090000</v>
@@ -2711,27 +2745,27 @@
         <v>312</v>
       </c>
       <c r="G45" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I45" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J45" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="3">
+      <c r="A46" s="2">
         <v>46150</v>
       </c>
       <c r="B46" t="s">
         <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D46">
         <v>1320000</v>
@@ -2740,27 +2774,27 @@
         <v>313</v>
       </c>
       <c r="G46" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H46" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I46" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J46" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="3">
+      <c r="A47" s="2">
         <v>46150</v>
       </c>
       <c r="B47" t="s">
         <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D47">
         <v>209000</v>
@@ -2769,27 +2803,27 @@
         <v>314</v>
       </c>
       <c r="G47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H47" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I47" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J47" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="3">
+      <c r="A48" s="2">
         <v>46150</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D48">
         <v>6445000</v>
@@ -2798,27 +2832,27 @@
         <v>315</v>
       </c>
       <c r="G48" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H48" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I48" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J48" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="3">
+      <c r="A49" s="2">
         <v>46150</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E49">
         <v>2712</v>
@@ -2827,27 +2861,27 @@
         <v>316</v>
       </c>
       <c r="G49" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H49" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I49" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J49" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="3">
+      <c r="A50" s="2">
         <v>46150</v>
       </c>
       <c r="B50" t="s">
         <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D50">
         <v>395000</v>
@@ -2856,27 +2890,27 @@
         <v>317</v>
       </c>
       <c r="G50" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H50" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I50" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="J50" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="3">
+      <c r="A51" s="2">
         <v>46150</v>
       </c>
       <c r="B51" t="s">
         <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D51">
         <v>812000</v>
@@ -2885,27 +2919,27 @@
         <v>318</v>
       </c>
       <c r="G51" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H51" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I51" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J51" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="3">
+      <c r="A52" s="2">
         <v>46150</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D52">
         <v>50000000</v>
@@ -2914,21 +2948,21 @@
         <v>319</v>
       </c>
       <c r="G52" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H52" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="3">
+      <c r="A53" s="2">
         <v>46150</v>
       </c>
       <c r="B53" t="s">
         <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="E53">
         <v>22390</v>
@@ -2937,27 +2971,27 @@
         <v>320</v>
       </c>
       <c r="G53" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H53" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I53" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J53" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="3">
+      <c r="A54" s="2">
         <v>46150</v>
       </c>
       <c r="B54" t="s">
         <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D54">
         <v>405000</v>
@@ -2966,27 +3000,27 @@
         <v>321</v>
       </c>
       <c r="G54" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H54" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I54" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J54" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="3">
+      <c r="A55" s="2">
         <v>46150</v>
       </c>
       <c r="B55" t="s">
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D55">
         <v>7512000</v>
@@ -2995,27 +3029,27 @@
         <v>322</v>
       </c>
       <c r="G55" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H55" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I55" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J55" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="3">
+      <c r="A56" s="2">
         <v>46150</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E56">
         <v>1356</v>
@@ -3024,27 +3058,27 @@
         <v>323</v>
       </c>
       <c r="G56" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H56" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I56" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J56" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="3">
+      <c r="A57" s="2">
         <v>46150</v>
       </c>
       <c r="B57" t="s">
         <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D57">
         <v>3790000</v>
@@ -3053,27 +3087,27 @@
         <v>324</v>
       </c>
       <c r="G57" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H57" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I57" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="J57" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="3">
+      <c r="A58" s="2">
         <v>46150</v>
       </c>
       <c r="B58" t="s">
         <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D58">
         <v>11790000</v>
@@ -3082,27 +3116,27 @@
         <v>325</v>
       </c>
       <c r="G58" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H58" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I58" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J58" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="3">
+      <c r="A59" s="2">
         <v>46150</v>
       </c>
       <c r="B59" t="s">
         <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D59">
         <v>498000</v>
@@ -3111,27 +3145,27 @@
         <v>326</v>
       </c>
       <c r="G59" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H59" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I59" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J59" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="3">
+      <c r="A60" s="2">
         <v>46150</v>
       </c>
       <c r="B60" t="s">
         <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D60">
         <v>3345000</v>
@@ -3140,27 +3174,27 @@
         <v>327</v>
       </c>
       <c r="G60" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H60" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I60" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J60" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="3">
+      <c r="A61" s="2">
         <v>46150</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D61">
         <v>2880000</v>
@@ -3169,27 +3203,27 @@
         <v>328</v>
       </c>
       <c r="G61" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H61" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I61" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J61" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="3">
+      <c r="A62" s="2">
         <v>46150</v>
       </c>
       <c r="B62" t="s">
         <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="D62">
         <v>419000</v>
@@ -3198,20 +3232,20 @@
         <v>329</v>
       </c>
       <c r="G62" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H62" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I62" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J62" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="3">
+      <c r="A63" s="2">
         <v>46150</v>
       </c>
       <c r="B63" t="s">
@@ -3225,14 +3259,14 @@
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="3">
+      <c r="A64" s="2">
         <v>46150</v>
       </c>
       <c r="B64" t="s">
         <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="D64">
         <v>14112000</v>
@@ -3241,27 +3275,27 @@
         <v>331</v>
       </c>
       <c r="G64" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H64" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I64" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J64" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="3">
+      <c r="A65" s="2">
         <v>46150</v>
       </c>
       <c r="B65" t="s">
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D65">
         <v>65000</v>
@@ -3270,27 +3304,27 @@
         <v>332</v>
       </c>
       <c r="G65" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H65" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I65" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J65" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="3">
+      <c r="A66" s="2">
         <v>46150</v>
       </c>
       <c r="B66" t="s">
         <v>65</v>
       </c>
       <c r="C66" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D66">
         <v>498000</v>
@@ -3299,27 +3333,27 @@
         <v>333</v>
       </c>
       <c r="G66" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H66" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I66" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J66" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="3">
+      <c r="A67" s="2">
         <v>46150</v>
       </c>
       <c r="B67" t="s">
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="D67">
         <v>1585000</v>
@@ -3328,27 +3362,27 @@
         <v>334</v>
       </c>
       <c r="G67" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H67" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I67" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J67" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="3">
+      <c r="A68" s="2">
         <v>46150</v>
       </c>
       <c r="B68" t="s">
         <v>46</v>
       </c>
       <c r="C68" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D68">
         <v>199000</v>
@@ -3357,20 +3391,20 @@
         <v>335</v>
       </c>
       <c r="G68" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H68" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I68" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J68" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="3">
+      <c r="A69" s="2">
         <v>46150</v>
       </c>
       <c r="B69" t="s">
@@ -3384,7 +3418,7 @@
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="3">
+      <c r="A70" s="2">
         <v>46150</v>
       </c>
       <c r="B70" t="s">
@@ -3398,14 +3432,14 @@
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="3">
+      <c r="A71" s="2">
         <v>46150</v>
       </c>
       <c r="B71" t="s">
         <v>72</v>
       </c>
       <c r="C71" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D71">
         <v>3160000</v>
@@ -3414,27 +3448,27 @@
         <v>338</v>
       </c>
       <c r="G71" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H71" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I71" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J71" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="3">
+      <c r="A72" s="2">
         <v>46150</v>
       </c>
       <c r="B72" t="s">
         <v>66</v>
       </c>
       <c r="C72" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D72">
         <v>3645000</v>
@@ -3443,27 +3477,27 @@
         <v>339</v>
       </c>
       <c r="G72" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H72" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="I72" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J72" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="3">
+      <c r="A73" s="2">
         <v>46150</v>
       </c>
       <c r="B73" t="s">
         <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D73">
         <v>890000</v>
@@ -3472,24 +3506,24 @@
         <v>340</v>
       </c>
       <c r="G73" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I73" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J73" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="3">
+      <c r="A74" s="2">
         <v>46150</v>
       </c>
       <c r="B74" t="s">
         <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D74">
         <v>3240000</v>
@@ -3498,24 +3532,24 @@
         <v>341</v>
       </c>
       <c r="G74" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I74" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J74" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="3">
+      <c r="A75" s="2">
         <v>46150</v>
       </c>
       <c r="B75" t="s">
         <v>75</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D75">
         <v>1970000</v>
@@ -3524,27 +3558,27 @@
         <v>342</v>
       </c>
       <c r="G75" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H75" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I75" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J75" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="3">
+      <c r="A76" s="2">
         <v>46150</v>
       </c>
       <c r="B76" t="s">
         <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D76">
         <v>1690000</v>
@@ -3553,27 +3587,27 @@
         <v>343</v>
       </c>
       <c r="G76" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H76" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="J76" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="3">
+      <c r="A77" s="2">
         <v>46150</v>
       </c>
       <c r="B77" t="s">
         <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D77">
         <v>6690000</v>
@@ -3582,27 +3616,27 @@
         <v>345</v>
       </c>
       <c r="G77" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H77" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J77" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="3">
+      <c r="A78" s="2">
         <v>46150</v>
       </c>
       <c r="B78" t="s">
         <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D78">
         <v>405000</v>
@@ -3611,27 +3645,27 @@
         <v>346</v>
       </c>
       <c r="G78" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H78" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I78" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J78" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="3">
+      <c r="A79" s="2">
         <v>46150</v>
       </c>
       <c r="B79" t="s">
         <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D79">
         <v>2370000</v>
@@ -3640,27 +3674,27 @@
         <v>347</v>
       </c>
       <c r="G79" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H79" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I79" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J79" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="3">
+      <c r="A80" s="2">
         <v>46150</v>
       </c>
       <c r="B80" t="s">
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E80">
         <v>6257.66</v>
@@ -3669,18 +3703,18 @@
         <v>348</v>
       </c>
       <c r="G80" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="3">
+      <c r="A81" s="2">
         <v>46150</v>
       </c>
       <c r="B81" t="s">
         <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="D81">
         <v>1635000</v>
@@ -3689,20 +3723,20 @@
         <v>349</v>
       </c>
       <c r="G81" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H81" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I81" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J81" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="3">
+      <c r="A82" s="2">
         <v>46150</v>
       </c>
       <c r="B82" t="s">
@@ -3716,14 +3750,14 @@
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="3">
+      <c r="A83" s="2">
         <v>46150</v>
       </c>
       <c r="B83" t="s">
         <v>25</v>
       </c>
       <c r="C83" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D83">
         <v>990000</v>
@@ -3732,27 +3766,27 @@
         <v>351</v>
       </c>
       <c r="G83" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H83" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I83" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J83" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="3">
+      <c r="A84" s="2">
         <v>46150</v>
       </c>
       <c r="B84" t="s">
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D84">
         <v>1580000</v>
@@ -3761,27 +3795,27 @@
         <v>352</v>
       </c>
       <c r="G84" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H84" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I84" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J84" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="3">
+      <c r="A85" s="2">
         <v>46150</v>
       </c>
       <c r="B85" t="s">
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D85">
         <v>1970000</v>
@@ -3790,27 +3824,27 @@
         <v>353</v>
       </c>
       <c r="G85" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H85" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I85" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J85" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="3">
+      <c r="A86" s="2">
         <v>46150</v>
       </c>
       <c r="B86" t="s">
         <v>37</v>
       </c>
       <c r="C86" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D86">
         <v>5190000</v>
@@ -3819,27 +3853,27 @@
         <v>354</v>
       </c>
       <c r="G86" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H86" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I86" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="J86" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="3">
+      <c r="A87" s="2">
         <v>46150</v>
       </c>
       <c r="B87" t="s">
         <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D87">
         <v>53800000</v>
@@ -3848,20 +3882,20 @@
         <v>355</v>
       </c>
       <c r="G87" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H87" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I87" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J87" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="3">
+      <c r="A88" s="2">
         <v>46150</v>
       </c>
       <c r="B88" t="s">
@@ -3875,14 +3909,14 @@
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="3">
+      <c r="A89" s="2">
         <v>46150</v>
       </c>
       <c r="B89" t="s">
         <v>85</v>
       </c>
       <c r="C89" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D89">
         <v>4320000</v>
@@ -3891,27 +3925,27 @@
         <v>357</v>
       </c>
       <c r="G89" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H89" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I89" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J89" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="3">
+      <c r="A90" s="2">
         <v>46150</v>
       </c>
       <c r="B90" t="s">
         <v>86</v>
       </c>
       <c r="C90" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D90">
         <v>1580000</v>
@@ -3920,27 +3954,27 @@
         <v>358</v>
       </c>
       <c r="G90" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H90" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I90" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J90" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="3">
+      <c r="A91" s="2">
         <v>46150</v>
       </c>
       <c r="B91" t="s">
         <v>87</v>
       </c>
       <c r="C91" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D91">
         <v>11976000</v>
@@ -3949,27 +3983,27 @@
         <v>359</v>
       </c>
       <c r="G91" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H91" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I91" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J91" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="3">
+      <c r="A92" s="2">
         <v>46150</v>
       </c>
       <c r="B92" t="s">
         <v>88</v>
       </c>
       <c r="C92" t="s">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="D92">
         <v>1990000</v>
@@ -3978,27 +4012,27 @@
         <v>360</v>
       </c>
       <c r="G92" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H92" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I92" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J92" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="3">
+      <c r="A93" s="2">
         <v>46150</v>
       </c>
       <c r="B93" t="s">
         <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D93">
         <v>3160000</v>
@@ -4007,27 +4041,27 @@
         <v>361</v>
       </c>
       <c r="G93" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H93" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I93" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J93" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="3">
+      <c r="A94" s="2">
         <v>46150</v>
       </c>
       <c r="B94" t="s">
         <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E94">
         <v>3616</v>
@@ -4036,27 +4070,27 @@
         <v>362</v>
       </c>
       <c r="G94" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H94" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I94" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J94" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="3">
+      <c r="A95" s="2">
         <v>46150</v>
       </c>
       <c r="B95" t="s">
         <v>90</v>
       </c>
       <c r="C95" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D95">
         <v>1980000</v>
@@ -4065,27 +4099,27 @@
         <v>363</v>
       </c>
       <c r="G95" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H95" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I95" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J95" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="3">
+      <c r="A96" s="2">
         <v>46150</v>
       </c>
       <c r="B96" t="s">
         <v>46</v>
       </c>
       <c r="C96" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D96">
         <v>199000</v>
@@ -4094,27 +4128,27 @@
         <v>364</v>
       </c>
       <c r="G96" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H96" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I96" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J96" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="3">
+      <c r="A97" s="2">
         <v>46150</v>
       </c>
       <c r="B97" t="s">
         <v>46</v>
       </c>
       <c r="C97" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D97">
         <v>199000</v>
@@ -4123,27 +4157,27 @@
         <v>365</v>
       </c>
       <c r="G97" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H97" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I97" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J97" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="3">
+      <c r="A98" s="2">
         <v>46150</v>
       </c>
       <c r="B98" t="s">
         <v>91</v>
       </c>
       <c r="C98" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D98">
         <v>2958000</v>
@@ -4152,27 +4186,27 @@
         <v>366</v>
       </c>
       <c r="G98" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H98" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I98" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J98" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="3">
+      <c r="A99" s="2">
         <v>46150</v>
       </c>
       <c r="B99" t="s">
         <v>92</v>
       </c>
       <c r="C99" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D99">
         <v>1980000</v>
@@ -4181,27 +4215,27 @@
         <v>367</v>
       </c>
       <c r="G99" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H99" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I99" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J99" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="3">
+      <c r="A100" s="2">
         <v>46150</v>
       </c>
       <c r="B100" t="s">
         <v>93</v>
       </c>
       <c r="C100" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D100">
         <v>790000</v>
@@ -4210,27 +4244,27 @@
         <v>368</v>
       </c>
       <c r="G100" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H100" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I100" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J100" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="3">
+      <c r="A101" s="2">
         <v>46150</v>
       </c>
       <c r="B101" t="s">
         <v>46</v>
       </c>
       <c r="C101" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D101">
         <v>200000</v>
@@ -4239,20 +4273,20 @@
         <v>369</v>
       </c>
       <c r="G101" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H101" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I101" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J101" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="3">
+      <c r="A102" s="2">
         <v>46150</v>
       </c>
       <c r="B102" t="s">
@@ -4266,14 +4300,14 @@
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="3">
+      <c r="A103" s="2">
         <v>46150</v>
       </c>
       <c r="B103" t="s">
         <v>93</v>
       </c>
       <c r="C103" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="D103">
         <v>790000</v>
@@ -4282,27 +4316,27 @@
         <v>371</v>
       </c>
       <c r="G103" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H103" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I103" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J103" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="3">
+      <c r="A104" s="2">
         <v>46150</v>
       </c>
       <c r="B104" t="s">
         <v>42</v>
       </c>
       <c r="C104" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D104">
         <v>199000</v>
@@ -4311,27 +4345,27 @@
         <v>372</v>
       </c>
       <c r="G104" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H104" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I104" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J104" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="3">
+      <c r="A105" s="2">
         <v>46150</v>
       </c>
       <c r="B105" t="s">
         <v>65</v>
       </c>
       <c r="C105" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D105">
         <v>498000</v>
@@ -4340,27 +4374,27 @@
         <v>373</v>
       </c>
       <c r="G105" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H105" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I105" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J105" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="3">
+      <c r="A106" s="2">
         <v>46150</v>
       </c>
       <c r="B106" t="s">
         <v>94</v>
       </c>
       <c r="C106" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D106">
         <v>7560000</v>
@@ -4369,27 +4403,27 @@
         <v>374</v>
       </c>
       <c r="G106" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H106" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I106" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J106" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="3">
+      <c r="A107" s="2">
         <v>46150</v>
       </c>
       <c r="B107" t="s">
         <v>95</v>
       </c>
       <c r="C107" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D107">
         <v>209000</v>
@@ -4398,27 +4432,27 @@
         <v>375</v>
       </c>
       <c r="G107" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H107" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I107" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J107" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="3">
+      <c r="A108" s="2">
         <v>46150</v>
       </c>
       <c r="B108" t="s">
         <v>96</v>
       </c>
       <c r="C108" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D108">
         <v>2880000</v>
@@ -4427,27 +4461,27 @@
         <v>376</v>
       </c>
       <c r="G108" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H108" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I108" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J108" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="3">
+      <c r="A109" s="2">
         <v>46150</v>
       </c>
       <c r="B109" t="s">
         <v>97</v>
       </c>
       <c r="C109" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D109">
         <v>775000</v>
@@ -4456,27 +4490,27 @@
         <v>377</v>
       </c>
       <c r="G109" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H109" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I109" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J109" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="3">
+      <c r="A110" s="2">
         <v>46150</v>
       </c>
       <c r="B110" t="s">
         <v>98</v>
       </c>
       <c r="C110" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E110">
         <v>3164</v>
@@ -4485,20 +4519,20 @@
         <v>378</v>
       </c>
       <c r="G110" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H110" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I110" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J110" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="3">
+      <c r="A111" s="2">
         <v>46150</v>
       </c>
       <c r="B111" t="s">
@@ -4512,7 +4546,7 @@
       </c>
     </row>
     <row r="112" spans="1:10">
-      <c r="A112" s="3">
+      <c r="A112" s="2">
         <v>46150</v>
       </c>
       <c r="B112" t="s">
@@ -4526,14 +4560,14 @@
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="3">
+      <c r="A113" s="2">
         <v>46150</v>
       </c>
       <c r="B113" t="s">
         <v>99</v>
       </c>
       <c r="C113" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D113">
         <v>6390000</v>
@@ -4542,27 +4576,27 @@
         <v>381</v>
       </c>
       <c r="G113" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H113" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I113" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J113" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="3">
+      <c r="A114" s="2">
         <v>46150</v>
       </c>
       <c r="B114" t="s">
         <v>100</v>
       </c>
       <c r="C114" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="D114">
         <v>1635000</v>
@@ -4571,27 +4605,27 @@
         <v>382</v>
       </c>
       <c r="G114" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H114" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I114" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J114" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="3">
+      <c r="A115" s="2">
         <v>46150</v>
       </c>
       <c r="B115" t="s">
         <v>101</v>
       </c>
       <c r="C115" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D115">
         <v>220000</v>
@@ -4600,27 +4634,27 @@
         <v>383</v>
       </c>
       <c r="G115" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H115" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I115" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J115" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="3">
+      <c r="A116" s="2">
         <v>46150</v>
       </c>
       <c r="B116" t="s">
         <v>97</v>
       </c>
       <c r="C116" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D116">
         <v>775000</v>
@@ -4629,20 +4663,20 @@
         <v>384</v>
       </c>
       <c r="G116" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H116" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I116" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J116" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:10">
-      <c r="A117" s="3">
+      <c r="A117" s="2">
         <v>46150</v>
       </c>
       <c r="B117" t="s">
@@ -4656,7 +4690,7 @@
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="3">
+      <c r="A118" s="2">
         <v>46150</v>
       </c>
       <c r="B118" t="s">
@@ -4670,14 +4704,14 @@
       </c>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="3">
+      <c r="A119" s="2">
         <v>46150</v>
       </c>
       <c r="B119" t="s">
         <v>102</v>
       </c>
       <c r="C119" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D119">
         <v>19404000</v>
@@ -4686,27 +4720,27 @@
         <v>387</v>
       </c>
       <c r="G119" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H119" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I119" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J119" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="3">
+      <c r="A120" s="2">
         <v>46150</v>
       </c>
       <c r="B120" t="s">
         <v>84</v>
       </c>
       <c r="C120" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D120">
         <v>53600000</v>
@@ -4715,27 +4749,27 @@
         <v>388</v>
       </c>
       <c r="G120" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H120" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I120" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J120" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" s="3">
+      <c r="A121" s="2">
         <v>46150</v>
       </c>
       <c r="B121" t="s">
         <v>99</v>
       </c>
       <c r="C121" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D121">
         <v>6300000</v>
@@ -4744,27 +4778,27 @@
         <v>389</v>
       </c>
       <c r="G121" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H121" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I121" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J121" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="122" spans="1:10">
-      <c r="A122" s="3">
+      <c r="A122" s="2">
         <v>46150</v>
       </c>
       <c r="B122" t="s">
         <v>103</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122">
         <v>19039000</v>
@@ -4773,27 +4807,27 @@
         <v>390</v>
       </c>
       <c r="G122" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H122" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I122" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J122" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="3">
+      <c r="A123" s="2">
         <v>46150</v>
       </c>
       <c r="B123" t="s">
         <v>104</v>
       </c>
       <c r="C123" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D123">
         <v>8981700</v>
@@ -4802,27 +4836,27 @@
         <v>391</v>
       </c>
       <c r="G123" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H123" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I123" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J123" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="3">
+      <c r="A124" s="2">
         <v>46150</v>
       </c>
       <c r="B124" t="s">
         <v>105</v>
       </c>
       <c r="C124" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D124">
         <v>265000</v>
@@ -4831,27 +4865,27 @@
         <v>392</v>
       </c>
       <c r="G124" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H124" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I124" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J124" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="3">
+      <c r="A125" s="2">
         <v>46150</v>
       </c>
       <c r="B125" t="s">
         <v>106</v>
       </c>
       <c r="C125" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D125">
         <v>990000</v>
@@ -4860,27 +4894,27 @@
         <v>393</v>
       </c>
       <c r="G125" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H125" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I125" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J125" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="126" spans="1:10">
-      <c r="A126" s="3">
+      <c r="A126" s="2">
         <v>46150</v>
       </c>
       <c r="B126" t="s">
         <v>107</v>
       </c>
       <c r="C126" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="E126">
         <v>815</v>
@@ -4890,14 +4924,14 @@
       </c>
     </row>
     <row r="127" spans="1:10">
-      <c r="A127" s="3">
+      <c r="A127" s="2">
         <v>46150</v>
       </c>
       <c r="B127" t="s">
         <v>108</v>
       </c>
       <c r="C127" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D127">
         <v>2160000</v>
@@ -4906,27 +4940,27 @@
         <v>395</v>
       </c>
       <c r="G127" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H127" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I127" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J127" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="128" spans="1:10">
-      <c r="A128" s="3">
+      <c r="A128" s="2">
         <v>46150</v>
       </c>
       <c r="B128" t="s">
         <v>109</v>
       </c>
       <c r="C128" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D128">
         <v>2370000</v>
@@ -4935,27 +4969,27 @@
         <v>396</v>
       </c>
       <c r="G128" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H128" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I128" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J128" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="129" spans="1:10">
-      <c r="A129" s="3">
+      <c r="A129" s="2">
         <v>46150</v>
       </c>
       <c r="B129" t="s">
         <v>110</v>
       </c>
       <c r="C129" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E129">
         <v>4972</v>
@@ -4964,20 +4998,20 @@
         <v>397</v>
       </c>
       <c r="G129" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H129" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I129" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J129" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="130" spans="1:10">
-      <c r="A130" s="3">
+      <c r="A130" s="2">
         <v>46150</v>
       </c>
       <c r="B130" t="s">
@@ -4991,14 +5025,14 @@
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" s="3">
+      <c r="A131" s="2">
         <v>46150</v>
       </c>
       <c r="B131" t="s">
         <v>111</v>
       </c>
       <c r="C131" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D131">
         <v>61779000</v>
@@ -5007,27 +5041,27 @@
         <v>399</v>
       </c>
       <c r="G131" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H131" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I131" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J131" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="132" spans="1:10">
-      <c r="A132" s="3">
+      <c r="A132" s="2">
         <v>46150</v>
       </c>
       <c r="B132" t="s">
         <v>112</v>
       </c>
       <c r="C132" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D132">
         <v>3600000</v>
@@ -5036,27 +5070,27 @@
         <v>400</v>
       </c>
       <c r="G132" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H132" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I132" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J132" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" s="3">
+      <c r="A133" s="2">
         <v>46150</v>
       </c>
       <c r="B133" t="s">
         <v>113</v>
       </c>
       <c r="C133" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D133">
         <v>2130000</v>
@@ -5065,27 +5099,27 @@
         <v>401</v>
       </c>
       <c r="G133" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H133" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I133" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="J133" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="3">
+      <c r="A134" s="2">
         <v>46150</v>
       </c>
       <c r="B134" t="s">
         <v>114</v>
       </c>
       <c r="C134" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D134">
         <v>996000</v>
@@ -5094,27 +5128,27 @@
         <v>402</v>
       </c>
       <c r="G134" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H134" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I134" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J134" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="A135" s="3">
+      <c r="A135" s="2">
         <v>46150</v>
       </c>
       <c r="B135" t="s">
         <v>115</v>
       </c>
       <c r="C135" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D135">
         <v>2370000</v>
@@ -5123,27 +5157,27 @@
         <v>403</v>
       </c>
       <c r="G135" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H135" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I135" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J135" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="136" spans="1:10">
-      <c r="A136" s="3">
+      <c r="A136" s="2">
         <v>46150</v>
       </c>
       <c r="B136" t="s">
         <v>116</v>
       </c>
       <c r="C136" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D136">
         <v>10990000</v>
@@ -5152,27 +5186,27 @@
         <v>404</v>
       </c>
       <c r="G136" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H136" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I136" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J136" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="137" spans="1:10">
-      <c r="A137" s="3">
+      <c r="A137" s="2">
         <v>46150</v>
       </c>
       <c r="B137" t="s">
         <v>117</v>
       </c>
       <c r="C137" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D137">
         <v>8640000</v>
@@ -5181,27 +5215,27 @@
         <v>405</v>
       </c>
       <c r="G137" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H137" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I137" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J137" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="3">
+      <c r="A138" s="2">
         <v>46150</v>
       </c>
       <c r="B138" t="s">
         <v>65</v>
       </c>
       <c r="C138" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D138">
         <v>498000</v>
@@ -5210,27 +5244,27 @@
         <v>406</v>
       </c>
       <c r="G138" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H138" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I138" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J138" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="3">
+      <c r="A139" s="2">
         <v>46150</v>
       </c>
       <c r="B139" t="s">
         <v>42</v>
       </c>
       <c r="C139" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D139">
         <v>200000</v>
@@ -5239,27 +5273,27 @@
         <v>407</v>
       </c>
       <c r="G139" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H139" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I139" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J139" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" s="3">
+      <c r="A140" s="2">
         <v>46150</v>
       </c>
       <c r="B140" t="s">
         <v>118</v>
       </c>
       <c r="C140" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="D140">
         <v>1080000</v>
@@ -5268,27 +5302,27 @@
         <v>408</v>
       </c>
       <c r="G140" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H140" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I140" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J140" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" s="3">
+      <c r="A141" s="2">
         <v>46150</v>
       </c>
       <c r="B141" t="s">
         <v>119</v>
       </c>
       <c r="C141" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D141">
         <v>1130000</v>
@@ -5297,27 +5331,27 @@
         <v>409</v>
       </c>
       <c r="G141" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H141" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I141" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J141" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="142" spans="1:10">
-      <c r="A142" s="3">
+      <c r="A142" s="2">
         <v>46150</v>
       </c>
       <c r="B142" t="s">
         <v>25</v>
       </c>
       <c r="C142" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="D142">
         <v>790000</v>
@@ -5326,20 +5360,20 @@
         <v>410</v>
       </c>
       <c r="G142" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H142" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I142" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J142" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="3">
+      <c r="A143" s="2">
         <v>46150</v>
       </c>
       <c r="B143" t="s">
@@ -5353,14 +5387,14 @@
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" s="3">
+      <c r="A144" s="2">
         <v>46150</v>
       </c>
       <c r="B144" t="s">
         <v>120</v>
       </c>
       <c r="C144" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D144">
         <v>1500000</v>
@@ -5369,27 +5403,27 @@
         <v>412</v>
       </c>
       <c r="G144" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H144" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I144" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J144" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" s="3">
+      <c r="A145" s="2">
         <v>46150</v>
       </c>
       <c r="B145" t="s">
         <v>121</v>
       </c>
       <c r="C145" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="D145">
         <v>1440000</v>
@@ -5398,27 +5432,27 @@
         <v>413</v>
       </c>
       <c r="G145" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H145" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I145" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J145" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="3">
+      <c r="A146" s="2">
         <v>46150</v>
       </c>
       <c r="B146" t="s">
         <v>97</v>
       </c>
       <c r="C146" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D146">
         <v>775000</v>
@@ -5427,27 +5461,27 @@
         <v>414</v>
       </c>
       <c r="G146" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H146" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I146" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J146" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="147" spans="1:10">
-      <c r="A147" s="3">
+      <c r="A147" s="2">
         <v>46150</v>
       </c>
       <c r="B147" t="s">
         <v>122</v>
       </c>
       <c r="C147" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D147">
         <v>545000</v>
@@ -5456,20 +5490,20 @@
         <v>415</v>
       </c>
       <c r="G147" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H147" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I147" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J147" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="148" spans="1:10">
-      <c r="A148" s="3">
+      <c r="A148" s="2">
         <v>46150</v>
       </c>
       <c r="B148" t="s">
@@ -5483,14 +5517,14 @@
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" s="3">
+      <c r="A149" s="2">
         <v>46150</v>
       </c>
       <c r="B149" t="s">
         <v>123</v>
       </c>
       <c r="C149" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D149">
         <v>56050000</v>
@@ -5499,27 +5533,27 @@
         <v>417</v>
       </c>
       <c r="G149" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H149" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I149" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J149" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" s="3">
+      <c r="A150" s="2">
         <v>46150</v>
       </c>
       <c r="B150" t="s">
         <v>124</v>
       </c>
       <c r="C150" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D150">
         <v>12000000</v>
@@ -5528,27 +5562,27 @@
         <v>418</v>
       </c>
       <c r="G150" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H150" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I150" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="J150" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="3">
+      <c r="A151" s="2">
         <v>46150</v>
       </c>
       <c r="B151" t="s">
         <v>41</v>
       </c>
       <c r="C151" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D151">
         <v>3160000</v>
@@ -5557,27 +5591,27 @@
         <v>419</v>
       </c>
       <c r="G151" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H151" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I151" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J151" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" s="3">
+      <c r="A152" s="2">
         <v>46150</v>
       </c>
       <c r="B152" t="s">
         <v>125</v>
       </c>
       <c r="C152" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D152">
         <v>5292000</v>
@@ -5586,27 +5620,27 @@
         <v>420</v>
       </c>
       <c r="G152" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H152" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I152" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J152" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="3">
+      <c r="A153" s="2">
         <v>46150</v>
       </c>
       <c r="B153" t="s">
         <v>123</v>
       </c>
       <c r="C153" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D153">
         <v>50500000</v>
@@ -5615,27 +5649,27 @@
         <v>421</v>
       </c>
       <c r="G153" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H153" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I153" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J153" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="3">
+      <c r="A154" s="2">
         <v>46150</v>
       </c>
       <c r="B154" t="s">
         <v>126</v>
       </c>
       <c r="C154" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D154">
         <v>5000000</v>
@@ -5644,27 +5678,27 @@
         <v>422</v>
       </c>
       <c r="G154" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H154" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="I154" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J154" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="3">
+      <c r="A155" s="2">
         <v>46150</v>
       </c>
       <c r="B155" t="s">
         <v>127</v>
       </c>
       <c r="C155" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D155">
         <v>65300000</v>
@@ -5673,27 +5707,27 @@
         <v>423</v>
       </c>
       <c r="G155" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H155" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I155" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J155" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="156" spans="1:10">
-      <c r="A156" s="3">
+      <c r="A156" s="2">
         <v>46150</v>
       </c>
       <c r="B156" t="s">
         <v>128</v>
       </c>
       <c r="C156" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D156">
         <v>1090000</v>
@@ -5702,27 +5736,27 @@
         <v>424</v>
       </c>
       <c r="G156" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H156" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I156" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J156" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="157" spans="1:10">
-      <c r="A157" s="3">
+      <c r="A157" s="2">
         <v>46150</v>
       </c>
       <c r="B157" t="s">
         <v>129</v>
       </c>
       <c r="C157" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="D157">
         <v>1080000</v>
@@ -5731,20 +5765,20 @@
         <v>425</v>
       </c>
       <c r="G157" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H157" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I157" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J157" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="158" spans="1:10">
-      <c r="A158" s="3">
+      <c r="A158" s="2">
         <v>46150</v>
       </c>
       <c r="B158" t="s">
@@ -5758,14 +5792,14 @@
       </c>
     </row>
     <row r="159" spans="1:10">
-      <c r="A159" s="3">
+      <c r="A159" s="2">
         <v>46150</v>
       </c>
       <c r="B159" t="s">
         <v>130</v>
       </c>
       <c r="C159" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D159">
         <v>5960500</v>
@@ -5774,27 +5808,27 @@
         <v>427</v>
       </c>
       <c r="G159" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H159" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I159" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J159" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="160" spans="1:10">
-      <c r="A160" s="3">
+      <c r="A160" s="2">
         <v>46150</v>
       </c>
       <c r="B160" t="s">
         <v>131</v>
       </c>
       <c r="C160" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D160">
         <v>67290000</v>
@@ -5803,27 +5837,27 @@
         <v>428</v>
       </c>
       <c r="G160" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H160" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I160" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J160" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="161" spans="1:10">
-      <c r="A161" s="3">
+      <c r="A161" s="2">
         <v>46150</v>
       </c>
       <c r="B161" t="s">
         <v>132</v>
       </c>
       <c r="C161" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
       <c r="D161">
         <v>4740000</v>
@@ -5832,27 +5866,27 @@
         <v>429</v>
       </c>
       <c r="G161" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H161" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I161" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J161" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="162" spans="1:10">
-      <c r="A162" s="3">
+      <c r="A162" s="2">
         <v>46150</v>
       </c>
       <c r="B162" t="s">
         <v>88</v>
       </c>
       <c r="C162" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D162">
         <v>1090000</v>
@@ -5861,27 +5895,27 @@
         <v>430</v>
       </c>
       <c r="G162" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H162" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I162" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J162" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="163" spans="1:10">
-      <c r="A163" s="3">
+      <c r="A163" s="2">
         <v>46150</v>
       </c>
       <c r="B163" t="s">
         <v>123</v>
       </c>
       <c r="C163" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D163">
         <v>53150000</v>
@@ -5890,27 +5924,27 @@
         <v>431</v>
       </c>
       <c r="G163" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H163" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I163" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J163" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="164" spans="1:10">
-      <c r="A164" s="3">
+      <c r="A164" s="2">
         <v>46150</v>
       </c>
       <c r="B164" t="s">
         <v>133</v>
       </c>
       <c r="C164" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D164">
         <v>220000</v>
@@ -5919,27 +5953,27 @@
         <v>432</v>
       </c>
       <c r="G164" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H164" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I164" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J164" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="165" spans="1:10">
-      <c r="A165" s="3">
+      <c r="A165" s="2">
         <v>46150</v>
       </c>
       <c r="B165" t="s">
         <v>134</v>
       </c>
       <c r="C165" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D165">
         <v>590000</v>
@@ -5948,27 +5982,27 @@
         <v>433</v>
       </c>
       <c r="G165" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H165" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I165" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J165" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="166" spans="1:10">
-      <c r="A166" s="3">
+      <c r="A166" s="2">
         <v>46150</v>
       </c>
       <c r="B166" t="s">
         <v>25</v>
       </c>
       <c r="C166" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D166">
         <v>939000</v>
@@ -5977,27 +6011,27 @@
         <v>434</v>
       </c>
       <c r="G166" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H166" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I166" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J166" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="167" spans="1:10">
-      <c r="A167" s="3">
+      <c r="A167" s="2">
         <v>46150</v>
       </c>
       <c r="B167" t="s">
         <v>135</v>
       </c>
       <c r="C167" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D167">
         <v>1970000</v>
@@ -6006,27 +6040,27 @@
         <v>435</v>
       </c>
       <c r="G167" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H167" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I167" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J167" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="168" spans="1:10">
-      <c r="A168" s="3">
+      <c r="A168" s="2">
         <v>46150</v>
       </c>
       <c r="B168" t="s">
         <v>136</v>
       </c>
       <c r="C168" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D168">
         <v>7560000</v>
@@ -6035,27 +6069,27 @@
         <v>436</v>
       </c>
       <c r="G168" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H168" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I168" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J168" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="169" spans="1:10">
-      <c r="A169" s="3">
+      <c r="A169" s="2">
         <v>46150</v>
       </c>
       <c r="B169" t="s">
         <v>99</v>
       </c>
       <c r="C169" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D169">
         <v>6590000</v>
@@ -6064,20 +6098,20 @@
         <v>437</v>
       </c>
       <c r="G169" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H169" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I169" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J169" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="170" spans="1:10">
-      <c r="A170" s="3">
+      <c r="A170" s="2">
         <v>46150</v>
       </c>
       <c r="B170" t="s">
@@ -6091,14 +6125,14 @@
       </c>
     </row>
     <row r="171" spans="1:10">
-      <c r="A171" s="3">
+      <c r="A171" s="2">
         <v>46150</v>
       </c>
       <c r="B171" t="s">
         <v>137</v>
       </c>
       <c r="C171" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D171">
         <v>25000000</v>
@@ -6107,14 +6141,14 @@
         <v>439</v>
       </c>
       <c r="G171" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H171" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="172" spans="1:10">
-      <c r="A172" s="3">
+      <c r="A172" s="2">
         <v>46150</v>
       </c>
       <c r="B172" t="s">
@@ -6128,14 +6162,14 @@
       </c>
     </row>
     <row r="173" spans="1:10">
-      <c r="A173" s="3">
+      <c r="A173" s="2">
         <v>46150</v>
       </c>
       <c r="B173" t="s">
         <v>138</v>
       </c>
       <c r="C173" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D173">
         <v>985000</v>
@@ -6144,20 +6178,20 @@
         <v>441</v>
       </c>
       <c r="G173" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H173" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I173" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J173" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="174" spans="1:10">
-      <c r="A174" s="3">
+      <c r="A174" s="2">
         <v>46150</v>
       </c>
       <c r="B174" t="s">
@@ -6171,14 +6205,14 @@
       </c>
     </row>
     <row r="175" spans="1:10">
-      <c r="A175" s="3">
+      <c r="A175" s="2">
         <v>46150</v>
       </c>
       <c r="B175" t="s">
         <v>139</v>
       </c>
       <c r="C175" t="s">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="D175">
         <v>4800000</v>
@@ -6187,27 +6221,27 @@
         <v>443</v>
       </c>
       <c r="G175" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H175" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I175" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J175" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="176" spans="1:10">
-      <c r="A176" s="3">
+      <c r="A176" s="2">
         <v>46150</v>
       </c>
       <c r="B176" t="s">
         <v>140</v>
       </c>
       <c r="C176" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D176">
         <v>1440000</v>
@@ -6216,20 +6250,20 @@
         <v>444</v>
       </c>
       <c r="G176" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H176" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I176" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J176" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="177" spans="1:10">
-      <c r="A177" s="3">
+      <c r="A177" s="2">
         <v>46150</v>
       </c>
       <c r="B177" t="s">
@@ -6245,27 +6279,27 @@
         <v>445</v>
       </c>
       <c r="G177" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H177" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I177" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J177" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="178" spans="1:10">
-      <c r="A178" s="3">
+      <c r="A178" s="2">
         <v>46150</v>
       </c>
       <c r="B178" t="s">
         <v>142</v>
       </c>
       <c r="C178" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D178">
         <v>2370000</v>
@@ -6274,27 +6308,27 @@
         <v>446</v>
       </c>
       <c r="G178" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H178" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I178" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J178" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="179" spans="1:10">
-      <c r="A179" s="3">
+      <c r="A179" s="2">
         <v>46150</v>
       </c>
       <c r="B179" t="s">
         <v>143</v>
       </c>
       <c r="C179" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D179">
         <v>2957500</v>
@@ -6303,20 +6337,20 @@
         <v>447</v>
       </c>
       <c r="G179" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H179" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I179" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J179" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="180" spans="1:10">
-      <c r="A180" s="3">
+      <c r="A180" s="2">
         <v>46150</v>
       </c>
       <c r="B180" t="s">
@@ -6332,27 +6366,27 @@
         <v>448</v>
       </c>
       <c r="G180" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H180" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I180" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J180" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="181" spans="1:10">
-      <c r="A181" s="3">
+      <c r="A181" s="2">
         <v>46150</v>
       </c>
       <c r="B181" t="s">
         <v>145</v>
       </c>
       <c r="C181" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E181">
         <v>1808</v>
@@ -6361,20 +6395,20 @@
         <v>449</v>
       </c>
       <c r="G181" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H181" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I181" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J181" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="182" spans="1:10">
-      <c r="A182" s="3">
+      <c r="A182" s="2">
         <v>46150</v>
       </c>
       <c r="B182" t="s">
@@ -6390,20 +6424,20 @@
         <v>450</v>
       </c>
       <c r="G182" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H182" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I182" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J182" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="183" spans="1:10">
-      <c r="A183" s="3">
+      <c r="A183" s="2">
         <v>46150</v>
       </c>
       <c r="B183" t="s">
@@ -6419,20 +6453,20 @@
         <v>451</v>
       </c>
       <c r="G183" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H183" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I183" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J183" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="184" spans="1:10">
-      <c r="A184" s="3">
+      <c r="A184" s="2">
         <v>46150</v>
       </c>
       <c r="B184" t="s">
@@ -6448,27 +6482,27 @@
         <v>452</v>
       </c>
       <c r="G184" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H184" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I184" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J184" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="185" spans="1:10">
-      <c r="A185" s="3">
+      <c r="A185" s="2">
         <v>46150</v>
       </c>
       <c r="B185" t="s">
         <v>147</v>
       </c>
       <c r="C185" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D185">
         <v>220000</v>
@@ -6477,27 +6511,27 @@
         <v>453</v>
       </c>
       <c r="G185" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H185" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I185" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J185" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="186" spans="1:10">
-      <c r="A186" s="3">
+      <c r="A186" s="2">
         <v>46150</v>
       </c>
       <c r="B186" t="s">
         <v>148</v>
       </c>
       <c r="C186" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D186">
         <v>5920000</v>
@@ -6506,27 +6540,27 @@
         <v>454</v>
       </c>
       <c r="G186" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H186" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I186" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J186" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="187" spans="1:10">
-      <c r="A187" s="3">
+      <c r="A187" s="2">
         <v>46150</v>
       </c>
       <c r="B187" t="s">
         <v>149</v>
       </c>
       <c r="C187" t="s">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="D187">
         <v>540000</v>
@@ -6535,27 +6569,27 @@
         <v>455</v>
       </c>
       <c r="G187" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H187" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I187" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J187" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="188" spans="1:10">
-      <c r="A188" s="3">
+      <c r="A188" s="2">
         <v>46150</v>
       </c>
       <c r="B188" t="s">
         <v>150</v>
       </c>
       <c r="C188" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D188">
         <v>25500000</v>
@@ -6564,14 +6598,14 @@
         <v>456</v>
       </c>
       <c r="G188" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H188" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="189" spans="1:10">
-      <c r="A189" s="3">
+      <c r="A189" s="2">
         <v>46150</v>
       </c>
       <c r="B189" t="s">
@@ -6587,20 +6621,20 @@
         <v>457</v>
       </c>
       <c r="G189" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H189" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I189" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J189" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="190" spans="1:10">
-      <c r="A190" s="3">
+      <c r="A190" s="2">
         <v>46150</v>
       </c>
       <c r="B190" t="s">
@@ -6616,20 +6650,20 @@
         <v>458</v>
       </c>
       <c r="G190" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H190" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I190" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J190" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="191" spans="1:10">
-      <c r="A191" s="3">
+      <c r="A191" s="2">
         <v>46150</v>
       </c>
       <c r="B191" t="s">
@@ -6645,27 +6679,27 @@
         <v>459</v>
       </c>
       <c r="G191" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H191" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I191" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J191" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="192" spans="1:10">
-      <c r="A192" s="3">
+      <c r="A192" s="2">
         <v>46150</v>
       </c>
       <c r="B192" t="s">
         <v>153</v>
       </c>
       <c r="C192" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="D192">
         <v>1580000</v>
@@ -6674,27 +6708,27 @@
         <v>460</v>
       </c>
       <c r="G192" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H192" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I192" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J192" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="193" spans="1:10">
-      <c r="A193" s="3">
+      <c r="A193" s="2">
         <v>46150</v>
       </c>
       <c r="B193" t="s">
         <v>123</v>
       </c>
       <c r="C193" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D193">
         <v>50500000</v>
@@ -6703,27 +6737,27 @@
         <v>461</v>
       </c>
       <c r="G193" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H193" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I193" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J193" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="194" spans="1:10">
-      <c r="A194" s="3">
+      <c r="A194" s="2">
         <v>46150</v>
       </c>
       <c r="B194" t="s">
         <v>42</v>
       </c>
       <c r="C194" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D194">
         <v>199000</v>
@@ -6732,27 +6766,27 @@
         <v>462</v>
       </c>
       <c r="G194" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H194" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I194" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J194" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="195" spans="1:10">
-      <c r="A195" s="3">
+      <c r="A195" s="2">
         <v>46150</v>
       </c>
       <c r="B195" t="s">
         <v>154</v>
       </c>
       <c r="C195" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D195">
         <v>1580000</v>
@@ -6761,27 +6795,27 @@
         <v>463</v>
       </c>
       <c r="G195" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H195" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I195" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J195" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="196" spans="1:10">
-      <c r="A196" s="3">
+      <c r="A196" s="2">
         <v>46150</v>
       </c>
       <c r="B196" t="s">
         <v>155</v>
       </c>
       <c r="C196" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D196">
         <v>419000</v>
@@ -6790,27 +6824,27 @@
         <v>464</v>
       </c>
       <c r="G196" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H196" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I196" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J196" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="1:10">
-      <c r="A197" s="3">
+      <c r="A197" s="2">
         <v>46150</v>
       </c>
       <c r="B197" t="s">
         <v>156</v>
       </c>
       <c r="C197" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D197">
         <v>8980000</v>
@@ -6819,27 +6853,27 @@
         <v>465</v>
       </c>
       <c r="G197" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H197" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I197" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J197" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="198" spans="1:10">
-      <c r="A198" s="3">
+      <c r="A198" s="2">
         <v>46150</v>
       </c>
       <c r="B198" t="s">
         <v>34</v>
       </c>
       <c r="C198" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D198">
         <v>2890000</v>
@@ -6848,27 +6882,27 @@
         <v>466</v>
       </c>
       <c r="G198" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H198" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I198" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J198" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="199" spans="1:10">
-      <c r="A199" s="3">
+      <c r="A199" s="2">
         <v>46150</v>
       </c>
       <c r="B199" t="s">
         <v>72</v>
       </c>
       <c r="C199" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D199">
         <v>3120000</v>
@@ -6877,27 +6911,27 @@
         <v>467</v>
       </c>
       <c r="G199" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H199" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I199" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J199" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="200" spans="1:10">
-      <c r="A200" s="3">
+      <c r="A200" s="2">
         <v>46150</v>
       </c>
       <c r="B200" t="s">
         <v>157</v>
       </c>
       <c r="C200" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D200">
         <v>1590000</v>
@@ -6906,20 +6940,20 @@
         <v>468</v>
       </c>
       <c r="G200" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H200" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I200" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="J200" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="201" spans="1:10">
-      <c r="A201" s="3">
+      <c r="A201" s="2">
         <v>46150</v>
       </c>
       <c r="B201" t="s">
@@ -6933,14 +6967,14 @@
       </c>
     </row>
     <row r="202" spans="1:10">
-      <c r="A202" s="3">
+      <c r="A202" s="2">
         <v>46150</v>
       </c>
       <c r="B202" t="s">
         <v>158</v>
       </c>
       <c r="C202" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D202">
         <v>14122000</v>
@@ -6949,27 +6983,27 @@
         <v>470</v>
       </c>
       <c r="G202" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H202" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I202" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J202" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="203" spans="1:10">
-      <c r="A203" s="3">
+      <c r="A203" s="2">
         <v>46150</v>
       </c>
       <c r="B203" t="s">
         <v>159</v>
       </c>
       <c r="C203" t="s">
-        <v>296</v>
+        <v>202</v>
       </c>
       <c r="E203">
         <v>1400</v>
@@ -6979,7 +7013,7 @@
       </c>
     </row>
     <row r="204" spans="1:10">
-      <c r="A204" s="3">
+      <c r="A204" s="2">
         <v>46150</v>
       </c>
       <c r="B204" t="s">
@@ -6993,14 +7027,14 @@
       </c>
     </row>
     <row r="205" spans="1:10">
-      <c r="A205" s="3">
+      <c r="A205" s="2">
         <v>46150</v>
       </c>
       <c r="B205" t="s">
         <v>160</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D205">
         <v>580000</v>
@@ -7009,27 +7043,27 @@
         <v>473</v>
       </c>
       <c r="G205" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H205" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I205" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J205" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="206" spans="1:10">
-      <c r="A206" s="3">
+      <c r="A206" s="2">
         <v>46150</v>
       </c>
       <c r="B206" t="s">
         <v>161</v>
       </c>
       <c r="C206" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D206">
         <v>2880000</v>
@@ -7038,27 +7072,27 @@
         <v>474</v>
       </c>
       <c r="G206" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H206" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I206" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J206" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="207" spans="1:10">
-      <c r="A207" s="3">
+      <c r="A207" s="2">
         <v>46150</v>
       </c>
       <c r="B207" t="s">
         <v>119</v>
       </c>
       <c r="C207" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D207">
         <v>1130000</v>
@@ -7067,27 +7101,27 @@
         <v>475</v>
       </c>
       <c r="G207" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H207" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I207" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J207" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="208" spans="1:10">
-      <c r="A208" s="3">
+      <c r="A208" s="2">
         <v>46150</v>
       </c>
       <c r="B208" t="s">
         <v>162</v>
       </c>
       <c r="C208" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D208">
         <v>50500000</v>
@@ -7096,27 +7130,27 @@
         <v>476</v>
       </c>
       <c r="G208" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H208" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I208" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J208" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="209" spans="1:10">
-      <c r="A209" s="3">
+      <c r="A209" s="2">
         <v>46150</v>
       </c>
       <c r="B209" t="s">
         <v>163</v>
       </c>
       <c r="C209" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D209">
         <v>65800000</v>
@@ -7125,27 +7159,27 @@
         <v>477</v>
       </c>
       <c r="G209" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H209" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I209" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J209" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="210" spans="1:10">
-      <c r="A210" s="3">
+      <c r="A210" s="2">
         <v>46150</v>
       </c>
       <c r="B210" t="s">
         <v>164</v>
       </c>
       <c r="C210" t="s">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="D210">
         <v>1080000</v>
@@ -7154,20 +7188,20 @@
         <v>478</v>
       </c>
       <c r="G210" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H210" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I210" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J210" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="211" spans="1:10">
-      <c r="A211" s="3">
+      <c r="A211" s="2">
         <v>46150</v>
       </c>
       <c r="B211" t="s">
@@ -7181,14 +7215,14 @@
       </c>
     </row>
     <row r="212" spans="1:10">
-      <c r="A212" s="3">
+      <c r="A212" s="2">
         <v>46150</v>
       </c>
       <c r="B212" t="s">
         <v>165</v>
       </c>
       <c r="C212" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D212">
         <v>1970000</v>
@@ -7197,27 +7231,27 @@
         <v>480</v>
       </c>
       <c r="G212" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H212" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I212" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J212" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="213" spans="1:10">
-      <c r="A213" s="3">
+      <c r="A213" s="2">
         <v>46150</v>
       </c>
       <c r="B213" t="s">
         <v>166</v>
       </c>
       <c r="C213" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E213">
         <v>4972</v>
@@ -7226,27 +7260,27 @@
         <v>481</v>
       </c>
       <c r="G213" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H213" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I213" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J213" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="A214" s="3">
+      <c r="A214" s="2">
         <v>46150</v>
       </c>
       <c r="B214" t="s">
         <v>143</v>
       </c>
       <c r="C214" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D214">
         <v>2934750</v>
@@ -7255,27 +7289,27 @@
         <v>482</v>
       </c>
       <c r="G214" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H214" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I214" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J214" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" s="3">
+      <c r="A215" s="2">
         <v>46150</v>
       </c>
       <c r="B215" t="s">
         <v>167</v>
       </c>
       <c r="C215" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D215">
         <v>395000</v>
@@ -7284,27 +7318,27 @@
         <v>483</v>
       </c>
       <c r="G215" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H215" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I215" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="J215" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="216" spans="1:10">
-      <c r="A216" s="3">
+      <c r="A216" s="2">
         <v>46150</v>
       </c>
       <c r="B216" t="s">
         <v>72</v>
       </c>
       <c r="C216" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D216">
         <v>3960000</v>
@@ -7313,20 +7347,20 @@
         <v>484</v>
       </c>
       <c r="G216" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H216" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I216" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J216" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="217" spans="1:10">
-      <c r="A217" s="3">
+      <c r="A217" s="2">
         <v>46150</v>
       </c>
       <c r="B217" t="s">
@@ -7340,14 +7374,14 @@
       </c>
     </row>
     <row r="218" spans="1:10">
-      <c r="A218" s="3">
+      <c r="A218" s="2">
         <v>46150</v>
       </c>
       <c r="B218" t="s">
         <v>168</v>
       </c>
       <c r="C218" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E218">
         <v>14955</v>
@@ -7356,21 +7390,21 @@
         <v>486</v>
       </c>
       <c r="G218" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H218" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="219" spans="1:10">
-      <c r="A219" s="3">
+      <c r="A219" s="2">
         <v>46150</v>
       </c>
       <c r="B219" t="s">
         <v>25</v>
       </c>
       <c r="C219" t="s">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="D219">
         <v>1000000</v>
@@ -7379,20 +7413,20 @@
         <v>487</v>
       </c>
       <c r="G219" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H219" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I219" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J219" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="220" spans="1:10">
-      <c r="A220" s="3">
+      <c r="A220" s="2">
         <v>46150</v>
       </c>
       <c r="B220" t="s">
@@ -7406,14 +7440,14 @@
       </c>
     </row>
     <row r="221" spans="1:10">
-      <c r="A221" s="3">
+      <c r="A221" s="2">
         <v>46150</v>
       </c>
       <c r="B221" t="s">
         <v>169</v>
       </c>
       <c r="C221" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="D221">
         <v>1580000</v>
@@ -7422,27 +7456,27 @@
         <v>489</v>
       </c>
       <c r="G221" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H221" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I221" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J221" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="222" spans="1:10">
-      <c r="A222" s="3">
+      <c r="A222" s="2">
         <v>46150</v>
       </c>
       <c r="B222" t="s">
         <v>170</v>
       </c>
       <c r="C222" t="s">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="D222">
         <v>1080000</v>
@@ -7451,27 +7485,27 @@
         <v>490</v>
       </c>
       <c r="G222" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H222" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I222" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J222" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="223" spans="1:10">
-      <c r="A223" s="3">
+      <c r="A223" s="2">
         <v>46150</v>
       </c>
       <c r="B223" t="s">
         <v>171</v>
       </c>
       <c r="C223" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D223">
         <v>6480000</v>
@@ -7480,27 +7514,27 @@
         <v>491</v>
       </c>
       <c r="G223" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H223" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I223" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J223" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="224" spans="1:10">
-      <c r="A224" s="3">
+      <c r="A224" s="2">
         <v>46150</v>
       </c>
       <c r="B224" t="s">
         <v>172</v>
       </c>
       <c r="C224" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D224">
         <v>18890000</v>
@@ -7509,27 +7543,27 @@
         <v>492</v>
       </c>
       <c r="G224" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H224" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I224" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J224" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="225" spans="1:11">
-      <c r="A225" s="3">
+      <c r="A225" s="2">
         <v>46150</v>
       </c>
       <c r="B225" t="s">
         <v>82</v>
       </c>
       <c r="C225" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D225">
         <v>1580000</v>
@@ -7538,27 +7572,27 @@
         <v>493</v>
       </c>
       <c r="G225" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H225" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I225" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J225" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="226" spans="1:11">
-      <c r="A226" s="3">
+      <c r="A226" s="2">
         <v>46150</v>
       </c>
       <c r="B226" t="s">
         <v>173</v>
       </c>
       <c r="C226" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E226">
         <v>1808</v>
@@ -7567,14 +7601,14 @@
         <v>494</v>
       </c>
       <c r="I226" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J226" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="227" spans="1:11">
-      <c r="A227" s="3">
+      <c r="A227" s="2">
         <v>46150</v>
       </c>
       <c r="B227" t="s">
@@ -7588,14 +7622,14 @@
       </c>
     </row>
     <row r="228" spans="1:11">
-      <c r="A228" s="3">
+      <c r="A228" s="2">
         <v>46150</v>
       </c>
       <c r="B228" t="s">
         <v>174</v>
       </c>
       <c r="C228" t="s">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="D228">
         <v>710000</v>
@@ -7604,27 +7638,27 @@
         <v>496</v>
       </c>
       <c r="G228" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H228" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I228" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J228" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="229" spans="1:11">
-      <c r="A229" s="3">
+      <c r="A229" s="2">
         <v>46150</v>
       </c>
       <c r="B229" t="s">
         <v>175</v>
       </c>
       <c r="C229" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D229">
         <v>3600000</v>
@@ -7633,20 +7667,20 @@
         <v>497</v>
       </c>
       <c r="G229" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H229" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I229" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J229" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="230" spans="1:11">
-      <c r="A230" s="3">
+      <c r="A230" s="2">
         <v>46150</v>
       </c>
       <c r="B230" t="s">
@@ -7662,27 +7696,27 @@
         <v>498</v>
       </c>
       <c r="G230" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H230" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I230" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J230" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="231" spans="1:11">
-      <c r="A231" s="3">
+      <c r="A231" s="2">
         <v>46150</v>
       </c>
       <c r="B231" t="s">
         <v>177</v>
       </c>
       <c r="C231" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D231">
         <v>5732000</v>
@@ -7691,27 +7725,27 @@
         <v>499</v>
       </c>
       <c r="G231" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H231" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I231" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J231" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="232" spans="1:11">
-      <c r="A232" s="3">
+      <c r="A232" s="2">
         <v>46150</v>
       </c>
       <c r="B232" t="s">
         <v>178</v>
       </c>
       <c r="C232" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D232">
         <v>2350000</v>
@@ -7720,27 +7754,27 @@
         <v>500</v>
       </c>
       <c r="G232" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H232" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I232" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J232" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="233" spans="1:11">
-      <c r="A233" s="3">
+      <c r="A233" s="2">
         <v>46150</v>
       </c>
       <c r="B233" t="s">
         <v>119</v>
       </c>
       <c r="C233" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D233">
         <v>1130000</v>
@@ -7749,27 +7783,27 @@
         <v>501</v>
       </c>
       <c r="G233" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H233" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I233" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J233" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="234" spans="1:11">
-      <c r="A234" s="3">
+      <c r="A234" s="2">
         <v>46150</v>
       </c>
       <c r="B234" t="s">
         <v>179</v>
       </c>
       <c r="C234" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D234">
         <v>6480000</v>
@@ -7778,27 +7812,27 @@
         <v>504</v>
       </c>
       <c r="G234" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H234" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I234" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J234" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
     </row>
     <row r="235" spans="1:11">
-      <c r="A235" s="3">
+      <c r="A235" s="2">
         <v>46150</v>
       </c>
       <c r="B235" t="s">
         <v>180</v>
       </c>
       <c r="C235" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="D235">
         <v>17659300</v>
@@ -7807,27 +7841,27 @@
         <v>502</v>
       </c>
       <c r="G235" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H235" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I235" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J235" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
     </row>
     <row r="236" spans="1:11">
-      <c r="A236" s="3">
+      <c r="A236" s="2">
         <v>46150</v>
       </c>
       <c r="B236" t="s">
         <v>11</v>
       </c>
       <c r="C236" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D236">
         <v>985000</v>
@@ -7836,24 +7870,24 @@
         <v>505</v>
       </c>
       <c r="G236" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H236" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J236" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
     </row>
     <row r="237" spans="1:11">
-      <c r="A237" s="3">
+      <c r="A237" s="2">
         <v>46150</v>
       </c>
       <c r="B237" t="s">
         <v>181</v>
       </c>
       <c r="C237" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D237">
         <v>1580000</v>
@@ -7862,30 +7896,30 @@
         <v>506</v>
       </c>
       <c r="G237" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H237" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I237" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J237" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="K237" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
     </row>
     <row r="238" spans="1:11">
-      <c r="A238" s="3">
+      <c r="A238" s="2">
         <v>46150</v>
       </c>
       <c r="B238" t="s">
         <v>182</v>
       </c>
       <c r="C238" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D238">
         <v>50500000</v>
@@ -7894,30 +7928,30 @@
         <v>503</v>
       </c>
       <c r="G238" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H238" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I238" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J238" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="K238" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="239" spans="1:11">
-      <c r="A239" s="3">
+      <c r="A239" s="2">
         <v>46150</v>
       </c>
       <c r="B239" t="s">
         <v>183</v>
       </c>
       <c r="C239" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D239">
         <v>7063720</v>
@@ -7926,30 +7960,30 @@
         <v>507</v>
       </c>
       <c r="G239" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H239" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I239" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J239" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="K239" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="240" spans="1:11">
-      <c r="A240" s="3">
+      <c r="A240" s="2">
         <v>46150</v>
       </c>
       <c r="B240" t="s">
         <v>184</v>
       </c>
       <c r="C240" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D240">
         <v>990000</v>
@@ -7958,30 +7992,30 @@
         <v>508</v>
       </c>
       <c r="G240" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H240" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I240" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J240" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="K240" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="241" spans="1:11">
-      <c r="A241" s="3">
+      <c r="A241" s="2">
         <v>46150</v>
       </c>
       <c r="B241" t="s">
         <v>185</v>
       </c>
       <c r="C241" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E241">
         <v>3616</v>
@@ -7990,30 +8024,30 @@
         <v>510</v>
       </c>
       <c r="G241" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H241" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I241" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J241" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="K241" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
     </row>
     <row r="242" spans="1:11">
-      <c r="A242" s="3">
+      <c r="A242" s="2">
         <v>46150</v>
       </c>
       <c r="B242" t="s">
         <v>186</v>
       </c>
       <c r="C242" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D242">
         <v>1580000</v>
@@ -8022,30 +8056,30 @@
         <v>511</v>
       </c>
       <c r="G242" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H242" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I242" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J242" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="K242" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="243" spans="1:11">
-      <c r="A243" s="3">
+      <c r="A243" s="2">
         <v>46150</v>
       </c>
       <c r="B243" t="s">
         <v>187</v>
       </c>
       <c r="C243" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E243">
         <v>7625</v>
@@ -8054,19 +8088,371 @@
         <v>512</v>
       </c>
       <c r="G243" t="s">
+        <v>307</v>
+      </c>
+      <c r="H243" t="s">
+        <v>319</v>
+      </c>
+      <c r="I243" t="s">
+        <v>347</v>
+      </c>
+      <c r="J243" t="s">
+        <v>372</v>
+      </c>
+      <c r="K243" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11">
+      <c r="A244" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B244" t="s">
+        <v>188</v>
+      </c>
+      <c r="C244" t="s">
+        <v>301</v>
+      </c>
+      <c r="E244">
+        <v>7625</v>
+      </c>
+      <c r="F244">
+        <v>512</v>
+      </c>
+      <c r="G244" t="s">
+        <v>310</v>
+      </c>
+      <c r="H244" t="s">
+        <v>319</v>
+      </c>
+      <c r="I244" t="s">
+        <v>347</v>
+      </c>
+      <c r="J244" t="s">
+        <v>372</v>
+      </c>
+      <c r="K244" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11">
+      <c r="A245" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B245" t="s">
+        <v>189</v>
+      </c>
+      <c r="C245" t="s">
+        <v>209</v>
+      </c>
+      <c r="D245">
+        <v>2880000</v>
+      </c>
+      <c r="F245">
+        <v>513</v>
+      </c>
+      <c r="G245" t="s">
+        <v>310</v>
+      </c>
+      <c r="H245" t="s">
+        <v>319</v>
+      </c>
+      <c r="I245" t="s">
+        <v>361</v>
+      </c>
+      <c r="J245" t="s">
+        <v>372</v>
+      </c>
+      <c r="K245" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11">
+      <c r="A246" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B246" t="s">
+        <v>190</v>
+      </c>
+      <c r="C246" t="s">
+        <v>302</v>
+      </c>
+      <c r="D246">
+        <v>775000</v>
+      </c>
+      <c r="F246">
+        <v>514</v>
+      </c>
+      <c r="G246" t="s">
+        <v>309</v>
+      </c>
+      <c r="H246" t="s">
+        <v>319</v>
+      </c>
+      <c r="I246" t="s">
+        <v>362</v>
+      </c>
+      <c r="J246" t="s">
+        <v>372</v>
+      </c>
+      <c r="K246" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11">
+      <c r="A247" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B247" t="s">
+        <v>191</v>
+      </c>
+      <c r="C247" t="s">
+        <v>303</v>
+      </c>
+      <c r="D247">
+        <v>199000</v>
+      </c>
+      <c r="F247">
+        <v>515</v>
+      </c>
+      <c r="G247" t="s">
+        <v>309</v>
+      </c>
+      <c r="H247" t="s">
+        <v>319</v>
+      </c>
+      <c r="I247" t="s">
+        <v>330</v>
+      </c>
+      <c r="J247" t="s">
+        <v>372</v>
+      </c>
+      <c r="K247" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11">
+      <c r="A248" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B248" t="s">
+        <v>192</v>
+      </c>
+      <c r="C248" t="s">
+        <v>200</v>
+      </c>
+      <c r="D248">
+        <v>1080000</v>
+      </c>
+      <c r="F248">
+        <v>516</v>
+      </c>
+      <c r="G248" t="s">
+        <v>307</v>
+      </c>
+      <c r="H248" t="s">
+        <v>319</v>
+      </c>
+      <c r="I248" t="s">
+        <v>363</v>
+      </c>
+      <c r="J248" t="s">
+        <v>372</v>
+      </c>
+      <c r="K248" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11">
+      <c r="A249" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B249" t="s">
+        <v>193</v>
+      </c>
+      <c r="C249" t="s">
         <v>304</v>
       </c>
-      <c r="H243" t="s">
-        <v>315</v>
-      </c>
-      <c r="I243" t="s">
-        <v>343</v>
-      </c>
-      <c r="J243" t="s">
-        <v>361</v>
-      </c>
-      <c r="K243" t="s">
-        <v>368</v>
+      <c r="D249">
+        <v>1180000</v>
+      </c>
+      <c r="F249">
+        <v>517</v>
+      </c>
+      <c r="G249" t="s">
+        <v>309</v>
+      </c>
+      <c r="H249" t="s">
+        <v>319</v>
+      </c>
+      <c r="I249" t="s">
+        <v>364</v>
+      </c>
+      <c r="J249" t="s">
+        <v>372</v>
+      </c>
+      <c r="K249" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11">
+      <c r="A250" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B250" t="s">
+        <v>194</v>
+      </c>
+      <c r="C250" t="s">
+        <v>266</v>
+      </c>
+      <c r="D250">
+        <v>950000</v>
+      </c>
+      <c r="F250">
+        <v>518</v>
+      </c>
+      <c r="G250" t="s">
+        <v>307</v>
+      </c>
+      <c r="H250" t="s">
+        <v>319</v>
+      </c>
+      <c r="I250" t="s">
+        <v>365</v>
+      </c>
+      <c r="J250" t="s">
+        <v>372</v>
+      </c>
+      <c r="K250" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11">
+      <c r="A251" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B251" t="s">
+        <v>195</v>
+      </c>
+      <c r="C251" t="s">
+        <v>271</v>
+      </c>
+      <c r="D251">
+        <v>2180000</v>
+      </c>
+      <c r="F251">
+        <v>519</v>
+      </c>
+      <c r="G251" t="s">
+        <v>307</v>
+      </c>
+      <c r="H251" t="s">
+        <v>319</v>
+      </c>
+      <c r="I251" t="s">
+        <v>366</v>
+      </c>
+      <c r="J251" t="s">
+        <v>372</v>
+      </c>
+      <c r="K251" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11">
+      <c r="A252" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B252" t="s">
+        <v>191</v>
+      </c>
+      <c r="C252" t="s">
+        <v>260</v>
+      </c>
+      <c r="D252">
+        <v>219000</v>
+      </c>
+      <c r="F252">
+        <v>520</v>
+      </c>
+      <c r="G252" t="s">
+        <v>310</v>
+      </c>
+      <c r="H252" t="s">
+        <v>319</v>
+      </c>
+      <c r="I252" t="s">
+        <v>330</v>
+      </c>
+      <c r="J252" t="s">
+        <v>372</v>
+      </c>
+      <c r="K252" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11">
+      <c r="A253" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B253" t="s">
+        <v>196</v>
+      </c>
+      <c r="C253" t="s">
+        <v>246</v>
+      </c>
+      <c r="D253">
+        <v>3090000</v>
+      </c>
+      <c r="F253" t="s">
+        <v>305</v>
+      </c>
+      <c r="G253" t="s">
+        <v>310</v>
+      </c>
+      <c r="H253" t="s">
+        <v>319</v>
+      </c>
+      <c r="I253" t="s">
+        <v>327</v>
+      </c>
+      <c r="J253" t="s">
+        <v>372</v>
+      </c>
+      <c r="K253" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11">
+      <c r="A254" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B254" t="s">
+        <v>197</v>
+      </c>
+      <c r="C254" t="s">
+        <v>203</v>
+      </c>
+      <c r="D254">
+        <v>169000</v>
+      </c>
+      <c r="F254" t="s">
+        <v>306</v>
+      </c>
+      <c r="G254" t="s">
+        <v>307</v>
+      </c>
+      <c r="H254" t="s">
+        <v>319</v>
+      </c>
+      <c r="I254" t="s">
+        <v>367</v>
+      </c>
+      <c r="J254" t="s">
+        <v>372</v>
+      </c>
+      <c r="K254" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
